--- a/examples/ltd-latest/Vatreturns.xlsx
+++ b/examples/ltd-latest/Vatreturns.xlsx
@@ -1217,6 +1217,11 @@
       <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
       <sheetData sheetId="11">
+        <row r="10">
+          <cell r="B10">
+            <v>45777</v>
+          </cell>
+        </row>
         <row r="12">
           <cell r="B12">
             <v>45808</v>
@@ -1350,21 +1355,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="3">
-        <row r="1">
-          <cell r="G1">
-            <v>0</v>
-          </cell>
-          <cell r="H1">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="G4">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
@@ -1438,16 +1429,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="3">
-        <row r="1">
-          <cell r="G1">
-            <v>0</v>
-          </cell>
-          <cell r="H1">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
@@ -1622,7 +1604,7 @@
       <c r="I2" s="14"/>
       <c r="K2" s="15" t="n">
         <f aca="false">Vatinterface!B6</f>
-        <v>45869</v>
+        <v>45838</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1639,7 +1621,7 @@
       <c r="I3" s="14"/>
       <c r="K3" s="15" t="n">
         <f aca="false">Vatinterface!B7</f>
-        <v>45900</v>
+        <v>45869</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1656,7 +1638,7 @@
       <c r="I4" s="14"/>
       <c r="K4" s="15" t="n">
         <f aca="false">Vatinterface!B8</f>
-        <v>45930</v>
+        <v>45900</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1669,13 +1651,13 @@
       </c>
       <c r="F5" s="26"/>
       <c r="G5" s="27" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="14"/>
       <c r="K5" s="15" t="n">
         <f aca="false">Vatinterface!B9</f>
-        <v>45961</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1690,7 +1672,7 @@
       <c r="I6" s="14"/>
       <c r="K6" s="15" t="n">
         <f aca="false">Vatinterface!B10</f>
-        <v>45991</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1710,7 +1692,7 @@
       <c r="I7" s="14"/>
       <c r="K7" s="15" t="n">
         <f aca="false">Vatinterface!B11</f>
-        <v>46022</v>
+        <v>45991</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1725,7 +1707,7 @@
       <c r="I8" s="14"/>
       <c r="K8" s="15" t="n">
         <f aca="false">Vatinterface!B12</f>
-        <v>46053</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1747,7 +1729,7 @@
       <c r="I9" s="14"/>
       <c r="K9" s="15" t="n">
         <f aca="false">Vatinterface!B13</f>
-        <v>46081</v>
+        <v>46053</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1762,7 +1744,7 @@
       <c r="I10" s="14"/>
       <c r="K10" s="15" t="n">
         <f aca="false">Vatinterface!B14</f>
-        <v>46112</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1783,7 +1765,7 @@
       <c r="I11" s="14"/>
       <c r="K11" s="15" t="n">
         <f aca="false">Vatinterface!B15</f>
-        <v>46142</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1798,7 +1780,7 @@
       <c r="I12" s="14"/>
       <c r="K12" s="15" t="n">
         <f aca="false">Vatinterface!B16</f>
-        <v>46173</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1820,7 +1802,7 @@
       <c r="I13" s="14"/>
       <c r="K13" s="15" t="n">
         <f aca="false">Vatinterface!B17</f>
-        <v>46203</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1835,7 +1817,7 @@
       <c r="I14" s="14"/>
       <c r="K14" s="15" t="n">
         <f aca="false">Vatinterface!B18</f>
-        <v>0</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13426,7 +13408,7 @@
       <c r="I2" s="14"/>
       <c r="K2" s="15" t="n">
         <f aca="false">Vatinterface!B6</f>
-        <v>45869</v>
+        <v>45838</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13443,7 +13425,7 @@
       <c r="I3" s="14"/>
       <c r="K3" s="15" t="n">
         <f aca="false">Vatinterface!B7</f>
-        <v>45900</v>
+        <v>45869</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13460,7 +13442,7 @@
       <c r="I4" s="14"/>
       <c r="K4" s="15" t="n">
         <f aca="false">Vatinterface!B8</f>
-        <v>45930</v>
+        <v>45900</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13473,13 +13455,13 @@
       </c>
       <c r="F5" s="26"/>
       <c r="G5" s="27" t="n">
-        <v>46387</v>
+        <v>46356</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="14"/>
       <c r="K5" s="15" t="n">
         <f aca="false">Vatinterface!B9</f>
-        <v>45961</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13494,7 +13476,7 @@
       <c r="I6" s="14"/>
       <c r="K6" s="15" t="n">
         <f aca="false">Vatinterface!B10</f>
-        <v>45991</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13514,7 +13496,7 @@
       <c r="I7" s="14"/>
       <c r="K7" s="15" t="n">
         <f aca="false">Vatinterface!B11</f>
-        <v>46022</v>
+        <v>45991</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13529,7 +13511,7 @@
       <c r="I8" s="14"/>
       <c r="K8" s="15" t="n">
         <f aca="false">Vatinterface!B12</f>
-        <v>46053</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13551,7 +13533,7 @@
       <c r="I9" s="14"/>
       <c r="K9" s="15" t="n">
         <f aca="false">Vatinterface!B13</f>
-        <v>46081</v>
+        <v>46053</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13566,7 +13548,7 @@
       <c r="I10" s="14"/>
       <c r="K10" s="15" t="n">
         <f aca="false">Vatinterface!B14</f>
-        <v>46112</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13587,7 +13569,7 @@
       <c r="I11" s="14"/>
       <c r="K11" s="15" t="n">
         <f aca="false">Vatinterface!B15</f>
-        <v>46142</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13602,7 +13584,7 @@
       <c r="I12" s="14"/>
       <c r="K12" s="15" t="n">
         <f aca="false">Vatinterface!B16</f>
-        <v>46173</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13624,7 +13606,7 @@
       <c r="I13" s="14"/>
       <c r="K13" s="15" t="n">
         <f aca="false">Vatinterface!B17</f>
-        <v>46203</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13639,7 +13621,7 @@
       <c r="I14" s="14"/>
       <c r="K14" s="15" t="n">
         <f aca="false">Vatinterface!B18</f>
-        <v>0</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13990,7 +13972,7 @@
       <c r="I2" s="14"/>
       <c r="K2" s="15" t="n">
         <f aca="false">Vatinterface!B6</f>
-        <v>45869</v>
+        <v>45838</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14007,7 +13989,7 @@
       <c r="I3" s="14"/>
       <c r="K3" s="15" t="n">
         <f aca="false">Vatinterface!B7</f>
-        <v>45900</v>
+        <v>45869</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14024,7 +14006,7 @@
       <c r="I4" s="14"/>
       <c r="K4" s="15" t="n">
         <f aca="false">Vatinterface!B8</f>
-        <v>45930</v>
+        <v>45900</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14037,13 +14019,13 @@
       </c>
       <c r="F5" s="26"/>
       <c r="G5" s="27" t="n">
-        <v>46477</v>
+        <v>46446</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="14"/>
       <c r="K5" s="15" t="n">
         <f aca="false">Vatinterface!B9</f>
-        <v>45961</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14058,7 +14040,7 @@
       <c r="I6" s="14"/>
       <c r="K6" s="15" t="n">
         <f aca="false">Vatinterface!B10</f>
-        <v>45991</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14078,7 +14060,7 @@
       <c r="I7" s="14"/>
       <c r="K7" s="15" t="n">
         <f aca="false">Vatinterface!B11</f>
-        <v>46022</v>
+        <v>45991</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14093,7 +14075,7 @@
       <c r="I8" s="14"/>
       <c r="K8" s="15" t="n">
         <f aca="false">Vatinterface!B12</f>
-        <v>46053</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14115,7 +14097,7 @@
       <c r="I9" s="14"/>
       <c r="K9" s="15" t="n">
         <f aca="false">Vatinterface!B13</f>
-        <v>46081</v>
+        <v>46053</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14130,7 +14112,7 @@
       <c r="I10" s="14"/>
       <c r="K10" s="15" t="n">
         <f aca="false">Vatinterface!B14</f>
-        <v>46112</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14151,7 +14133,7 @@
       <c r="I11" s="14"/>
       <c r="K11" s="15" t="n">
         <f aca="false">Vatinterface!B15</f>
-        <v>46142</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14166,7 +14148,7 @@
       <c r="I12" s="14"/>
       <c r="K12" s="15" t="n">
         <f aca="false">Vatinterface!B16</f>
-        <v>46173</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14188,7 +14170,7 @@
       <c r="I13" s="14"/>
       <c r="K13" s="15" t="n">
         <f aca="false">Vatinterface!B17</f>
-        <v>46203</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14203,7 +14185,7 @@
       <c r="I14" s="14"/>
       <c r="K14" s="15" t="n">
         <f aca="false">Vatinterface!B18</f>
-        <v>0</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14554,7 +14536,7 @@
       <c r="I2" s="14"/>
       <c r="K2" s="15" t="n">
         <f aca="false">Vatinterface!B6</f>
-        <v>45869</v>
+        <v>45838</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14571,7 +14553,7 @@
       <c r="I3" s="14"/>
       <c r="K3" s="15" t="n">
         <f aca="false">Vatinterface!B7</f>
-        <v>45900</v>
+        <v>45869</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14588,7 +14570,7 @@
       <c r="I4" s="14"/>
       <c r="K4" s="15" t="n">
         <f aca="false">Vatinterface!B8</f>
-        <v>45930</v>
+        <v>45900</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14601,13 +14583,13 @@
       </c>
       <c r="F5" s="26"/>
       <c r="G5" s="27" t="n">
-        <v>46568</v>
+        <v>46538</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="14"/>
       <c r="K5" s="15" t="n">
         <f aca="false">Vatinterface!B9</f>
-        <v>45961</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14622,7 +14604,7 @@
       <c r="I6" s="14"/>
       <c r="K6" s="15" t="n">
         <f aca="false">Vatinterface!B10</f>
-        <v>45991</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14642,7 +14624,7 @@
       <c r="I7" s="14"/>
       <c r="K7" s="15" t="n">
         <f aca="false">Vatinterface!B11</f>
-        <v>46022</v>
+        <v>45991</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14657,7 +14639,7 @@
       <c r="I8" s="14"/>
       <c r="K8" s="15" t="n">
         <f aca="false">Vatinterface!B12</f>
-        <v>46053</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14679,7 +14661,7 @@
       <c r="I9" s="14"/>
       <c r="K9" s="15" t="n">
         <f aca="false">Vatinterface!B13</f>
-        <v>46081</v>
+        <v>46053</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14694,7 +14676,7 @@
       <c r="I10" s="14"/>
       <c r="K10" s="15" t="n">
         <f aca="false">Vatinterface!B14</f>
-        <v>46112</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14715,7 +14697,7 @@
       <c r="I11" s="14"/>
       <c r="K11" s="15" t="n">
         <f aca="false">Vatinterface!B15</f>
-        <v>46142</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14730,7 +14712,7 @@
       <c r="I12" s="14"/>
       <c r="K12" s="15" t="n">
         <f aca="false">Vatinterface!B16</f>
-        <v>46173</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14752,7 +14734,7 @@
       <c r="I13" s="14"/>
       <c r="K13" s="15" t="n">
         <f aca="false">Vatinterface!B17</f>
-        <v>46203</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14767,7 +14749,7 @@
       <c r="I14" s="14"/>
       <c r="K14" s="15" t="n">
         <f aca="false">Vatinterface!B18</f>
-        <v>0</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15118,7 +15100,7 @@
       <c r="I2" s="14"/>
       <c r="K2" s="15" t="n">
         <f aca="false">Vatinterface!B6</f>
-        <v>45869</v>
+        <v>45838</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15135,7 +15117,7 @@
       <c r="I3" s="14"/>
       <c r="K3" s="15" t="n">
         <f aca="false">Vatinterface!B7</f>
-        <v>45900</v>
+        <v>45869</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15152,7 +15134,7 @@
       <c r="I4" s="14"/>
       <c r="K4" s="15" t="n">
         <f aca="false">Vatinterface!B8</f>
-        <v>45930</v>
+        <v>45900</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15165,13 +15147,13 @@
       </c>
       <c r="F5" s="26"/>
       <c r="G5" s="27" t="n">
-        <v>46599</v>
+        <v>46568</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="14"/>
       <c r="K5" s="15" t="n">
         <f aca="false">Vatinterface!B9</f>
-        <v>45961</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15186,7 +15168,7 @@
       <c r="I6" s="14"/>
       <c r="K6" s="15" t="n">
         <f aca="false">Vatinterface!B10</f>
-        <v>45991</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15206,7 +15188,7 @@
       <c r="I7" s="14"/>
       <c r="K7" s="15" t="n">
         <f aca="false">Vatinterface!B11</f>
-        <v>46022</v>
+        <v>45991</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15221,7 +15203,7 @@
       <c r="I8" s="14"/>
       <c r="K8" s="15" t="n">
         <f aca="false">Vatinterface!B12</f>
-        <v>46053</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15243,7 +15225,7 @@
       <c r="I9" s="14"/>
       <c r="K9" s="15" t="n">
         <f aca="false">Vatinterface!B13</f>
-        <v>46081</v>
+        <v>46053</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15258,7 +15240,7 @@
       <c r="I10" s="14"/>
       <c r="K10" s="15" t="n">
         <f aca="false">Vatinterface!B14</f>
-        <v>46112</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15279,7 +15261,7 @@
       <c r="I11" s="14"/>
       <c r="K11" s="15" t="n">
         <f aca="false">Vatinterface!B15</f>
-        <v>46142</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15294,7 +15276,7 @@
       <c r="I12" s="14"/>
       <c r="K12" s="15" t="n">
         <f aca="false">Vatinterface!B16</f>
-        <v>46173</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15316,7 +15298,7 @@
       <c r="I13" s="14"/>
       <c r="K13" s="15" t="n">
         <f aca="false">Vatinterface!B17</f>
-        <v>46203</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15331,7 +15313,7 @@
       <c r="I14" s="14"/>
       <c r="K14" s="15" t="n">
         <f aca="false">Vatinterface!B18</f>
-        <v>0</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15725,12 +15707,12 @@
     <row r="4" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="84"/>
       <c r="B4" s="85" t="n">
-        <f aca="false">[1]Admin!$B$12</f>
-        <v>45808</v>
+        <f aca="false">[1]Admin!$B$10</f>
+        <v>45777</v>
       </c>
       <c r="C4" s="85" t="n">
         <f aca="false">B5</f>
-        <v>45838</v>
+        <v>45808</v>
       </c>
       <c r="D4" s="86" t="n">
         <f aca="false">S02Y1!$H$1</f>
@@ -15762,12 +15744,12 @@
     <row r="5" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="84"/>
       <c r="B5" s="85" t="n">
-        <f aca="false">[1]Admin!$B$14</f>
-        <v>45838</v>
+        <f aca="false">[1]Admin!$B$12</f>
+        <v>45808</v>
       </c>
       <c r="C5" s="85" t="n">
         <f aca="false">B6</f>
-        <v>45869</v>
+        <v>45838</v>
       </c>
       <c r="D5" s="86" t="n">
         <f aca="false">S03Y1!$H$1</f>
@@ -15799,12 +15781,12 @@
     <row r="6" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="84"/>
       <c r="B6" s="85" t="n">
-        <f aca="false">[1]Admin!$B$16</f>
-        <v>45869</v>
+        <f aca="false">[1]Admin!$B$14</f>
+        <v>45838</v>
       </c>
       <c r="C6" s="85" t="n">
         <f aca="false">B7</f>
-        <v>45900</v>
+        <v>45869</v>
       </c>
       <c r="D6" s="86" t="n">
         <f aca="false">[2]Apr!$H$1</f>
@@ -15848,12 +15830,12 @@
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="84"/>
       <c r="B7" s="85" t="n">
-        <f aca="false">[1]Admin!$B$18</f>
-        <v>45900</v>
+        <f aca="false">[1]Admin!$B$16</f>
+        <v>45869</v>
       </c>
       <c r="C7" s="85" t="n">
         <f aca="false">B8</f>
-        <v>45930</v>
+        <v>45900</v>
       </c>
       <c r="D7" s="86" t="n">
         <f aca="false">[2]May!$H$1</f>
@@ -15897,15 +15879,15 @@
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="84"/>
       <c r="B8" s="85" t="n">
-        <f aca="false">[1]Admin!$B$20</f>
-        <v>45930</v>
+        <f aca="false">[1]Admin!$B$18</f>
+        <v>45900</v>
       </c>
       <c r="C8" s="85" t="n">
         <f aca="false">B9</f>
-        <v>45961</v>
+        <v>45930</v>
       </c>
       <c r="D8" s="86" t="n">
-        <f aca="false">[2]Jun!$H$1</f>
+        <f aca="false">[2]Apr!$H$1</f>
         <v>0</v>
       </c>
       <c r="E8" s="87" t="n">
@@ -15913,7 +15895,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="87" t="n">
-        <f aca="false">[2]Jun!$G$1</f>
+        <f aca="false">[2]Apr!$G$1</f>
         <v>0</v>
       </c>
       <c r="G8" s="87" t="n">
@@ -15921,7 +15903,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="87" t="n">
-        <f aca="false">[3]Jun!$H$1</f>
+        <f aca="false">[3]Apr!$H$1</f>
         <v>0</v>
       </c>
       <c r="I8" s="87" t="n">
@@ -15929,7 +15911,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="87" t="n">
-        <f aca="false">[3]Jun!$G$1</f>
+        <f aca="false">[3]Apr!$G$1</f>
         <v>0</v>
       </c>
       <c r="K8" s="87" t="n">
@@ -15938,7 +15920,7 @@
       </c>
       <c r="L8" s="88"/>
       <c r="M8" s="89" t="n">
-        <f aca="false">IF([2]Jun!$G$4&gt;0,[2]Jun!$G$4,0)</f>
+        <f aca="false">IF([2]May!$G$4&gt;0,[2]May!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N8" s="90"/>
@@ -15946,15 +15928,15 @@
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="84"/>
       <c r="B9" s="85" t="n">
-        <f aca="false">[1]Admin!$B$22</f>
-        <v>45961</v>
+        <f aca="false">[1]Admin!$B$20</f>
+        <v>45930</v>
       </c>
       <c r="C9" s="85" t="n">
         <f aca="false">B10</f>
-        <v>45991</v>
+        <v>45961</v>
       </c>
       <c r="D9" s="86" t="n">
-        <f aca="false">[2]Apr!$H$1</f>
+        <f aca="false">[2]May!$H$1</f>
         <v>0</v>
       </c>
       <c r="E9" s="87" t="n">
@@ -15962,7 +15944,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="87" t="n">
-        <f aca="false">[2]Apr!$G$1</f>
+        <f aca="false">[2]May!$G$1</f>
         <v>0</v>
       </c>
       <c r="G9" s="87" t="n">
@@ -15970,7 +15952,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="87" t="n">
-        <f aca="false">[3]Apr!$H$1</f>
+        <f aca="false">[3]May!$H$1</f>
         <v>0</v>
       </c>
       <c r="I9" s="87" t="n">
@@ -15978,7 +15960,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="87" t="n">
-        <f aca="false">[3]Apr!$G$1</f>
+        <f aca="false">[3]May!$G$1</f>
         <v>0</v>
       </c>
       <c r="K9" s="87" t="n">
@@ -15995,15 +15977,15 @@
     <row r="10" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="84"/>
       <c r="B10" s="85" t="n">
-        <f aca="false">[1]Admin!$B$24</f>
-        <v>45991</v>
+        <f aca="false">[1]Admin!$B$22</f>
+        <v>45961</v>
       </c>
       <c r="C10" s="85" t="n">
         <f aca="false">B11</f>
-        <v>46022</v>
+        <v>45991</v>
       </c>
       <c r="D10" s="86" t="n">
-        <f aca="false">[2]May!$H$1</f>
+        <f aca="false">[2]Apr!$H$1</f>
         <v>0</v>
       </c>
       <c r="E10" s="87" t="n">
@@ -16011,7 +15993,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="87" t="n">
-        <f aca="false">[2]May!$G$1</f>
+        <f aca="false">[2]Apr!$G$1</f>
         <v>0</v>
       </c>
       <c r="G10" s="87" t="n">
@@ -16019,7 +16001,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="87" t="n">
-        <f aca="false">[3]May!$H$1</f>
+        <f aca="false">[3]Apr!$H$1</f>
         <v>0</v>
       </c>
       <c r="I10" s="87" t="n">
@@ -16027,7 +16009,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="87" t="n">
-        <f aca="false">[3]May!$G$1</f>
+        <f aca="false">[3]Apr!$G$1</f>
         <v>0</v>
       </c>
       <c r="K10" s="87" t="n">
@@ -16036,7 +16018,7 @@
       </c>
       <c r="L10" s="88"/>
       <c r="M10" s="89" t="n">
-        <f aca="false">IF([2]Jun!$G$4&gt;0,[2]Jun!$G$4,0)</f>
+        <f aca="false">IF([2]May!$G$4&gt;0,[2]May!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N10" s="90"/>
@@ -16044,15 +16026,15 @@
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="84"/>
       <c r="B11" s="85" t="n">
-        <f aca="false">[1]Admin!$B$26</f>
-        <v>46022</v>
+        <f aca="false">[1]Admin!$B$24</f>
+        <v>45991</v>
       </c>
       <c r="C11" s="85" t="n">
         <f aca="false">B12</f>
-        <v>46053</v>
+        <v>46022</v>
       </c>
       <c r="D11" s="86" t="n">
-        <f aca="false">[2]Jun!$H$1</f>
+        <f aca="false">[2]May!$H$1</f>
         <v>0</v>
       </c>
       <c r="E11" s="87" t="n">
@@ -16060,7 +16042,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="87" t="n">
-        <f aca="false">[2]Jun!$G$1</f>
+        <f aca="false">[2]May!$G$1</f>
         <v>0</v>
       </c>
       <c r="G11" s="87" t="n">
@@ -16068,7 +16050,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="87" t="n">
-        <f aca="false">[3]Jun!$H$1</f>
+        <f aca="false">[3]May!$H$1</f>
         <v>0</v>
       </c>
       <c r="I11" s="87" t="n">
@@ -16076,7 +16058,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="87" t="n">
-        <f aca="false">[3]Jun!$G$1</f>
+        <f aca="false">[3]May!$G$1</f>
         <v>0</v>
       </c>
       <c r="K11" s="87" t="n">
@@ -16085,7 +16067,7 @@
       </c>
       <c r="L11" s="88"/>
       <c r="M11" s="89" t="n">
-        <f aca="false">IF([2]Jun!$G$4&gt;0,[2]Jun!$G$4,0)</f>
+        <f aca="false">IF([2]Apr!$G$4&gt;0,[2]Apr!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N11" s="90"/>
@@ -16093,12 +16075,12 @@
     <row r="12" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="84"/>
       <c r="B12" s="85" t="n">
-        <f aca="false">[1]Admin!$B$28</f>
-        <v>46053</v>
+        <f aca="false">[1]Admin!$B$26</f>
+        <v>46022</v>
       </c>
       <c r="C12" s="85" t="n">
         <f aca="false">B13</f>
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="D12" s="86" t="n">
         <f aca="false">[2]Apr!$H$1</f>
@@ -16142,12 +16124,12 @@
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="84"/>
       <c r="B13" s="85" t="n">
-        <f aca="false">[1]Admin!$B$30</f>
-        <v>46081</v>
+        <f aca="false">[1]Admin!$B$28</f>
+        <v>46053</v>
       </c>
       <c r="C13" s="85" t="n">
         <f aca="false">B14</f>
-        <v>46112</v>
+        <v>46081</v>
       </c>
       <c r="D13" s="86" t="n">
         <f aca="false">[2]May!$H$1</f>
@@ -16183,7 +16165,7 @@
       </c>
       <c r="L13" s="88"/>
       <c r="M13" s="89" t="n">
-        <f aca="false">IF([2]May!$G$4&gt;0,[2]May!$G$4,0)</f>
+        <f aca="false">IF([2]Apr!$G$4&gt;0,[2]Apr!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N13" s="90"/>
@@ -16191,15 +16173,15 @@
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="84"/>
       <c r="B14" s="85" t="n">
-        <f aca="false">[1]Admin!$B$32</f>
-        <v>46112</v>
+        <f aca="false">[1]Admin!$B$30</f>
+        <v>46081</v>
       </c>
       <c r="C14" s="85" t="n">
         <f aca="false">B15</f>
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="D14" s="86" t="n">
-        <f aca="false">[2]Jun!$H$1</f>
+        <f aca="false">[2]Apr!$H$1</f>
         <v>0</v>
       </c>
       <c r="E14" s="87" t="n">
@@ -16207,7 +16189,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="87" t="n">
-        <f aca="false">[2]Jun!$G$1</f>
+        <f aca="false">[2]Apr!$G$1</f>
         <v>0</v>
       </c>
       <c r="G14" s="87" t="n">
@@ -16215,7 +16197,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="87" t="n">
-        <f aca="false">[3]Jun!$H$1</f>
+        <f aca="false">[3]Apr!$H$1</f>
         <v>0</v>
       </c>
       <c r="I14" s="87" t="n">
@@ -16223,7 +16205,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="87" t="n">
-        <f aca="false">[3]Jun!$G$1</f>
+        <f aca="false">[3]Apr!$G$1</f>
         <v>0</v>
       </c>
       <c r="K14" s="87" t="n">
@@ -16232,7 +16214,7 @@
       </c>
       <c r="L14" s="88"/>
       <c r="M14" s="89" t="n">
-        <f aca="false">IF([2]May!$G$4&gt;0,[2]May!$G$4,0)</f>
+        <f aca="false">IF([2]Apr!$G$4&gt;0,[2]Apr!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N14" s="90"/>
@@ -16240,15 +16222,15 @@
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="84"/>
       <c r="B15" s="85" t="n">
-        <f aca="false">[1]Admin!$B$34</f>
-        <v>46142</v>
+        <f aca="false">[1]Admin!$B$32</f>
+        <v>46112</v>
       </c>
       <c r="C15" s="85" t="n">
         <f aca="false">B16</f>
-        <v>46173</v>
+        <v>46142</v>
       </c>
       <c r="D15" s="86" t="n">
-        <f aca="false">[2]Apr!$H$1</f>
+        <f aca="false">[2]May!$H$1</f>
         <v>0</v>
       </c>
       <c r="E15" s="87" t="n">
@@ -16256,7 +16238,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="87" t="n">
-        <f aca="false">[2]Apr!$G$1</f>
+        <f aca="false">[2]May!$G$1</f>
         <v>0</v>
       </c>
       <c r="G15" s="87" t="n">
@@ -16264,7 +16246,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="87" t="n">
-        <f aca="false">[3]Apr!$H$1</f>
+        <f aca="false">[3]May!$H$1</f>
         <v>0</v>
       </c>
       <c r="I15" s="87" t="n">
@@ -16272,7 +16254,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="87" t="n">
-        <f aca="false">[3]Apr!$G$1</f>
+        <f aca="false">[3]May!$G$1</f>
         <v>0</v>
       </c>
       <c r="K15" s="87" t="n">
@@ -16289,15 +16271,15 @@
     <row r="16" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="84"/>
       <c r="B16" s="85" t="n">
-        <f aca="false">[1]Admin!$B$36</f>
-        <v>46173</v>
+        <f aca="false">[1]Admin!$B$34</f>
+        <v>46142</v>
       </c>
       <c r="C16" s="85" t="n">
         <f aca="false">B17</f>
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D16" s="86" t="n">
-        <f aca="false">[2]May!$H$1</f>
+        <f aca="false">[2]Apr!$H$1</f>
         <v>0</v>
       </c>
       <c r="E16" s="87" t="n">
@@ -16305,7 +16287,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="87" t="n">
-        <f aca="false">[2]May!$G$1</f>
+        <f aca="false">[2]Apr!$G$1</f>
         <v>0</v>
       </c>
       <c r="G16" s="87" t="n">
@@ -16313,7 +16295,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="87" t="n">
-        <f aca="false">[3]May!$H$1</f>
+        <f aca="false">[3]Apr!$H$1</f>
         <v>0</v>
       </c>
       <c r="I16" s="87" t="n">
@@ -16321,7 +16303,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="87" t="n">
-        <f aca="false">[3]May!$G$1</f>
+        <f aca="false">[3]Apr!$G$1</f>
         <v>0</v>
       </c>
       <c r="K16" s="87" t="n">
@@ -16330,7 +16312,7 @@
       </c>
       <c r="L16" s="88"/>
       <c r="M16" s="89" t="n">
-        <f aca="false">IF([2]Jun!$G$4&gt;0,[2]Jun!$G$4,0)</f>
+        <f aca="false">IF([2]Apr!$G$4&gt;0,[2]Apr!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N16" s="90"/>
@@ -16338,15 +16320,15 @@
     <row r="17" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="84"/>
       <c r="B17" s="85" t="n">
-        <f aca="false">[1]Admin!$B$38</f>
-        <v>46203</v>
+        <f aca="false">[1]Admin!$B$36</f>
+        <v>46173</v>
       </c>
       <c r="C17" s="85" t="n">
         <f aca="false">B18</f>
-        <v>0</v>
+        <v>46203</v>
       </c>
       <c r="D17" s="86" t="n">
-        <f aca="false">[2]Jun!$H$1</f>
+        <f aca="false">[2]May!$H$1</f>
         <v>0</v>
       </c>
       <c r="E17" s="87" t="n">
@@ -16354,7 +16336,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="87" t="n">
-        <f aca="false">[2]Jun!$G$1</f>
+        <f aca="false">[2]May!$G$1</f>
         <v>0</v>
       </c>
       <c r="G17" s="87" t="n">
@@ -16362,7 +16344,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="87" t="n">
-        <f aca="false">[3]Jun!$H$1</f>
+        <f aca="false">[3]May!$H$1</f>
         <v>0</v>
       </c>
       <c r="I17" s="87" t="n">
@@ -16370,7 +16352,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="87" t="n">
-        <f aca="false">[3]Jun!$G$1</f>
+        <f aca="false">[3]May!$G$1</f>
         <v>0</v>
       </c>
       <c r="K17" s="87" t="n">
@@ -16379,7 +16361,7 @@
       </c>
       <c r="L17" s="88"/>
       <c r="M17" s="89" t="n">
-        <f aca="false">IF([2]Jun!$G$4&gt;0,[2]Jun!$G$4,0)</f>
+        <f aca="false">IF([2]May!$G$4&gt;0,[2]May!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N17" s="90"/>
@@ -16387,8 +16369,8 @@
     <row r="18" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="84"/>
       <c r="B18" s="85" t="n">
-        <f aca="false">[1]Admin!$B$40</f>
-        <v>0</v>
+        <f aca="false">[1]Admin!$B$38</f>
+        <v>46203</v>
       </c>
       <c r="C18" s="85" t="n">
         <f aca="false">B19</f>
@@ -16428,7 +16410,7 @@
       </c>
       <c r="L18" s="88"/>
       <c r="M18" s="89" t="n">
-        <f aca="false">IF([2]Jun!$G$4&gt;0,[2]Jun!$G$4,0)</f>
+        <f aca="false">IF([2]May!$G$4&gt;0,[2]May!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N18" s="90"/>
@@ -16436,7 +16418,7 @@
     <row r="19" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="84"/>
       <c r="B19" s="85" t="n">
-        <f aca="false">[1]Admin!$B$42</f>
+        <f aca="false">[1]Admin!$B$40</f>
         <v>0</v>
       </c>
       <c r="C19" s="91" t="n">
@@ -16477,7 +16459,7 @@
       </c>
       <c r="L19" s="88"/>
       <c r="M19" s="89" t="n">
-        <f aca="false">IF([2]Jun!$G$4&gt;0,[2]Jun!$G$4,0)</f>
+        <f aca="false">IF([2]May!$G$4&gt;0,[2]May!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N19" s="90"/>

--- a/examples/ltd-latest/Vatreturns.xlsx
+++ b/examples/ltd-latest/Vatreturns.xlsx
@@ -1217,21 +1217,6 @@
       <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
       <sheetData sheetId="11">
-        <row r="12">
-          <cell r="B12">
-            <v>45808</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="B14">
-            <v>45838</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="B16">
-            <v>45869</v>
-          </cell>
-        </row>
         <row r="18">
           <cell r="B18">
             <v>45900</v>
@@ -1365,9 +1350,46 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
+      <sheetData sheetId="4">
+        <row r="1">
+          <cell r="G1">
+            <v>0</v>
+          </cell>
+          <cell r="H1">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="5">
+        <row r="1">
+          <cell r="G1">
+            <v>0</v>
+          </cell>
+          <cell r="H1">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="G4">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="6">
+        <row r="1">
+          <cell r="G1">
+            <v>0</v>
+          </cell>
+          <cell r="H1">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="G4">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
       <sheetData sheetId="9"/>
@@ -1448,9 +1470,36 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
+      <sheetData sheetId="4">
+        <row r="1">
+          <cell r="G1">
+            <v>0</v>
+          </cell>
+          <cell r="H1">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="5">
+        <row r="1">
+          <cell r="G1">
+            <v>0</v>
+          </cell>
+          <cell r="H1">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="6">
+        <row r="1">
+          <cell r="G1">
+            <v>0</v>
+          </cell>
+          <cell r="H1">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
       <sheetData sheetId="9"/>
@@ -1622,7 +1671,7 @@
       <c r="I2" s="14"/>
       <c r="K2" s="15" t="n">
         <f aca="false">Vatinterface!B6</f>
-        <v>45869</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1639,7 +1688,7 @@
       <c r="I3" s="14"/>
       <c r="K3" s="15" t="n">
         <f aca="false">Vatinterface!B7</f>
-        <v>45900</v>
+        <v>45991</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1656,7 +1705,7 @@
       <c r="I4" s="14"/>
       <c r="K4" s="15" t="n">
         <f aca="false">Vatinterface!B8</f>
-        <v>45930</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1669,13 +1718,13 @@
       </c>
       <c r="F5" s="26"/>
       <c r="G5" s="27" t="n">
-        <v>46295</v>
+        <v>46387</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="14"/>
       <c r="K5" s="15" t="n">
         <f aca="false">Vatinterface!B9</f>
-        <v>45961</v>
+        <v>46053</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1690,7 +1739,7 @@
       <c r="I6" s="14"/>
       <c r="K6" s="15" t="n">
         <f aca="false">Vatinterface!B10</f>
-        <v>45991</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1710,7 +1759,7 @@
       <c r="I7" s="14"/>
       <c r="K7" s="15" t="n">
         <f aca="false">Vatinterface!B11</f>
-        <v>46022</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1725,7 +1774,7 @@
       <c r="I8" s="14"/>
       <c r="K8" s="15" t="n">
         <f aca="false">Vatinterface!B12</f>
-        <v>46053</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1747,7 +1796,7 @@
       <c r="I9" s="14"/>
       <c r="K9" s="15" t="n">
         <f aca="false">Vatinterface!B13</f>
-        <v>46081</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1762,7 +1811,7 @@
       <c r="I10" s="14"/>
       <c r="K10" s="15" t="n">
         <f aca="false">Vatinterface!B14</f>
-        <v>46112</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1783,7 +1832,7 @@
       <c r="I11" s="14"/>
       <c r="K11" s="15" t="n">
         <f aca="false">Vatinterface!B15</f>
-        <v>46142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1798,7 +1847,7 @@
       <c r="I12" s="14"/>
       <c r="K12" s="15" t="n">
         <f aca="false">Vatinterface!B16</f>
-        <v>46173</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1820,7 +1869,7 @@
       <c r="I13" s="14"/>
       <c r="K13" s="15" t="n">
         <f aca="false">Vatinterface!B17</f>
-        <v>46203</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13426,7 +13475,7 @@
       <c r="I2" s="14"/>
       <c r="K2" s="15" t="n">
         <f aca="false">Vatinterface!B6</f>
-        <v>45869</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13443,7 +13492,7 @@
       <c r="I3" s="14"/>
       <c r="K3" s="15" t="n">
         <f aca="false">Vatinterface!B7</f>
-        <v>45900</v>
+        <v>45991</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13460,7 +13509,7 @@
       <c r="I4" s="14"/>
       <c r="K4" s="15" t="n">
         <f aca="false">Vatinterface!B8</f>
-        <v>45930</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13473,13 +13522,13 @@
       </c>
       <c r="F5" s="26"/>
       <c r="G5" s="27" t="n">
-        <v>46387</v>
+        <v>46477</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="14"/>
       <c r="K5" s="15" t="n">
         <f aca="false">Vatinterface!B9</f>
-        <v>45961</v>
+        <v>46053</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13494,7 +13543,7 @@
       <c r="I6" s="14"/>
       <c r="K6" s="15" t="n">
         <f aca="false">Vatinterface!B10</f>
-        <v>45991</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13514,7 +13563,7 @@
       <c r="I7" s="14"/>
       <c r="K7" s="15" t="n">
         <f aca="false">Vatinterface!B11</f>
-        <v>46022</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13529,7 +13578,7 @@
       <c r="I8" s="14"/>
       <c r="K8" s="15" t="n">
         <f aca="false">Vatinterface!B12</f>
-        <v>46053</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13551,7 +13600,7 @@
       <c r="I9" s="14"/>
       <c r="K9" s="15" t="n">
         <f aca="false">Vatinterface!B13</f>
-        <v>46081</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13566,7 +13615,7 @@
       <c r="I10" s="14"/>
       <c r="K10" s="15" t="n">
         <f aca="false">Vatinterface!B14</f>
-        <v>46112</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13587,7 +13636,7 @@
       <c r="I11" s="14"/>
       <c r="K11" s="15" t="n">
         <f aca="false">Vatinterface!B15</f>
-        <v>46142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13602,7 +13651,7 @@
       <c r="I12" s="14"/>
       <c r="K12" s="15" t="n">
         <f aca="false">Vatinterface!B16</f>
-        <v>46173</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13624,7 +13673,7 @@
       <c r="I13" s="14"/>
       <c r="K13" s="15" t="n">
         <f aca="false">Vatinterface!B17</f>
-        <v>46203</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13990,7 +14039,7 @@
       <c r="I2" s="14"/>
       <c r="K2" s="15" t="n">
         <f aca="false">Vatinterface!B6</f>
-        <v>45869</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14007,7 +14056,7 @@
       <c r="I3" s="14"/>
       <c r="K3" s="15" t="n">
         <f aca="false">Vatinterface!B7</f>
-        <v>45900</v>
+        <v>45991</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14024,7 +14073,7 @@
       <c r="I4" s="14"/>
       <c r="K4" s="15" t="n">
         <f aca="false">Vatinterface!B8</f>
-        <v>45930</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14037,13 +14086,13 @@
       </c>
       <c r="F5" s="26"/>
       <c r="G5" s="27" t="n">
-        <v>46477</v>
+        <v>46568</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="14"/>
       <c r="K5" s="15" t="n">
         <f aca="false">Vatinterface!B9</f>
-        <v>45961</v>
+        <v>46053</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14058,7 +14107,7 @@
       <c r="I6" s="14"/>
       <c r="K6" s="15" t="n">
         <f aca="false">Vatinterface!B10</f>
-        <v>45991</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14078,7 +14127,7 @@
       <c r="I7" s="14"/>
       <c r="K7" s="15" t="n">
         <f aca="false">Vatinterface!B11</f>
-        <v>46022</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14093,7 +14142,7 @@
       <c r="I8" s="14"/>
       <c r="K8" s="15" t="n">
         <f aca="false">Vatinterface!B12</f>
-        <v>46053</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14115,7 +14164,7 @@
       <c r="I9" s="14"/>
       <c r="K9" s="15" t="n">
         <f aca="false">Vatinterface!B13</f>
-        <v>46081</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14130,7 +14179,7 @@
       <c r="I10" s="14"/>
       <c r="K10" s="15" t="n">
         <f aca="false">Vatinterface!B14</f>
-        <v>46112</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14151,7 +14200,7 @@
       <c r="I11" s="14"/>
       <c r="K11" s="15" t="n">
         <f aca="false">Vatinterface!B15</f>
-        <v>46142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14166,7 +14215,7 @@
       <c r="I12" s="14"/>
       <c r="K12" s="15" t="n">
         <f aca="false">Vatinterface!B16</f>
-        <v>46173</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14188,7 +14237,7 @@
       <c r="I13" s="14"/>
       <c r="K13" s="15" t="n">
         <f aca="false">Vatinterface!B17</f>
-        <v>46203</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14554,7 +14603,7 @@
       <c r="I2" s="14"/>
       <c r="K2" s="15" t="n">
         <f aca="false">Vatinterface!B6</f>
-        <v>45869</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14571,7 +14620,7 @@
       <c r="I3" s="14"/>
       <c r="K3" s="15" t="n">
         <f aca="false">Vatinterface!B7</f>
-        <v>45900</v>
+        <v>45991</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14588,7 +14637,7 @@
       <c r="I4" s="14"/>
       <c r="K4" s="15" t="n">
         <f aca="false">Vatinterface!B8</f>
-        <v>45930</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14601,13 +14650,13 @@
       </c>
       <c r="F5" s="26"/>
       <c r="G5" s="27" t="n">
-        <v>46568</v>
+        <v>46660</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="14"/>
       <c r="K5" s="15" t="n">
         <f aca="false">Vatinterface!B9</f>
-        <v>45961</v>
+        <v>46053</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14622,7 +14671,7 @@
       <c r="I6" s="14"/>
       <c r="K6" s="15" t="n">
         <f aca="false">Vatinterface!B10</f>
-        <v>45991</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14642,7 +14691,7 @@
       <c r="I7" s="14"/>
       <c r="K7" s="15" t="n">
         <f aca="false">Vatinterface!B11</f>
-        <v>46022</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14657,7 +14706,7 @@
       <c r="I8" s="14"/>
       <c r="K8" s="15" t="n">
         <f aca="false">Vatinterface!B12</f>
-        <v>46053</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14679,7 +14728,7 @@
       <c r="I9" s="14"/>
       <c r="K9" s="15" t="n">
         <f aca="false">Vatinterface!B13</f>
-        <v>46081</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14694,7 +14743,7 @@
       <c r="I10" s="14"/>
       <c r="K10" s="15" t="n">
         <f aca="false">Vatinterface!B14</f>
-        <v>46112</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14715,7 +14764,7 @@
       <c r="I11" s="14"/>
       <c r="K11" s="15" t="n">
         <f aca="false">Vatinterface!B15</f>
-        <v>46142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14730,7 +14779,7 @@
       <c r="I12" s="14"/>
       <c r="K12" s="15" t="n">
         <f aca="false">Vatinterface!B16</f>
-        <v>46173</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14752,7 +14801,7 @@
       <c r="I13" s="14"/>
       <c r="K13" s="15" t="n">
         <f aca="false">Vatinterface!B17</f>
-        <v>46203</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15118,7 +15167,7 @@
       <c r="I2" s="14"/>
       <c r="K2" s="15" t="n">
         <f aca="false">Vatinterface!B6</f>
-        <v>45869</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15135,7 +15184,7 @@
       <c r="I3" s="14"/>
       <c r="K3" s="15" t="n">
         <f aca="false">Vatinterface!B7</f>
-        <v>45900</v>
+        <v>45991</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15152,7 +15201,7 @@
       <c r="I4" s="14"/>
       <c r="K4" s="15" t="n">
         <f aca="false">Vatinterface!B8</f>
-        <v>45930</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15165,13 +15214,13 @@
       </c>
       <c r="F5" s="26"/>
       <c r="G5" s="27" t="n">
-        <v>46599</v>
+        <v>46691</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="14"/>
       <c r="K5" s="15" t="n">
         <f aca="false">Vatinterface!B9</f>
-        <v>45961</v>
+        <v>46053</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15186,7 +15235,7 @@
       <c r="I6" s="14"/>
       <c r="K6" s="15" t="n">
         <f aca="false">Vatinterface!B10</f>
-        <v>45991</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15206,7 +15255,7 @@
       <c r="I7" s="14"/>
       <c r="K7" s="15" t="n">
         <f aca="false">Vatinterface!B11</f>
-        <v>46022</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15221,7 +15270,7 @@
       <c r="I8" s="14"/>
       <c r="K8" s="15" t="n">
         <f aca="false">Vatinterface!B12</f>
-        <v>46053</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15243,7 +15292,7 @@
       <c r="I9" s="14"/>
       <c r="K9" s="15" t="n">
         <f aca="false">Vatinterface!B13</f>
-        <v>46081</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15258,7 +15307,7 @@
       <c r="I10" s="14"/>
       <c r="K10" s="15" t="n">
         <f aca="false">Vatinterface!B14</f>
-        <v>46112</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15279,7 +15328,7 @@
       <c r="I11" s="14"/>
       <c r="K11" s="15" t="n">
         <f aca="false">Vatinterface!B15</f>
-        <v>46142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15294,7 +15343,7 @@
       <c r="I12" s="14"/>
       <c r="K12" s="15" t="n">
         <f aca="false">Vatinterface!B16</f>
-        <v>46173</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15316,7 +15365,7 @@
       <c r="I13" s="14"/>
       <c r="K13" s="15" t="n">
         <f aca="false">Vatinterface!B17</f>
-        <v>46203</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15725,12 +15774,12 @@
     <row r="4" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="84"/>
       <c r="B4" s="85" t="n">
-        <f aca="false">[1]Admin!$B$12</f>
-        <v>45808</v>
+        <f aca="false">[1]Admin!$B$18</f>
+        <v>45900</v>
       </c>
       <c r="C4" s="85" t="n">
         <f aca="false">B5</f>
-        <v>45838</v>
+        <v>45930</v>
       </c>
       <c r="D4" s="86" t="n">
         <f aca="false">S02Y1!$H$1</f>
@@ -15762,12 +15811,12 @@
     <row r="5" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="84"/>
       <c r="B5" s="85" t="n">
-        <f aca="false">[1]Admin!$B$14</f>
-        <v>45838</v>
+        <f aca="false">[1]Admin!$B$20</f>
+        <v>45930</v>
       </c>
       <c r="C5" s="85" t="n">
         <f aca="false">B6</f>
-        <v>45869</v>
+        <v>45961</v>
       </c>
       <c r="D5" s="86" t="n">
         <f aca="false">S03Y1!$H$1</f>
@@ -15799,12 +15848,12 @@
     <row r="6" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="84"/>
       <c r="B6" s="85" t="n">
-        <f aca="false">[1]Admin!$B$16</f>
-        <v>45869</v>
+        <f aca="false">[1]Admin!$B$22</f>
+        <v>45961</v>
       </c>
       <c r="C6" s="85" t="n">
         <f aca="false">B7</f>
-        <v>45900</v>
+        <v>45991</v>
       </c>
       <c r="D6" s="86" t="n">
         <f aca="false">[2]Apr!$H$1</f>
@@ -15848,12 +15897,12 @@
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="84"/>
       <c r="B7" s="85" t="n">
-        <f aca="false">[1]Admin!$B$18</f>
-        <v>45900</v>
+        <f aca="false">[1]Admin!$B$24</f>
+        <v>45991</v>
       </c>
       <c r="C7" s="85" t="n">
         <f aca="false">B8</f>
-        <v>45930</v>
+        <v>46022</v>
       </c>
       <c r="D7" s="86" t="n">
         <f aca="false">[2]May!$H$1</f>
@@ -15897,12 +15946,12 @@
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="84"/>
       <c r="B8" s="85" t="n">
-        <f aca="false">[1]Admin!$B$20</f>
-        <v>45930</v>
+        <f aca="false">[1]Admin!$B$26</f>
+        <v>46022</v>
       </c>
       <c r="C8" s="85" t="n">
         <f aca="false">B9</f>
-        <v>45961</v>
+        <v>46053</v>
       </c>
       <c r="D8" s="86" t="n">
         <f aca="false">[2]Jun!$H$1</f>
@@ -15938,7 +15987,7 @@
       </c>
       <c r="L8" s="88"/>
       <c r="M8" s="89" t="n">
-        <f aca="false">IF([2]Jun!$G$4&gt;0,[2]Jun!$G$4,0)</f>
+        <f aca="false">IF([2]Sep!$G$4&gt;0,[2]Sep!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N8" s="90"/>
@@ -15946,15 +15995,15 @@
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="84"/>
       <c r="B9" s="85" t="n">
-        <f aca="false">[1]Admin!$B$22</f>
-        <v>45961</v>
+        <f aca="false">[1]Admin!$B$28</f>
+        <v>46053</v>
       </c>
       <c r="C9" s="85" t="n">
         <f aca="false">B10</f>
-        <v>45991</v>
+        <v>46081</v>
       </c>
       <c r="D9" s="86" t="n">
-        <f aca="false">[2]Apr!$H$1</f>
+        <f aca="false">[2]Jul!$H$1</f>
         <v>0</v>
       </c>
       <c r="E9" s="87" t="n">
@@ -15962,7 +16011,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="87" t="n">
-        <f aca="false">[2]Apr!$G$1</f>
+        <f aca="false">[2]Jul!$G$1</f>
         <v>0</v>
       </c>
       <c r="G9" s="87" t="n">
@@ -15970,7 +16019,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="87" t="n">
-        <f aca="false">[3]Apr!$H$1</f>
+        <f aca="false">[3]Jul!$H$1</f>
         <v>0</v>
       </c>
       <c r="I9" s="87" t="n">
@@ -15978,7 +16027,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="87" t="n">
-        <f aca="false">[3]Apr!$G$1</f>
+        <f aca="false">[3]Jul!$G$1</f>
         <v>0</v>
       </c>
       <c r="K9" s="87" t="n">
@@ -15995,15 +16044,15 @@
     <row r="10" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="84"/>
       <c r="B10" s="85" t="n">
-        <f aca="false">[1]Admin!$B$24</f>
-        <v>45991</v>
+        <f aca="false">[1]Admin!$B$30</f>
+        <v>46081</v>
       </c>
       <c r="C10" s="85" t="n">
         <f aca="false">B11</f>
-        <v>46022</v>
+        <v>46112</v>
       </c>
       <c r="D10" s="86" t="n">
-        <f aca="false">[2]May!$H$1</f>
+        <f aca="false">[2]Aug!$H$1</f>
         <v>0</v>
       </c>
       <c r="E10" s="87" t="n">
@@ -16011,7 +16060,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="87" t="n">
-        <f aca="false">[2]May!$G$1</f>
+        <f aca="false">[2]Aug!$G$1</f>
         <v>0</v>
       </c>
       <c r="G10" s="87" t="n">
@@ -16019,7 +16068,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="87" t="n">
-        <f aca="false">[3]May!$H$1</f>
+        <f aca="false">[3]Aug!$H$1</f>
         <v>0</v>
       </c>
       <c r="I10" s="87" t="n">
@@ -16027,7 +16076,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="87" t="n">
-        <f aca="false">[3]May!$G$1</f>
+        <f aca="false">[3]Aug!$G$1</f>
         <v>0</v>
       </c>
       <c r="K10" s="87" t="n">
@@ -16036,7 +16085,7 @@
       </c>
       <c r="L10" s="88"/>
       <c r="M10" s="89" t="n">
-        <f aca="false">IF([2]Jun!$G$4&gt;0,[2]Jun!$G$4,0)</f>
+        <f aca="false">IF([2]Sep!$G$4&gt;0,[2]Sep!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N10" s="90"/>
@@ -16044,15 +16093,15 @@
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="84"/>
       <c r="B11" s="85" t="n">
-        <f aca="false">[1]Admin!$B$26</f>
-        <v>46022</v>
+        <f aca="false">[1]Admin!$B$32</f>
+        <v>46112</v>
       </c>
       <c r="C11" s="85" t="n">
         <f aca="false">B12</f>
-        <v>46053</v>
+        <v>46142</v>
       </c>
       <c r="D11" s="86" t="n">
-        <f aca="false">[2]Jun!$H$1</f>
+        <f aca="false">[2]Sep!$H$1</f>
         <v>0</v>
       </c>
       <c r="E11" s="87" t="n">
@@ -16060,7 +16109,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="87" t="n">
-        <f aca="false">[2]Jun!$G$1</f>
+        <f aca="false">[2]Sep!$G$1</f>
         <v>0</v>
       </c>
       <c r="G11" s="87" t="n">
@@ -16068,7 +16117,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="87" t="n">
-        <f aca="false">[3]Jun!$H$1</f>
+        <f aca="false">[3]Sep!$H$1</f>
         <v>0</v>
       </c>
       <c r="I11" s="87" t="n">
@@ -16076,7 +16125,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="87" t="n">
-        <f aca="false">[3]Jun!$G$1</f>
+        <f aca="false">[3]Sep!$G$1</f>
         <v>0</v>
       </c>
       <c r="K11" s="87" t="n">
@@ -16093,12 +16142,12 @@
     <row r="12" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="84"/>
       <c r="B12" s="85" t="n">
-        <f aca="false">[1]Admin!$B$28</f>
-        <v>46053</v>
+        <f aca="false">[1]Admin!$B$34</f>
+        <v>46142</v>
       </c>
       <c r="C12" s="85" t="n">
         <f aca="false">B13</f>
-        <v>46081</v>
+        <v>46173</v>
       </c>
       <c r="D12" s="86" t="n">
         <f aca="false">[2]Apr!$H$1</f>
@@ -16142,12 +16191,12 @@
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="84"/>
       <c r="B13" s="85" t="n">
-        <f aca="false">[1]Admin!$B$30</f>
-        <v>46081</v>
+        <f aca="false">[1]Admin!$B$36</f>
+        <v>46173</v>
       </c>
       <c r="C13" s="85" t="n">
         <f aca="false">B14</f>
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="D13" s="86" t="n">
         <f aca="false">[2]May!$H$1</f>
@@ -16183,7 +16232,7 @@
       </c>
       <c r="L13" s="88"/>
       <c r="M13" s="89" t="n">
-        <f aca="false">IF([2]May!$G$4&gt;0,[2]May!$G$4,0)</f>
+        <f aca="false">IF([2]Aug!$G$4&gt;0,[2]Aug!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N13" s="90"/>
@@ -16191,12 +16240,12 @@
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="84"/>
       <c r="B14" s="85" t="n">
-        <f aca="false">[1]Admin!$B$32</f>
-        <v>46112</v>
+        <f aca="false">[1]Admin!$B$38</f>
+        <v>46203</v>
       </c>
       <c r="C14" s="85" t="n">
         <f aca="false">B15</f>
-        <v>46142</v>
+        <v>0</v>
       </c>
       <c r="D14" s="86" t="n">
         <f aca="false">[2]Jun!$H$1</f>
@@ -16232,7 +16281,7 @@
       </c>
       <c r="L14" s="88"/>
       <c r="M14" s="89" t="n">
-        <f aca="false">IF([2]May!$G$4&gt;0,[2]May!$G$4,0)</f>
+        <f aca="false">IF([2]Aug!$G$4&gt;0,[2]Aug!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N14" s="90"/>
@@ -16240,15 +16289,15 @@
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="84"/>
       <c r="B15" s="85" t="n">
-        <f aca="false">[1]Admin!$B$34</f>
-        <v>46142</v>
+        <f aca="false">[1]Admin!$B$40</f>
+        <v>0</v>
       </c>
       <c r="C15" s="85" t="n">
         <f aca="false">B16</f>
-        <v>46173</v>
+        <v>0</v>
       </c>
       <c r="D15" s="86" t="n">
-        <f aca="false">[2]Apr!$H$1</f>
+        <f aca="false">[2]Jul!$H$1</f>
         <v>0</v>
       </c>
       <c r="E15" s="87" t="n">
@@ -16256,7 +16305,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="87" t="n">
-        <f aca="false">[2]Apr!$G$1</f>
+        <f aca="false">[2]Jul!$G$1</f>
         <v>0</v>
       </c>
       <c r="G15" s="87" t="n">
@@ -16264,7 +16313,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="87" t="n">
-        <f aca="false">[3]Apr!$H$1</f>
+        <f aca="false">[3]Jul!$H$1</f>
         <v>0</v>
       </c>
       <c r="I15" s="87" t="n">
@@ -16272,7 +16321,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="87" t="n">
-        <f aca="false">[3]Apr!$G$1</f>
+        <f aca="false">[3]Jul!$G$1</f>
         <v>0</v>
       </c>
       <c r="K15" s="87" t="n">
@@ -16289,15 +16338,15 @@
     <row r="16" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="84"/>
       <c r="B16" s="85" t="n">
-        <f aca="false">[1]Admin!$B$36</f>
-        <v>46173</v>
+        <f aca="false">[1]Admin!$B$42</f>
+        <v>0</v>
       </c>
       <c r="C16" s="85" t="n">
         <f aca="false">B17</f>
-        <v>46203</v>
+        <v>0</v>
       </c>
       <c r="D16" s="86" t="n">
-        <f aca="false">[2]May!$H$1</f>
+        <f aca="false">[2]Aug!$H$1</f>
         <v>0</v>
       </c>
       <c r="E16" s="87" t="n">
@@ -16305,7 +16354,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="87" t="n">
-        <f aca="false">[2]May!$G$1</f>
+        <f aca="false">[2]Aug!$G$1</f>
         <v>0</v>
       </c>
       <c r="G16" s="87" t="n">
@@ -16313,7 +16362,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="87" t="n">
-        <f aca="false">[3]May!$H$1</f>
+        <f aca="false">[3]Aug!$H$1</f>
         <v>0</v>
       </c>
       <c r="I16" s="87" t="n">
@@ -16321,7 +16370,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="87" t="n">
-        <f aca="false">[3]May!$G$1</f>
+        <f aca="false">[3]Aug!$G$1</f>
         <v>0</v>
       </c>
       <c r="K16" s="87" t="n">
@@ -16338,15 +16387,15 @@
     <row r="17" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="84"/>
       <c r="B17" s="85" t="n">
-        <f aca="false">[1]Admin!$B$38</f>
-        <v>46203</v>
+        <f aca="false">[1]Admin!$B$44</f>
+        <v>0</v>
       </c>
       <c r="C17" s="85" t="n">
         <f aca="false">B18</f>
         <v>0</v>
       </c>
       <c r="D17" s="86" t="n">
-        <f aca="false">[2]Jun!$H$1</f>
+        <f aca="false">[2]Sep!$H$1</f>
         <v>0</v>
       </c>
       <c r="E17" s="87" t="n">
@@ -16354,7 +16403,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="87" t="n">
-        <f aca="false">[2]Jun!$G$1</f>
+        <f aca="false">[2]Sep!$G$1</f>
         <v>0</v>
       </c>
       <c r="G17" s="87" t="n">
@@ -16362,7 +16411,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="87" t="n">
-        <f aca="false">[3]Jun!$H$1</f>
+        <f aca="false">[3]Sep!$H$1</f>
         <v>0</v>
       </c>
       <c r="I17" s="87" t="n">
@@ -16370,7 +16419,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="87" t="n">
-        <f aca="false">[3]Jun!$G$1</f>
+        <f aca="false">[3]Sep!$G$1</f>
         <v>0</v>
       </c>
       <c r="K17" s="87" t="n">
@@ -16379,7 +16428,7 @@
       </c>
       <c r="L17" s="88"/>
       <c r="M17" s="89" t="n">
-        <f aca="false">IF([2]Jun!$G$4&gt;0,[2]Jun!$G$4,0)</f>
+        <f aca="false">IF([2]Sep!$G$4&gt;0,[2]Sep!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N17" s="90"/>
@@ -16387,7 +16436,7 @@
     <row r="18" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="84"/>
       <c r="B18" s="85" t="n">
-        <f aca="false">[1]Admin!$B$40</f>
+        <f aca="false">[1]Admin!$B$46</f>
         <v>0</v>
       </c>
       <c r="C18" s="85" t="n">
@@ -16428,7 +16477,7 @@
       </c>
       <c r="L18" s="88"/>
       <c r="M18" s="89" t="n">
-        <f aca="false">IF([2]Jun!$G$4&gt;0,[2]Jun!$G$4,0)</f>
+        <f aca="false">IF([2]Sep!$G$4&gt;0,[2]Sep!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N18" s="90"/>
@@ -16436,7 +16485,7 @@
     <row r="19" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="84"/>
       <c r="B19" s="85" t="n">
-        <f aca="false">[1]Admin!$B$42</f>
+        <f aca="false">[1]Admin!$B$48</f>
         <v>0</v>
       </c>
       <c r="C19" s="91" t="n">
@@ -16477,7 +16526,7 @@
       </c>
       <c r="L19" s="88"/>
       <c r="M19" s="89" t="n">
-        <f aca="false">IF([2]Jun!$G$4&gt;0,[2]Jun!$G$4,0)</f>
+        <f aca="false">IF([2]Sep!$G$4&gt;0,[2]Sep!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N19" s="90"/>

--- a/examples/ltd-latest/Vatreturns.xlsx
+++ b/examples/ltd-latest/Vatreturns.xlsx
@@ -1217,59 +1217,89 @@
       <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
       <sheetData sheetId="11">
+        <row r="6">
+          <cell r="B6">
+            <v>46265</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="B8">
+            <v>46295</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="B10">
+            <v>46326</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="B12">
+            <v>46356</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="B14">
+            <v>46387</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="B16">
+            <v>46418</v>
+          </cell>
+        </row>
         <row r="18">
           <cell r="B18">
-            <v>45900</v>
+            <v>46446</v>
           </cell>
         </row>
         <row r="20">
           <cell r="B20">
-            <v>45930</v>
+            <v>46477</v>
           </cell>
         </row>
         <row r="22">
           <cell r="B22">
-            <v>45961</v>
+            <v>46507</v>
           </cell>
         </row>
         <row r="24">
           <cell r="B24">
-            <v>45991</v>
+            <v>46538</v>
           </cell>
         </row>
         <row r="26">
           <cell r="B26">
-            <v>46022</v>
+            <v>46568</v>
           </cell>
         </row>
         <row r="28">
           <cell r="B28">
-            <v>46053</v>
+            <v>46599</v>
           </cell>
         </row>
         <row r="30">
           <cell r="B30">
-            <v>46081</v>
+            <v>46630</v>
           </cell>
         </row>
         <row r="32">
           <cell r="B32">
-            <v>46112</v>
+            <v>46660</v>
           </cell>
         </row>
         <row r="34">
           <cell r="B34">
-            <v>46142</v>
+            <v>46691</v>
           </cell>
         </row>
         <row r="36">
           <cell r="B36">
-            <v>46173</v>
+            <v>46721</v>
           </cell>
         </row>
         <row r="38">
           <cell r="B38">
-            <v>46203</v>
+            <v>46752</v>
           </cell>
         </row>
       </sheetData>
@@ -1671,7 +1701,7 @@
       <c r="I2" s="14"/>
       <c r="K2" s="15" t="n">
         <f aca="false">Vatinterface!B6</f>
-        <v>45961</v>
+        <v>46326</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1688,7 +1718,7 @@
       <c r="I3" s="14"/>
       <c r="K3" s="15" t="n">
         <f aca="false">Vatinterface!B7</f>
-        <v>45991</v>
+        <v>46356</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1705,7 +1735,7 @@
       <c r="I4" s="14"/>
       <c r="K4" s="15" t="n">
         <f aca="false">Vatinterface!B8</f>
-        <v>46022</v>
+        <v>46387</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1724,7 +1754,7 @@
       <c r="I5" s="14"/>
       <c r="K5" s="15" t="n">
         <f aca="false">Vatinterface!B9</f>
-        <v>46053</v>
+        <v>46418</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1739,7 +1769,7 @@
       <c r="I6" s="14"/>
       <c r="K6" s="15" t="n">
         <f aca="false">Vatinterface!B10</f>
-        <v>46081</v>
+        <v>46446</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1753,13 +1783,13 @@
       <c r="F7" s="31"/>
       <c r="G7" s="32" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!C1:C20)</f>
-        <v>46203</v>
+        <v>46418</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="14"/>
       <c r="K7" s="15" t="n">
         <f aca="false">Vatinterface!B11</f>
-        <v>46112</v>
+        <v>46477</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1774,7 +1804,7 @@
       <c r="I8" s="14"/>
       <c r="K8" s="15" t="n">
         <f aca="false">Vatinterface!B12</f>
-        <v>46142</v>
+        <v>46507</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1796,7 +1826,7 @@
       <c r="I9" s="14"/>
       <c r="K9" s="15" t="n">
         <f aca="false">Vatinterface!B13</f>
-        <v>46173</v>
+        <v>46538</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1811,7 +1841,7 @@
       <c r="I10" s="14"/>
       <c r="K10" s="15" t="n">
         <f aca="false">Vatinterface!B14</f>
-        <v>46203</v>
+        <v>46568</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1832,7 +1862,7 @@
       <c r="I11" s="14"/>
       <c r="K11" s="15" t="n">
         <f aca="false">Vatinterface!B15</f>
-        <v>0</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1847,7 +1877,7 @@
       <c r="I12" s="14"/>
       <c r="K12" s="15" t="n">
         <f aca="false">Vatinterface!B16</f>
-        <v>0</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1869,7 +1899,7 @@
       <c r="I13" s="14"/>
       <c r="K13" s="15" t="n">
         <f aca="false">Vatinterface!B17</f>
-        <v>0</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1884,7 +1914,7 @@
       <c r="I14" s="14"/>
       <c r="K14" s="15" t="n">
         <f aca="false">Vatinterface!B18</f>
-        <v>0</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1906,7 +1936,7 @@
       <c r="I15" s="14"/>
       <c r="K15" s="15" t="n">
         <f aca="false">Vatinterface!B19</f>
-        <v>0</v>
+        <v>46721</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13475,7 +13505,7 @@
       <c r="I2" s="14"/>
       <c r="K2" s="15" t="n">
         <f aca="false">Vatinterface!B6</f>
-        <v>45961</v>
+        <v>46326</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13492,7 +13522,7 @@
       <c r="I3" s="14"/>
       <c r="K3" s="15" t="n">
         <f aca="false">Vatinterface!B7</f>
-        <v>45991</v>
+        <v>46356</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13509,7 +13539,7 @@
       <c r="I4" s="14"/>
       <c r="K4" s="15" t="n">
         <f aca="false">Vatinterface!B8</f>
-        <v>46022</v>
+        <v>46387</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13528,7 +13558,7 @@
       <c r="I5" s="14"/>
       <c r="K5" s="15" t="n">
         <f aca="false">Vatinterface!B9</f>
-        <v>46053</v>
+        <v>46418</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13543,7 +13573,7 @@
       <c r="I6" s="14"/>
       <c r="K6" s="15" t="n">
         <f aca="false">Vatinterface!B10</f>
-        <v>46081</v>
+        <v>46446</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13557,13 +13587,13 @@
       <c r="F7" s="31"/>
       <c r="G7" s="32" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!C1:C20)</f>
-        <v>46203</v>
+        <v>46507</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="14"/>
       <c r="K7" s="15" t="n">
         <f aca="false">Vatinterface!B11</f>
-        <v>46112</v>
+        <v>46477</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13578,7 +13608,7 @@
       <c r="I8" s="14"/>
       <c r="K8" s="15" t="n">
         <f aca="false">Vatinterface!B12</f>
-        <v>46142</v>
+        <v>46507</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13600,7 +13630,7 @@
       <c r="I9" s="14"/>
       <c r="K9" s="15" t="n">
         <f aca="false">Vatinterface!B13</f>
-        <v>46173</v>
+        <v>46538</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13615,7 +13645,7 @@
       <c r="I10" s="14"/>
       <c r="K10" s="15" t="n">
         <f aca="false">Vatinterface!B14</f>
-        <v>46203</v>
+        <v>46568</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13636,7 +13666,7 @@
       <c r="I11" s="14"/>
       <c r="K11" s="15" t="n">
         <f aca="false">Vatinterface!B15</f>
-        <v>0</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13651,7 +13681,7 @@
       <c r="I12" s="14"/>
       <c r="K12" s="15" t="n">
         <f aca="false">Vatinterface!B16</f>
-        <v>0</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13673,7 +13703,7 @@
       <c r="I13" s="14"/>
       <c r="K13" s="15" t="n">
         <f aca="false">Vatinterface!B17</f>
-        <v>0</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13688,7 +13718,7 @@
       <c r="I14" s="14"/>
       <c r="K14" s="15" t="n">
         <f aca="false">Vatinterface!B18</f>
-        <v>0</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13710,7 +13740,7 @@
       <c r="I15" s="14"/>
       <c r="K15" s="15" t="n">
         <f aca="false">Vatinterface!B19</f>
-        <v>0</v>
+        <v>46721</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14039,7 +14069,7 @@
       <c r="I2" s="14"/>
       <c r="K2" s="15" t="n">
         <f aca="false">Vatinterface!B6</f>
-        <v>45961</v>
+        <v>46326</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14056,7 +14086,7 @@
       <c r="I3" s="14"/>
       <c r="K3" s="15" t="n">
         <f aca="false">Vatinterface!B7</f>
-        <v>45991</v>
+        <v>46356</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14073,7 +14103,7 @@
       <c r="I4" s="14"/>
       <c r="K4" s="15" t="n">
         <f aca="false">Vatinterface!B8</f>
-        <v>46022</v>
+        <v>46387</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14092,7 +14122,7 @@
       <c r="I5" s="14"/>
       <c r="K5" s="15" t="n">
         <f aca="false">Vatinterface!B9</f>
-        <v>46053</v>
+        <v>46418</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14107,7 +14137,7 @@
       <c r="I6" s="14"/>
       <c r="K6" s="15" t="n">
         <f aca="false">Vatinterface!B10</f>
-        <v>46081</v>
+        <v>46446</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14121,13 +14151,13 @@
       <c r="F7" s="31"/>
       <c r="G7" s="32" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!C1:C20)</f>
-        <v>46203</v>
+        <v>46599</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="14"/>
       <c r="K7" s="15" t="n">
         <f aca="false">Vatinterface!B11</f>
-        <v>46112</v>
+        <v>46477</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14142,7 +14172,7 @@
       <c r="I8" s="14"/>
       <c r="K8" s="15" t="n">
         <f aca="false">Vatinterface!B12</f>
-        <v>46142</v>
+        <v>46507</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14164,7 +14194,7 @@
       <c r="I9" s="14"/>
       <c r="K9" s="15" t="n">
         <f aca="false">Vatinterface!B13</f>
-        <v>46173</v>
+        <v>46538</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14179,7 +14209,7 @@
       <c r="I10" s="14"/>
       <c r="K10" s="15" t="n">
         <f aca="false">Vatinterface!B14</f>
-        <v>46203</v>
+        <v>46568</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14200,7 +14230,7 @@
       <c r="I11" s="14"/>
       <c r="K11" s="15" t="n">
         <f aca="false">Vatinterface!B15</f>
-        <v>0</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14215,7 +14245,7 @@
       <c r="I12" s="14"/>
       <c r="K12" s="15" t="n">
         <f aca="false">Vatinterface!B16</f>
-        <v>0</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14237,7 +14267,7 @@
       <c r="I13" s="14"/>
       <c r="K13" s="15" t="n">
         <f aca="false">Vatinterface!B17</f>
-        <v>0</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14252,7 +14282,7 @@
       <c r="I14" s="14"/>
       <c r="K14" s="15" t="n">
         <f aca="false">Vatinterface!B18</f>
-        <v>0</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14274,7 +14304,7 @@
       <c r="I15" s="14"/>
       <c r="K15" s="15" t="n">
         <f aca="false">Vatinterface!B19</f>
-        <v>0</v>
+        <v>46721</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14603,7 +14633,7 @@
       <c r="I2" s="14"/>
       <c r="K2" s="15" t="n">
         <f aca="false">Vatinterface!B6</f>
-        <v>45961</v>
+        <v>46326</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14620,7 +14650,7 @@
       <c r="I3" s="14"/>
       <c r="K3" s="15" t="n">
         <f aca="false">Vatinterface!B7</f>
-        <v>45991</v>
+        <v>46356</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14637,7 +14667,7 @@
       <c r="I4" s="14"/>
       <c r="K4" s="15" t="n">
         <f aca="false">Vatinterface!B8</f>
-        <v>46022</v>
+        <v>46387</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14656,7 +14686,7 @@
       <c r="I5" s="14"/>
       <c r="K5" s="15" t="n">
         <f aca="false">Vatinterface!B9</f>
-        <v>46053</v>
+        <v>46418</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14671,7 +14701,7 @@
       <c r="I6" s="14"/>
       <c r="K6" s="15" t="n">
         <f aca="false">Vatinterface!B10</f>
-        <v>46081</v>
+        <v>46446</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14685,13 +14715,13 @@
       <c r="F7" s="31"/>
       <c r="G7" s="32" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!C1:C20)</f>
-        <v>46203</v>
+        <v>46691</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="14"/>
       <c r="K7" s="15" t="n">
         <f aca="false">Vatinterface!B11</f>
-        <v>46112</v>
+        <v>46477</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14706,7 +14736,7 @@
       <c r="I8" s="14"/>
       <c r="K8" s="15" t="n">
         <f aca="false">Vatinterface!B12</f>
-        <v>46142</v>
+        <v>46507</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14728,7 +14758,7 @@
       <c r="I9" s="14"/>
       <c r="K9" s="15" t="n">
         <f aca="false">Vatinterface!B13</f>
-        <v>46173</v>
+        <v>46538</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14743,7 +14773,7 @@
       <c r="I10" s="14"/>
       <c r="K10" s="15" t="n">
         <f aca="false">Vatinterface!B14</f>
-        <v>46203</v>
+        <v>46568</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14764,7 +14794,7 @@
       <c r="I11" s="14"/>
       <c r="K11" s="15" t="n">
         <f aca="false">Vatinterface!B15</f>
-        <v>0</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14779,7 +14809,7 @@
       <c r="I12" s="14"/>
       <c r="K12" s="15" t="n">
         <f aca="false">Vatinterface!B16</f>
-        <v>0</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14801,7 +14831,7 @@
       <c r="I13" s="14"/>
       <c r="K13" s="15" t="n">
         <f aca="false">Vatinterface!B17</f>
-        <v>0</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14816,7 +14846,7 @@
       <c r="I14" s="14"/>
       <c r="K14" s="15" t="n">
         <f aca="false">Vatinterface!B18</f>
-        <v>0</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14838,7 +14868,7 @@
       <c r="I15" s="14"/>
       <c r="K15" s="15" t="n">
         <f aca="false">Vatinterface!B19</f>
-        <v>0</v>
+        <v>46721</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15167,7 +15197,7 @@
       <c r="I2" s="14"/>
       <c r="K2" s="15" t="n">
         <f aca="false">Vatinterface!B6</f>
-        <v>45961</v>
+        <v>46326</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15184,7 +15214,7 @@
       <c r="I3" s="14"/>
       <c r="K3" s="15" t="n">
         <f aca="false">Vatinterface!B7</f>
-        <v>45991</v>
+        <v>46356</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15201,7 +15231,7 @@
       <c r="I4" s="14"/>
       <c r="K4" s="15" t="n">
         <f aca="false">Vatinterface!B8</f>
-        <v>46022</v>
+        <v>46387</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15220,7 +15250,7 @@
       <c r="I5" s="14"/>
       <c r="K5" s="15" t="n">
         <f aca="false">Vatinterface!B9</f>
-        <v>46053</v>
+        <v>46418</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15235,7 +15265,7 @@
       <c r="I6" s="14"/>
       <c r="K6" s="15" t="n">
         <f aca="false">Vatinterface!B10</f>
-        <v>46081</v>
+        <v>46446</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15249,13 +15279,13 @@
       <c r="F7" s="31"/>
       <c r="G7" s="32" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!C1:C20)</f>
-        <v>46203</v>
+        <v>46721</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="14"/>
       <c r="K7" s="15" t="n">
         <f aca="false">Vatinterface!B11</f>
-        <v>46112</v>
+        <v>46477</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15270,7 +15300,7 @@
       <c r="I8" s="14"/>
       <c r="K8" s="15" t="n">
         <f aca="false">Vatinterface!B12</f>
-        <v>46142</v>
+        <v>46507</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15292,7 +15322,7 @@
       <c r="I9" s="14"/>
       <c r="K9" s="15" t="n">
         <f aca="false">Vatinterface!B13</f>
-        <v>46173</v>
+        <v>46538</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15307,7 +15337,7 @@
       <c r="I10" s="14"/>
       <c r="K10" s="15" t="n">
         <f aca="false">Vatinterface!B14</f>
-        <v>46203</v>
+        <v>46568</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15328,7 +15358,7 @@
       <c r="I11" s="14"/>
       <c r="K11" s="15" t="n">
         <f aca="false">Vatinterface!B15</f>
-        <v>0</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15343,7 +15373,7 @@
       <c r="I12" s="14"/>
       <c r="K12" s="15" t="n">
         <f aca="false">Vatinterface!B16</f>
-        <v>0</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15365,7 +15395,7 @@
       <c r="I13" s="14"/>
       <c r="K13" s="15" t="n">
         <f aca="false">Vatinterface!B17</f>
-        <v>0</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15380,7 +15410,7 @@
       <c r="I14" s="14"/>
       <c r="K14" s="15" t="n">
         <f aca="false">Vatinterface!B18</f>
-        <v>0</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15402,7 +15432,7 @@
       <c r="I15" s="14"/>
       <c r="K15" s="15" t="n">
         <f aca="false">Vatinterface!B19</f>
-        <v>0</v>
+        <v>46721</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15774,12 +15804,12 @@
     <row r="4" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="84"/>
       <c r="B4" s="85" t="n">
-        <f aca="false">[1]Admin!$B$18</f>
-        <v>45900</v>
+        <f aca="false">[1]Admin!$B$6</f>
+        <v>46265</v>
       </c>
       <c r="C4" s="85" t="n">
         <f aca="false">B5</f>
-        <v>45930</v>
+        <v>46295</v>
       </c>
       <c r="D4" s="86" t="n">
         <f aca="false">S02Y1!$H$1</f>
@@ -15811,12 +15841,12 @@
     <row r="5" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="84"/>
       <c r="B5" s="85" t="n">
-        <f aca="false">[1]Admin!$B$20</f>
-        <v>45930</v>
+        <f aca="false">[1]Admin!$B$8</f>
+        <v>46295</v>
       </c>
       <c r="C5" s="85" t="n">
         <f aca="false">B6</f>
-        <v>45961</v>
+        <v>46326</v>
       </c>
       <c r="D5" s="86" t="n">
         <f aca="false">S03Y1!$H$1</f>
@@ -15848,12 +15878,12 @@
     <row r="6" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="84"/>
       <c r="B6" s="85" t="n">
-        <f aca="false">[1]Admin!$B$22</f>
-        <v>45961</v>
+        <f aca="false">[1]Admin!$B$10</f>
+        <v>46326</v>
       </c>
       <c r="C6" s="85" t="n">
         <f aca="false">B7</f>
-        <v>45991</v>
+        <v>46356</v>
       </c>
       <c r="D6" s="86" t="n">
         <f aca="false">[2]Apr!$H$1</f>
@@ -15897,12 +15927,12 @@
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="84"/>
       <c r="B7" s="85" t="n">
-        <f aca="false">[1]Admin!$B$24</f>
-        <v>45991</v>
+        <f aca="false">[1]Admin!$B$12</f>
+        <v>46356</v>
       </c>
       <c r="C7" s="85" t="n">
         <f aca="false">B8</f>
-        <v>46022</v>
+        <v>46387</v>
       </c>
       <c r="D7" s="86" t="n">
         <f aca="false">[2]May!$H$1</f>
@@ -15946,12 +15976,12 @@
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="84"/>
       <c r="B8" s="85" t="n">
-        <f aca="false">[1]Admin!$B$26</f>
-        <v>46022</v>
+        <f aca="false">[1]Admin!$B$14</f>
+        <v>46387</v>
       </c>
       <c r="C8" s="85" t="n">
         <f aca="false">B9</f>
-        <v>46053</v>
+        <v>46418</v>
       </c>
       <c r="D8" s="86" t="n">
         <f aca="false">[2]Jun!$H$1</f>
@@ -15995,12 +16025,12 @@
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="84"/>
       <c r="B9" s="85" t="n">
-        <f aca="false">[1]Admin!$B$28</f>
-        <v>46053</v>
+        <f aca="false">[1]Admin!$B$16</f>
+        <v>46418</v>
       </c>
       <c r="C9" s="85" t="n">
         <f aca="false">B10</f>
-        <v>46081</v>
+        <v>46446</v>
       </c>
       <c r="D9" s="86" t="n">
         <f aca="false">[2]Jul!$H$1</f>
@@ -16044,12 +16074,12 @@
     <row r="10" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="84"/>
       <c r="B10" s="85" t="n">
-        <f aca="false">[1]Admin!$B$30</f>
-        <v>46081</v>
+        <f aca="false">[1]Admin!$B$18</f>
+        <v>46446</v>
       </c>
       <c r="C10" s="85" t="n">
         <f aca="false">B11</f>
-        <v>46112</v>
+        <v>46477</v>
       </c>
       <c r="D10" s="86" t="n">
         <f aca="false">[2]Aug!$H$1</f>
@@ -16093,12 +16123,12 @@
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="84"/>
       <c r="B11" s="85" t="n">
-        <f aca="false">[1]Admin!$B$32</f>
-        <v>46112</v>
+        <f aca="false">[1]Admin!$B$20</f>
+        <v>46477</v>
       </c>
       <c r="C11" s="85" t="n">
         <f aca="false">B12</f>
-        <v>46142</v>
+        <v>46507</v>
       </c>
       <c r="D11" s="86" t="n">
         <f aca="false">[2]Sep!$H$1</f>
@@ -16142,12 +16172,12 @@
     <row r="12" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="84"/>
       <c r="B12" s="85" t="n">
-        <f aca="false">[1]Admin!$B$34</f>
-        <v>46142</v>
+        <f aca="false">[1]Admin!$B$22</f>
+        <v>46507</v>
       </c>
       <c r="C12" s="85" t="n">
         <f aca="false">B13</f>
-        <v>46173</v>
+        <v>46538</v>
       </c>
       <c r="D12" s="86" t="n">
         <f aca="false">[2]Apr!$H$1</f>
@@ -16191,12 +16221,12 @@
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="84"/>
       <c r="B13" s="85" t="n">
-        <f aca="false">[1]Admin!$B$36</f>
-        <v>46173</v>
+        <f aca="false">[1]Admin!$B$24</f>
+        <v>46538</v>
       </c>
       <c r="C13" s="85" t="n">
         <f aca="false">B14</f>
-        <v>46203</v>
+        <v>46568</v>
       </c>
       <c r="D13" s="86" t="n">
         <f aca="false">[2]May!$H$1</f>
@@ -16240,12 +16270,12 @@
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="84"/>
       <c r="B14" s="85" t="n">
-        <f aca="false">[1]Admin!$B$38</f>
-        <v>46203</v>
+        <f aca="false">[1]Admin!$B$26</f>
+        <v>46568</v>
       </c>
       <c r="C14" s="85" t="n">
         <f aca="false">B15</f>
-        <v>0</v>
+        <v>46599</v>
       </c>
       <c r="D14" s="86" t="n">
         <f aca="false">[2]Jun!$H$1</f>
@@ -16289,12 +16319,12 @@
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="84"/>
       <c r="B15" s="85" t="n">
-        <f aca="false">[1]Admin!$B$40</f>
-        <v>0</v>
+        <f aca="false">[1]Admin!$B$28</f>
+        <v>46599</v>
       </c>
       <c r="C15" s="85" t="n">
         <f aca="false">B16</f>
-        <v>0</v>
+        <v>46630</v>
       </c>
       <c r="D15" s="86" t="n">
         <f aca="false">[2]Jul!$H$1</f>
@@ -16338,12 +16368,12 @@
     <row r="16" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="84"/>
       <c r="B16" s="85" t="n">
-        <f aca="false">[1]Admin!$B$42</f>
-        <v>0</v>
+        <f aca="false">[1]Admin!$B$30</f>
+        <v>46630</v>
       </c>
       <c r="C16" s="85" t="n">
         <f aca="false">B17</f>
-        <v>0</v>
+        <v>46660</v>
       </c>
       <c r="D16" s="86" t="n">
         <f aca="false">[2]Aug!$H$1</f>
@@ -16387,12 +16417,12 @@
     <row r="17" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="84"/>
       <c r="B17" s="85" t="n">
-        <f aca="false">[1]Admin!$B$44</f>
-        <v>0</v>
+        <f aca="false">[1]Admin!$B$32</f>
+        <v>46660</v>
       </c>
       <c r="C17" s="85" t="n">
         <f aca="false">B18</f>
-        <v>0</v>
+        <v>46691</v>
       </c>
       <c r="D17" s="86" t="n">
         <f aca="false">[2]Sep!$H$1</f>
@@ -16436,12 +16466,12 @@
     <row r="18" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="84"/>
       <c r="B18" s="85" t="n">
-        <f aca="false">[1]Admin!$B$46</f>
-        <v>0</v>
+        <f aca="false">[1]Admin!$B$34</f>
+        <v>46691</v>
       </c>
       <c r="C18" s="85" t="n">
         <f aca="false">B19</f>
-        <v>0</v>
+        <v>46721</v>
       </c>
       <c r="D18" s="86" t="n">
         <f aca="false">S04Y2!$H$1</f>
@@ -16485,12 +16515,12 @@
     <row r="19" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="84"/>
       <c r="B19" s="85" t="n">
-        <f aca="false">[1]Admin!$B$48</f>
-        <v>0</v>
+        <f aca="false">[1]Admin!$B$36</f>
+        <v>46721</v>
       </c>
       <c r="C19" s="91" t="n">
         <f aca="false">[1]Admin!$B$38</f>
-        <v>46203</v>
+        <v>46752</v>
       </c>
       <c r="D19" s="86" t="n">
         <f aca="false">S05Y2!$H$1</f>

--- a/examples/ltd-latest/Vatreturns.xlsx
+++ b/examples/ltd-latest/Vatreturns.xlsx
@@ -1374,11 +1374,6 @@
             <v>0</v>
           </cell>
         </row>
-        <row r="4">
-          <cell r="G4">
-            <v>0</v>
-          </cell>
-        </row>
       </sheetData>
       <sheetData sheetId="4">
         <row r="1">
@@ -1399,11 +1394,6 @@
             <v>0</v>
           </cell>
         </row>
-        <row r="4">
-          <cell r="G4">
-            <v>0</v>
-          </cell>
-        </row>
       </sheetData>
       <sheetData sheetId="6">
         <row r="1">
@@ -1420,12 +1410,76 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
+      <sheetData sheetId="7">
+        <row r="1">
+          <cell r="G1">
+            <v>0</v>
+          </cell>
+          <cell r="H1">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="8">
+        <row r="1">
+          <cell r="G1">
+            <v>0</v>
+          </cell>
+          <cell r="H1">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="G4">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="9">
+        <row r="1">
+          <cell r="G1">
+            <v>0</v>
+          </cell>
+          <cell r="H1">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="10">
+        <row r="1">
+          <cell r="G1">
+            <v>0</v>
+          </cell>
+          <cell r="H1">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="11">
+        <row r="1">
+          <cell r="G1">
+            <v>0</v>
+          </cell>
+          <cell r="H1">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="12">
+        <row r="1">
+          <cell r="G1">
+            <v>0</v>
+          </cell>
+          <cell r="H1">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="G4">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="13">
         <row r="2">
           <cell r="G2">
@@ -1530,12 +1584,66 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
+      <sheetData sheetId="7">
+        <row r="1">
+          <cell r="G1">
+            <v>0</v>
+          </cell>
+          <cell r="H1">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="8">
+        <row r="1">
+          <cell r="G1">
+            <v>0</v>
+          </cell>
+          <cell r="H1">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="9">
+        <row r="1">
+          <cell r="G1">
+            <v>0</v>
+          </cell>
+          <cell r="H1">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="10">
+        <row r="1">
+          <cell r="G1">
+            <v>0</v>
+          </cell>
+          <cell r="H1">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="11">
+        <row r="1">
+          <cell r="G1">
+            <v>0</v>
+          </cell>
+          <cell r="H1">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="12">
+        <row r="1">
+          <cell r="G1">
+            <v>0</v>
+          </cell>
+          <cell r="H1">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="13">
         <row r="2">
           <cell r="G2">
@@ -15833,7 +15941,7 @@
       <c r="K4" s="87"/>
       <c r="L4" s="88"/>
       <c r="M4" s="89" t="n">
-        <f aca="false">IF([2]Apr!$G$4&gt;0,[2]Apr!$G$4,0)</f>
+        <f aca="false">IF([2]Oct!$G$4&gt;0,[2]Oct!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N4" s="90"/>
@@ -15870,7 +15978,7 @@
       <c r="K5" s="87"/>
       <c r="L5" s="88"/>
       <c r="M5" s="89" t="n">
-        <f aca="false">IF([2]Apr!$G$4&gt;0,[2]Apr!$G$4,0)</f>
+        <f aca="false">IF([2]Oct!$G$4&gt;0,[2]Oct!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N5" s="90"/>
@@ -15886,7 +15994,7 @@
         <v>46356</v>
       </c>
       <c r="D6" s="86" t="n">
-        <f aca="false">[2]Apr!$H$1</f>
+        <f aca="false">[2]Oct!$H$1</f>
         <v>0</v>
       </c>
       <c r="E6" s="87" t="n">
@@ -15894,7 +16002,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="87" t="n">
-        <f aca="false">[2]Apr!$G$1</f>
+        <f aca="false">[2]Oct!$G$1</f>
         <v>0</v>
       </c>
       <c r="G6" s="87" t="n">
@@ -15902,7 +16010,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="87" t="n">
-        <f aca="false">[3]Apr!$H$1</f>
+        <f aca="false">[3]Oct!$H$1</f>
         <v>0</v>
       </c>
       <c r="I6" s="87" t="n">
@@ -15910,7 +16018,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="87" t="n">
-        <f aca="false">[3]Apr!$G$1</f>
+        <f aca="false">[3]Oct!$G$1</f>
         <v>0</v>
       </c>
       <c r="K6" s="87" t="n">
@@ -15919,7 +16027,7 @@
       </c>
       <c r="L6" s="88"/>
       <c r="M6" s="89" t="n">
-        <f aca="false">IF([2]Apr!$G$4&gt;0,[2]Apr!$G$4,0)</f>
+        <f aca="false">IF([2]Oct!$G$4&gt;0,[2]Oct!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N6" s="90"/>
@@ -15935,7 +16043,7 @@
         <v>46387</v>
       </c>
       <c r="D7" s="86" t="n">
-        <f aca="false">[2]May!$H$1</f>
+        <f aca="false">[2]Nov!$H$1</f>
         <v>0</v>
       </c>
       <c r="E7" s="87" t="n">
@@ -15943,7 +16051,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="87" t="n">
-        <f aca="false">[2]May!$G$1</f>
+        <f aca="false">[2]Nov!$G$1</f>
         <v>0</v>
       </c>
       <c r="G7" s="87" t="n">
@@ -15951,7 +16059,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="87" t="n">
-        <f aca="false">[3]May!$H$1</f>
+        <f aca="false">[3]Nov!$H$1</f>
         <v>0</v>
       </c>
       <c r="I7" s="87" t="n">
@@ -15959,7 +16067,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="87" t="n">
-        <f aca="false">[3]May!$G$1</f>
+        <f aca="false">[3]Nov!$G$1</f>
         <v>0</v>
       </c>
       <c r="K7" s="87" t="n">
@@ -15968,7 +16076,7 @@
       </c>
       <c r="L7" s="88"/>
       <c r="M7" s="89" t="n">
-        <f aca="false">IF([2]May!$G$4&gt;0,[2]May!$G$4,0)</f>
+        <f aca="false">IF([2]Nov!$G$4&gt;0,[2]Nov!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N7" s="90"/>
@@ -15984,7 +16092,7 @@
         <v>46418</v>
       </c>
       <c r="D8" s="86" t="n">
-        <f aca="false">[2]Jun!$H$1</f>
+        <f aca="false">[2]Dec!$H$1</f>
         <v>0</v>
       </c>
       <c r="E8" s="87" t="n">
@@ -15992,7 +16100,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="87" t="n">
-        <f aca="false">[2]Jun!$G$1</f>
+        <f aca="false">[2]Dec!$G$1</f>
         <v>0</v>
       </c>
       <c r="G8" s="87" t="n">
@@ -16000,7 +16108,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="87" t="n">
-        <f aca="false">[3]Jun!$H$1</f>
+        <f aca="false">[3]Dec!$H$1</f>
         <v>0</v>
       </c>
       <c r="I8" s="87" t="n">
@@ -16008,7 +16116,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="87" t="n">
-        <f aca="false">[3]Jun!$G$1</f>
+        <f aca="false">[3]Dec!$G$1</f>
         <v>0</v>
       </c>
       <c r="K8" s="87" t="n">
@@ -16017,7 +16125,7 @@
       </c>
       <c r="L8" s="88"/>
       <c r="M8" s="89" t="n">
-        <f aca="false">IF([2]Sep!$G$4&gt;0,[2]Sep!$G$4,0)</f>
+        <f aca="false">IF([2]Mar!$G$4&gt;0,[2]Mar!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N8" s="90"/>
@@ -16033,7 +16141,7 @@
         <v>46446</v>
       </c>
       <c r="D9" s="86" t="n">
-        <f aca="false">[2]Jul!$H$1</f>
+        <f aca="false">[2]Jan!$H$1</f>
         <v>0</v>
       </c>
       <c r="E9" s="87" t="n">
@@ -16041,7 +16149,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="87" t="n">
-        <f aca="false">[2]Jul!$G$1</f>
+        <f aca="false">[2]Jan!$G$1</f>
         <v>0</v>
       </c>
       <c r="G9" s="87" t="n">
@@ -16049,7 +16157,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="87" t="n">
-        <f aca="false">[3]Jul!$H$1</f>
+        <f aca="false">[3]Jan!$H$1</f>
         <v>0</v>
       </c>
       <c r="I9" s="87" t="n">
@@ -16057,7 +16165,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="87" t="n">
-        <f aca="false">[3]Jul!$G$1</f>
+        <f aca="false">[3]Jan!$G$1</f>
         <v>0</v>
       </c>
       <c r="K9" s="87" t="n">
@@ -16066,7 +16174,7 @@
       </c>
       <c r="L9" s="88"/>
       <c r="M9" s="89" t="n">
-        <f aca="false">IF([2]May!$G$4&gt;0,[2]May!$G$4,0)</f>
+        <f aca="false">IF([2]Nov!$G$4&gt;0,[2]Nov!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N9" s="90"/>
@@ -16082,7 +16190,7 @@
         <v>46477</v>
       </c>
       <c r="D10" s="86" t="n">
-        <f aca="false">[2]Aug!$H$1</f>
+        <f aca="false">[2]Feb!$H$1</f>
         <v>0</v>
       </c>
       <c r="E10" s="87" t="n">
@@ -16090,7 +16198,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="87" t="n">
-        <f aca="false">[2]Aug!$G$1</f>
+        <f aca="false">[2]Feb!$G$1</f>
         <v>0</v>
       </c>
       <c r="G10" s="87" t="n">
@@ -16098,7 +16206,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="87" t="n">
-        <f aca="false">[3]Aug!$H$1</f>
+        <f aca="false">[3]Feb!$H$1</f>
         <v>0</v>
       </c>
       <c r="I10" s="87" t="n">
@@ -16106,7 +16214,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="87" t="n">
-        <f aca="false">[3]Aug!$G$1</f>
+        <f aca="false">[3]Feb!$G$1</f>
         <v>0</v>
       </c>
       <c r="K10" s="87" t="n">
@@ -16131,7 +16239,7 @@
         <v>46507</v>
       </c>
       <c r="D11" s="86" t="n">
-        <f aca="false">[2]Sep!$H$1</f>
+        <f aca="false">[2]Mar!$H$1</f>
         <v>0</v>
       </c>
       <c r="E11" s="87" t="n">
@@ -16139,7 +16247,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="87" t="n">
-        <f aca="false">[2]Sep!$G$1</f>
+        <f aca="false">[2]Mar!$G$1</f>
         <v>0</v>
       </c>
       <c r="G11" s="87" t="n">
@@ -16147,7 +16255,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="87" t="n">
-        <f aca="false">[3]Sep!$H$1</f>
+        <f aca="false">[3]Mar!$H$1</f>
         <v>0</v>
       </c>
       <c r="I11" s="87" t="n">
@@ -16155,7 +16263,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="87" t="n">
-        <f aca="false">[3]Sep!$G$1</f>
+        <f aca="false">[3]Mar!$G$1</f>
         <v>0</v>
       </c>
       <c r="K11" s="87" t="n">
@@ -16164,7 +16272,7 @@
       </c>
       <c r="L11" s="88"/>
       <c r="M11" s="89" t="n">
-        <f aca="false">IF([2]Jun!$G$4&gt;0,[2]Jun!$G$4,0)</f>
+        <f aca="false">IF([2]Dec!$G$4&gt;0,[2]Dec!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N11" s="90"/>
@@ -16262,7 +16370,7 @@
       </c>
       <c r="L13" s="88"/>
       <c r="M13" s="89" t="n">
-        <f aca="false">IF([2]Aug!$G$4&gt;0,[2]Aug!$G$4,0)</f>
+        <f aca="false">IF([2]Feb!$G$4&gt;0,[2]Feb!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N13" s="90"/>
@@ -16311,7 +16419,7 @@
       </c>
       <c r="L14" s="88"/>
       <c r="M14" s="89" t="n">
-        <f aca="false">IF([2]Aug!$G$4&gt;0,[2]Aug!$G$4,0)</f>
+        <f aca="false">IF([2]Feb!$G$4&gt;0,[2]Feb!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N14" s="90"/>
@@ -16409,7 +16517,7 @@
       </c>
       <c r="L16" s="88"/>
       <c r="M16" s="89" t="n">
-        <f aca="false">IF([2]Jun!$G$4&gt;0,[2]Jun!$G$4,0)</f>
+        <f aca="false">IF([2]Dec!$G$4&gt;0,[2]Dec!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N16" s="90"/>

--- a/examples/ltd-latest/Vatreturns.xlsx
+++ b/examples/ltd-latest/Vatreturns.xlsx
@@ -1374,6 +1374,11 @@
             <v>0</v>
           </cell>
         </row>
+        <row r="4">
+          <cell r="G4">
+            <v>0</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="4">
         <row r="1">
@@ -1391,6 +1396,11 @@
             <v>0</v>
           </cell>
           <cell r="H1">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="G4">
             <v>0</v>
           </cell>
         </row>
@@ -16125,7 +16135,7 @@
       </c>
       <c r="L8" s="88"/>
       <c r="M8" s="89" t="n">
-        <f aca="false">IF([2]Mar!$G$4&gt;0,[2]Mar!$G$4,0)</f>
+        <f aca="false">IF([2]Dec!$G$4&gt;0,[2]Dec!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N8" s="90"/>
@@ -16174,7 +16184,7 @@
       </c>
       <c r="L9" s="88"/>
       <c r="M9" s="89" t="n">
-        <f aca="false">IF([2]Nov!$G$4&gt;0,[2]Nov!$G$4,0)</f>
+        <f aca="false">IF([2]Jan!$G$4&gt;0,[2]Jan!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N9" s="90"/>
@@ -16223,7 +16233,7 @@
       </c>
       <c r="L10" s="88"/>
       <c r="M10" s="89" t="n">
-        <f aca="false">IF([2]Sep!$G$4&gt;0,[2]Sep!$G$4,0)</f>
+        <f aca="false">IF([2]Feb!$G$4&gt;0,[2]Feb!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N10" s="90"/>
@@ -16272,7 +16282,7 @@
       </c>
       <c r="L11" s="88"/>
       <c r="M11" s="89" t="n">
-        <f aca="false">IF([2]Dec!$G$4&gt;0,[2]Dec!$G$4,0)</f>
+        <f aca="false">IF([2]Mar!$G$4&gt;0,[2]Mar!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N11" s="90"/>
@@ -16321,7 +16331,7 @@
       </c>
       <c r="L12" s="88"/>
       <c r="M12" s="89" t="n">
-        <f aca="false">IF([2]May!$G$4&gt;0,[2]May!$G$4,0)</f>
+        <f aca="false">IF([2]Apr!$G$4&gt;0,[2]Apr!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N12" s="90"/>
@@ -16370,7 +16380,7 @@
       </c>
       <c r="L13" s="88"/>
       <c r="M13" s="89" t="n">
-        <f aca="false">IF([2]Feb!$G$4&gt;0,[2]Feb!$G$4,0)</f>
+        <f aca="false">IF([2]May!$G$4&gt;0,[2]May!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N13" s="90"/>
@@ -16419,7 +16429,7 @@
       </c>
       <c r="L14" s="88"/>
       <c r="M14" s="89" t="n">
-        <f aca="false">IF([2]Feb!$G$4&gt;0,[2]Feb!$G$4,0)</f>
+        <f aca="false">IF([2]Jun!$G$4&gt;0,[2]Jun!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N14" s="90"/>
@@ -16468,7 +16478,7 @@
       </c>
       <c r="L15" s="88"/>
       <c r="M15" s="89" t="n">
-        <f aca="false">IF([2]May!$G$4&gt;0,[2]May!$G$4,0)</f>
+        <f aca="false">IF([2]Jul!$G$4&gt;0,[2]Jul!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N15" s="90"/>
@@ -16517,7 +16527,7 @@
       </c>
       <c r="L16" s="88"/>
       <c r="M16" s="89" t="n">
-        <f aca="false">IF([2]Dec!$G$4&gt;0,[2]Dec!$G$4,0)</f>
+        <f aca="false">IF([2]Aug!$G$4&gt;0,[2]Aug!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N16" s="90"/>

--- a/examples/ltd-latest/Vatreturns.xlsx
+++ b/examples/ltd-latest/Vatreturns.xlsx
@@ -1374,11 +1374,6 @@
             <v>0</v>
           </cell>
         </row>
-        <row r="4">
-          <cell r="G4">
-            <v>0</v>
-          </cell>
-        </row>
       </sheetData>
       <sheetData sheetId="4">
         <row r="1">
@@ -1396,11 +1391,6 @@
             <v>0</v>
           </cell>
           <cell r="H1">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="G4">
             <v>0</v>
           </cell>
         </row>
@@ -16135,7 +16125,7 @@
       </c>
       <c r="L8" s="88"/>
       <c r="M8" s="89" t="n">
-        <f aca="false">IF([2]Dec!$G$4&gt;0,[2]Dec!$G$4,0)</f>
+        <f aca="false">IF([2]Mar!$G$4&gt;0,[2]Mar!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N8" s="90"/>
@@ -16184,7 +16174,7 @@
       </c>
       <c r="L9" s="88"/>
       <c r="M9" s="89" t="n">
-        <f aca="false">IF([2]Jan!$G$4&gt;0,[2]Jan!$G$4,0)</f>
+        <f aca="false">IF([2]Nov!$G$4&gt;0,[2]Nov!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N9" s="90"/>
@@ -16233,7 +16223,7 @@
       </c>
       <c r="L10" s="88"/>
       <c r="M10" s="89" t="n">
-        <f aca="false">IF([2]Feb!$G$4&gt;0,[2]Feb!$G$4,0)</f>
+        <f aca="false">IF([2]Sep!$G$4&gt;0,[2]Sep!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N10" s="90"/>
@@ -16282,7 +16272,7 @@
       </c>
       <c r="L11" s="88"/>
       <c r="M11" s="89" t="n">
-        <f aca="false">IF([2]Mar!$G$4&gt;0,[2]Mar!$G$4,0)</f>
+        <f aca="false">IF([2]Dec!$G$4&gt;0,[2]Dec!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N11" s="90"/>
@@ -16331,7 +16321,7 @@
       </c>
       <c r="L12" s="88"/>
       <c r="M12" s="89" t="n">
-        <f aca="false">IF([2]Apr!$G$4&gt;0,[2]Apr!$G$4,0)</f>
+        <f aca="false">IF([2]May!$G$4&gt;0,[2]May!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N12" s="90"/>
@@ -16380,7 +16370,7 @@
       </c>
       <c r="L13" s="88"/>
       <c r="M13" s="89" t="n">
-        <f aca="false">IF([2]May!$G$4&gt;0,[2]May!$G$4,0)</f>
+        <f aca="false">IF([2]Feb!$G$4&gt;0,[2]Feb!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N13" s="90"/>
@@ -16429,7 +16419,7 @@
       </c>
       <c r="L14" s="88"/>
       <c r="M14" s="89" t="n">
-        <f aca="false">IF([2]Jun!$G$4&gt;0,[2]Jun!$G$4,0)</f>
+        <f aca="false">IF([2]Feb!$G$4&gt;0,[2]Feb!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N14" s="90"/>
@@ -16478,7 +16468,7 @@
       </c>
       <c r="L15" s="88"/>
       <c r="M15" s="89" t="n">
-        <f aca="false">IF([2]Jul!$G$4&gt;0,[2]Jul!$G$4,0)</f>
+        <f aca="false">IF([2]May!$G$4&gt;0,[2]May!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N15" s="90"/>
@@ -16527,7 +16517,7 @@
       </c>
       <c r="L16" s="88"/>
       <c r="M16" s="89" t="n">
-        <f aca="false">IF([2]Aug!$G$4&gt;0,[2]Aug!$G$4,0)</f>
+        <f aca="false">IF([2]Dec!$G$4&gt;0,[2]Dec!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N16" s="90"/>

--- a/examples/ltd-latest/Vatreturns.xlsx
+++ b/examples/ltd-latest/Vatreturns.xlsx
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="60">
   <si>
     <t xml:space="preserve">Value  Added  Tax  Return</t>
   </si>
@@ -266,7 +266,28 @@
     <t xml:space="preserve">Vat       Output</t>
   </si>
   <si>
+    <t xml:space="preserve">Acme Corp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INV-0801</t>
+  </si>
+  <si>
     <t xml:space="preserve">Entries below this row are not included in Row 1 Totals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beta Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INV-0802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INV-1301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gamma Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INV-1302</t>
   </si>
   <si>
     <t xml:space="preserve">Purchase Date</t>
@@ -285,6 +306,30 @@
   </si>
   <si>
     <t xml:space="preserve">Vat Input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TechParts Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TP-2402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WorkSpace Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WS-2402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SH-2604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BT Business</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BT-2605</t>
   </si>
 </sst>
 </file>
@@ -1343,9 +1388,14 @@
       <sheetData sheetId="1">
         <row r="1">
           <cell r="G1">
-            <v>0</v>
+            <v>8426.66666666667</v>
           </cell>
           <cell r="H1">
+            <v>42133.3333333333</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="G4">
             <v>0</v>
           </cell>
         </row>
@@ -1353,10 +1403,10 @@
       <sheetData sheetId="2">
         <row r="1">
           <cell r="G1">
-            <v>0</v>
+            <v>5886.66666666667</v>
           </cell>
           <cell r="H1">
-            <v>0</v>
+            <v>29433.3333333333</v>
           </cell>
         </row>
         <row r="4">
@@ -1368,10 +1418,10 @@
       <sheetData sheetId="3">
         <row r="1">
           <cell r="G1">
-            <v>0</v>
+            <v>5466.66666666667</v>
           </cell>
           <cell r="H1">
-            <v>0</v>
+            <v>27333.3333333333</v>
           </cell>
         </row>
         <row r="4">
@@ -1383,9 +1433,14 @@
       <sheetData sheetId="4">
         <row r="1">
           <cell r="G1">
-            <v>0</v>
+            <v>5906.66666666667</v>
           </cell>
           <cell r="H1">
+            <v>29533.3333333333</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="G4">
             <v>0</v>
           </cell>
         </row>
@@ -1393,10 +1448,10 @@
       <sheetData sheetId="5">
         <row r="1">
           <cell r="G1">
-            <v>0</v>
+            <v>5726.66666666667</v>
           </cell>
           <cell r="H1">
-            <v>0</v>
+            <v>28633.3333333333</v>
           </cell>
         </row>
         <row r="4">
@@ -1408,10 +1463,10 @@
       <sheetData sheetId="6">
         <row r="1">
           <cell r="G1">
-            <v>0</v>
+            <v>5226.66666666667</v>
           </cell>
           <cell r="H1">
-            <v>0</v>
+            <v>26133.3333333333</v>
           </cell>
         </row>
         <row r="4">
@@ -1423,20 +1478,20 @@
       <sheetData sheetId="7">
         <row r="1">
           <cell r="G1">
-            <v>0</v>
+            <v>5566.66666666667</v>
           </cell>
           <cell r="H1">
-            <v>0</v>
+            <v>27833.3333333333</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="8">
         <row r="1">
           <cell r="G1">
-            <v>0</v>
+            <v>5486.66666666667</v>
           </cell>
           <cell r="H1">
-            <v>0</v>
+            <v>27433.3333333333</v>
           </cell>
         </row>
         <row r="4">
@@ -1448,9 +1503,14 @@
       <sheetData sheetId="9">
         <row r="1">
           <cell r="G1">
-            <v>0</v>
+            <v>5866.66666666667</v>
           </cell>
           <cell r="H1">
+            <v>29333.3333333333</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="G4">
             <v>0</v>
           </cell>
         </row>
@@ -1458,9 +1518,14 @@
       <sheetData sheetId="10">
         <row r="1">
           <cell r="G1">
-            <v>0</v>
+            <v>5626.66666666667</v>
           </cell>
           <cell r="H1">
+            <v>28133.3333333333</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="G4">
             <v>0</v>
           </cell>
         </row>
@@ -1468,9 +1533,14 @@
       <sheetData sheetId="11">
         <row r="1">
           <cell r="G1">
-            <v>0</v>
+            <v>6003.33333333333</v>
           </cell>
           <cell r="H1">
+            <v>30016.6666666667</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="G4">
             <v>0</v>
           </cell>
         </row>
@@ -1478,10 +1548,10 @@
       <sheetData sheetId="12">
         <row r="1">
           <cell r="G1">
-            <v>0</v>
+            <v>5626.66666666667</v>
           </cell>
           <cell r="H1">
-            <v>0</v>
+            <v>28133.3333333333</v>
           </cell>
         </row>
         <row r="4">
@@ -1537,120 +1607,120 @@
       <sheetData sheetId="1">
         <row r="1">
           <cell r="G1">
-            <v>0</v>
+            <v>7167.625</v>
           </cell>
           <cell r="H1">
-            <v>0</v>
+            <v>35838.125</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="2">
         <row r="1">
           <cell r="G1">
-            <v>0</v>
+            <v>1153</v>
           </cell>
           <cell r="H1">
-            <v>0</v>
+            <v>5765</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="3">
         <row r="1">
           <cell r="G1">
-            <v>0</v>
+            <v>1575.25</v>
           </cell>
           <cell r="H1">
-            <v>0</v>
+            <v>7876.25</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="4">
         <row r="1">
           <cell r="G1">
-            <v>0</v>
+            <v>751.875</v>
           </cell>
           <cell r="H1">
-            <v>0</v>
+            <v>3759.375</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="5">
         <row r="1">
           <cell r="G1">
-            <v>0</v>
+            <v>732.75</v>
           </cell>
           <cell r="H1">
-            <v>0</v>
+            <v>3663.75</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="6">
         <row r="1">
           <cell r="G1">
-            <v>0</v>
+            <v>621.083333333333</v>
           </cell>
           <cell r="H1">
-            <v>0</v>
+            <v>3105.41666666667</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="7">
         <row r="1">
           <cell r="G1">
-            <v>0</v>
+            <v>851.875</v>
           </cell>
           <cell r="H1">
-            <v>0</v>
+            <v>4259.375</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="8">
         <row r="1">
           <cell r="G1">
-            <v>0</v>
+            <v>1062.5</v>
           </cell>
           <cell r="H1">
-            <v>0</v>
+            <v>5312.5</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="9">
         <row r="1">
           <cell r="G1">
-            <v>0</v>
+            <v>1509.5</v>
           </cell>
           <cell r="H1">
-            <v>0</v>
+            <v>7547.5</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="10">
         <row r="1">
           <cell r="G1">
-            <v>0</v>
+            <v>1509.875</v>
           </cell>
           <cell r="H1">
-            <v>0</v>
+            <v>7549.375</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="11">
         <row r="1">
           <cell r="G1">
-            <v>0</v>
+            <v>734.208333333333</v>
           </cell>
           <cell r="H1">
-            <v>0</v>
+            <v>3671.04166666667</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="12">
         <row r="1">
           <cell r="G1">
-            <v>0</v>
+            <v>829.166666666667</v>
           </cell>
           <cell r="H1">
-            <v>0</v>
+            <v>4145.83333333333</v>
           </cell>
         </row>
       </sheetData>
@@ -1938,7 +2008,7 @@
       </c>
       <c r="G9" s="37" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!G1:G20)</f>
-        <v>0</v>
+        <v>16920</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="14"/>
@@ -2011,7 +2081,7 @@
       </c>
       <c r="G13" s="37" t="n">
         <f aca="false">G9+G11</f>
-        <v>0</v>
+        <v>16920</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="14"/>
@@ -2048,7 +2118,7 @@
       </c>
       <c r="G15" s="37" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!K1:K20)</f>
-        <v>0</v>
+        <v>3423.875</v>
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="14"/>
@@ -2073,7 +2143,7 @@
       <c r="A17" s="41"/>
       <c r="B17" s="43" t="str">
         <f aca="false">IF(G17&gt;0,"Net VAT to be PAID to Customs","Net VAT to be RECLIAMED from Customs")</f>
-        <v>Net VAT to be RECLIAMED from Customs</v>
+        <v>Net VAT to be PAID to Customs</v>
       </c>
       <c r="C17" s="43"/>
       <c r="D17" s="43"/>
@@ -2083,7 +2153,7 @@
       </c>
       <c r="G17" s="37" t="n">
         <f aca="false">G13-G15</f>
-        <v>0</v>
+        <v>13496.125</v>
       </c>
       <c r="H17" s="13"/>
       <c r="I17" s="14"/>
@@ -2142,7 +2212,7 @@
       </c>
       <c r="G21" s="52" t="n">
         <f aca="false">IF(LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!M1:M20)&gt;0,(LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!E1:E20)+LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!G1:G20)),LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!E1:E20))</f>
-        <v>0</v>
+        <v>84599.9999999999</v>
       </c>
       <c r="H21" s="13"/>
       <c r="I21" s="14"/>
@@ -2171,7 +2241,7 @@
       </c>
       <c r="G23" s="52" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!I1:I20)</f>
-        <v>0</v>
+        <v>17119.375</v>
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="14"/>
@@ -2366,15 +2436,15 @@
       <c r="E1" s="104"/>
       <c r="F1" s="105" t="n">
         <f aca="false">SUM(F5:F500)</f>
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="G1" s="105" t="n">
         <f aca="false">SUM(G5:G500)</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H1" s="105" t="n">
         <f aca="false">SUM(H5:H500)</f>
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="2" s="106" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2428,13 +2498,25 @@
       <c r="H4" s="108"/>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G5" s="99" t="str">
+      <c r="A5" s="98" t="n">
+        <v>46338</v>
+      </c>
+      <c r="B5" s="99" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="100" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="99" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G5" s="99" t="n">
         <f aca="false">IF(G$4&gt;0,(IF(F5&lt;&gt;0,F5*G$4/100," ")),IF(F5&lt;&gt;0,F5*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H5" s="99" t="str">
+        <v>300</v>
+      </c>
+      <c r="H5" s="99" t="n">
         <f aca="false">IF((F5&lt;&gt;0),F5-G5," ")</f>
-        <v> </v>
+        <v>1500</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4395,7 +4477,7 @@
     </row>
     <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="98" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -4451,41 +4533,41 @@
       <c r="E1" s="105"/>
       <c r="F1" s="105" t="n">
         <f aca="false">SUM(F5:F200)</f>
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="G1" s="105" t="n">
         <f aca="false">SUM(G5:G200)</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H1" s="105" t="n">
         <f aca="false">SUM(H5:H200)</f>
-        <v>0</v>
+        <v>600</v>
       </c>
     </row>
     <row r="2" s="127" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="107" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B2" s="108" t="str">
         <f aca="false">IF((H1-SUM(O1:AK1)&lt;&gt;0),"COMPLETE EXPENSE ANALYSIS by inserting expense letter in col F","Supplier")</f>
-        <v>Supplier</v>
+        <v>COMPLETE EXPENSE ANALYSIS by inserting expense letter in col F</v>
       </c>
       <c r="C2" s="110" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D2" s="124" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E2" s="125"/>
       <c r="F2" s="108" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G2" s="126" t="n">
         <f aca="false">[3]OpeningCreditors!$G$2</f>
         <v>20</v>
       </c>
       <c r="H2" s="108" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" s="128" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4496,7 +4578,7 @@
       <c r="E3" s="125"/>
       <c r="F3" s="108"/>
       <c r="G3" s="108" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="H3" s="108"/>
     </row>
@@ -4510,19 +4592,27 @@
       <c r="G4" s="108"/>
       <c r="H4" s="108"/>
     </row>
-    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="122"/>
-      <c r="C5" s="129"/>
+    <row r="5" s="119" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="118" t="n">
+        <v>45889</v>
+      </c>
+      <c r="B5" s="122" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="129" t="s">
+        <v>53</v>
+      </c>
       <c r="D5" s="122"/>
-      <c r="E5" s="119"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="123" t="str">
+      <c r="F5" s="130" t="n">
+        <v>720</v>
+      </c>
+      <c r="G5" s="123" t="n">
         <f aca="false">IF(F5&lt;&gt;0,F5*G$2/(100+G$2)," ")</f>
-        <v> </v>
-      </c>
-      <c r="H5" s="123" t="str">
+        <v>120</v>
+      </c>
+      <c r="H5" s="123" t="n">
         <f aca="false">IF((F5&lt;&gt;0),F5-G5," ")</f>
-        <v> </v>
+        <v>600</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6679,7 +6769,7 @@
     </row>
     <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="98" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G201" s="123" t="e">
         <f aca="false">NA()</f>
@@ -6740,41 +6830,41 @@
       <c r="E1" s="105"/>
       <c r="F1" s="105" t="n">
         <f aca="false">SUM(F5:F200)</f>
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="G1" s="105" t="n">
         <f aca="false">SUM(G5:G200)</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H1" s="105" t="n">
         <f aca="false">SUM(H5:H200)</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="2" s="127" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="107" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B2" s="108" t="str">
         <f aca="false">IF((H1-SUM(O1:AK1)&lt;&gt;0),"COMPLETE EXPENSE ANALYSIS by inserting expense letter in col F","Supplier")</f>
-        <v>Supplier</v>
+        <v>COMPLETE EXPENSE ANALYSIS by inserting expense letter in col F</v>
       </c>
       <c r="C2" s="110" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D2" s="124" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E2" s="125"/>
       <c r="F2" s="108" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G2" s="126" t="n">
         <f aca="false">[3]OpeningCreditors!$G$2</f>
         <v>20</v>
       </c>
       <c r="H2" s="108" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" s="128" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6785,7 +6875,7 @@
       <c r="E3" s="125"/>
       <c r="F3" s="108"/>
       <c r="G3" s="108" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="H3" s="108"/>
     </row>
@@ -6799,19 +6889,27 @@
       <c r="G4" s="108"/>
       <c r="H4" s="108"/>
     </row>
-    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="122"/>
-      <c r="C5" s="129"/>
+    <row r="5" s="119" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="118" t="n">
+        <v>45924</v>
+      </c>
+      <c r="B5" s="122" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="129" t="s">
+        <v>55</v>
+      </c>
       <c r="D5" s="122"/>
-      <c r="E5" s="119"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="123" t="str">
+      <c r="F5" s="130" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G5" s="123" t="n">
         <f aca="false">IF(F5&lt;&gt;0,F5*G$2/(100+G$2)," ")</f>
-        <v> </v>
-      </c>
-      <c r="H5" s="123" t="str">
+        <v>200</v>
+      </c>
+      <c r="H5" s="123" t="n">
         <f aca="false">IF((F5&lt;&gt;0),F5-G5," ")</f>
-        <v> </v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8968,7 +9066,7 @@
     </row>
     <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="98" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G201" s="123" t="e">
         <f aca="false">NA()</f>
@@ -9029,41 +9127,41 @@
       <c r="E1" s="105"/>
       <c r="F1" s="105" t="n">
         <f aca="false">SUM(F5:F200)</f>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="G1" s="105" t="n">
         <f aca="false">SUM(G5:G200)</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H1" s="105" t="n">
         <f aca="false">SUM(H5:H200)</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" s="127" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="107" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B2" s="108" t="str">
         <f aca="false">IF((H1-SUM(O1:AK1)&lt;&gt;0),"COMPLETE EXPENSE ANALYSIS by inserting expense letter in col F","Supplier")</f>
-        <v>Supplier</v>
+        <v>COMPLETE EXPENSE ANALYSIS by inserting expense letter in col F</v>
       </c>
       <c r="C2" s="110" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D2" s="124" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E2" s="125"/>
       <c r="F2" s="108" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G2" s="126" t="n">
         <f aca="false">[3]ClosingCreditors!$G$2</f>
         <v>20</v>
       </c>
       <c r="H2" s="108" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" s="128" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9074,7 +9172,7 @@
       <c r="E3" s="125"/>
       <c r="F3" s="108"/>
       <c r="G3" s="108" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="H3" s="108"/>
     </row>
@@ -9088,19 +9186,27 @@
       <c r="G4" s="108"/>
       <c r="H4" s="108"/>
     </row>
-    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="122"/>
-      <c r="C5" s="129"/>
+    <row r="5" s="119" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="118" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B5" s="122" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="129" t="s">
+        <v>57</v>
+      </c>
       <c r="D5" s="122"/>
-      <c r="E5" s="119"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="123" t="str">
+      <c r="F5" s="130" t="n">
+        <v>240</v>
+      </c>
+      <c r="G5" s="123" t="n">
         <f aca="false">IF(F5&lt;&gt;0,F5*G$2/(100+G$2)," ")</f>
-        <v> </v>
-      </c>
-      <c r="H5" s="123" t="str">
+        <v>40</v>
+      </c>
+      <c r="H5" s="123" t="n">
         <f aca="false">IF((F5&lt;&gt;0),F5-G5," ")</f>
-        <v> </v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11257,7 +11363,7 @@
     </row>
     <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="98" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G201" s="123" t="e">
         <f aca="false">NA()</f>
@@ -11318,41 +11424,41 @@
       <c r="E1" s="105"/>
       <c r="F1" s="105" t="n">
         <f aca="false">SUM(F5:F200)</f>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="G1" s="105" t="n">
         <f aca="false">SUM(G5:G200)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H1" s="105" t="n">
         <f aca="false">SUM(H5:H200)</f>
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="2" s="127" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="107" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B2" s="108" t="str">
         <f aca="false">IF((H1-SUM(O1:AK1)&lt;&gt;0),"COMPLETE EXPENSE ANALYSIS by inserting expense letter in col F","Supplier")</f>
-        <v>Supplier</v>
+        <v>COMPLETE EXPENSE ANALYSIS by inserting expense letter in col F</v>
       </c>
       <c r="C2" s="110" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D2" s="124" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E2" s="125"/>
       <c r="F2" s="108" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G2" s="126" t="n">
         <f aca="false">[3]ClosingCreditors!$G$2</f>
         <v>20</v>
       </c>
       <c r="H2" s="108" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" s="128" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11363,7 +11469,7 @@
       <c r="E3" s="125"/>
       <c r="F3" s="108"/>
       <c r="G3" s="108" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="H3" s="108"/>
     </row>
@@ -11377,19 +11483,27 @@
       <c r="G4" s="108"/>
       <c r="H4" s="108"/>
     </row>
-    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="122"/>
-      <c r="C5" s="129"/>
+    <row r="5" s="119" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="118" t="n">
+        <v>46345</v>
+      </c>
+      <c r="B5" s="122" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="129" t="s">
+        <v>59</v>
+      </c>
       <c r="D5" s="122"/>
-      <c r="E5" s="119"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="123" t="str">
+      <c r="F5" s="130" t="n">
+        <v>360</v>
+      </c>
+      <c r="G5" s="123" t="n">
         <f aca="false">IF(F5&lt;&gt;0,F5*G$2/(100+G$2)," ")</f>
-        <v> </v>
-      </c>
-      <c r="H5" s="123" t="str">
+        <v>60</v>
+      </c>
+      <c r="H5" s="123" t="n">
         <f aca="false">IF((F5&lt;&gt;0),F5-G5," ")</f>
-        <v> </v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13546,7 +13660,7 @@
     </row>
     <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="98" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G201" s="123" t="e">
         <f aca="false">NA()</f>
@@ -13742,7 +13856,7 @@
       </c>
       <c r="G9" s="37" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!G1:G20)</f>
-        <v>0</v>
+        <v>17256.6666666667</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="14"/>
@@ -13815,7 +13929,7 @@
       </c>
       <c r="G13" s="37" t="n">
         <f aca="false">G9+G11</f>
-        <v>0</v>
+        <v>17256.6666666667</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="14"/>
@@ -13852,7 +13966,7 @@
       </c>
       <c r="G15" s="37" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!K1:K20)</f>
-        <v>0</v>
+        <v>3073.25</v>
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="14"/>
@@ -13877,7 +13991,7 @@
       <c r="A17" s="41"/>
       <c r="B17" s="43" t="str">
         <f aca="false">IF(G17&gt;0,"Net VAT to be PAID to Customs","Net VAT to be RECLIAMED from Customs")</f>
-        <v>Net VAT to be RECLIAMED from Customs</v>
+        <v>Net VAT to be PAID to Customs</v>
       </c>
       <c r="C17" s="43"/>
       <c r="D17" s="43"/>
@@ -13887,7 +14001,7 @@
       </c>
       <c r="G17" s="37" t="n">
         <f aca="false">G13-G15</f>
-        <v>0</v>
+        <v>14183.4166666667</v>
       </c>
       <c r="H17" s="13"/>
       <c r="I17" s="14"/>
@@ -13946,7 +14060,7 @@
       </c>
       <c r="G21" s="52" t="n">
         <f aca="false">IF(LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!M1:M20)&gt;0,(LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!E1:E20)+LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!G1:G20)),LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!E1:E20))</f>
-        <v>0</v>
+        <v>86283.3333333333</v>
       </c>
       <c r="H21" s="13"/>
       <c r="I21" s="14"/>
@@ -13975,7 +14089,7 @@
       </c>
       <c r="G23" s="52" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!I1:I20)</f>
-        <v>0</v>
+        <v>15366.25</v>
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="14"/>
@@ -14306,7 +14420,7 @@
       </c>
       <c r="G9" s="37" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!G1:G20)</f>
-        <v>0</v>
+        <v>19780</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="14"/>
@@ -14379,7 +14493,7 @@
       </c>
       <c r="G13" s="37" t="n">
         <f aca="false">G9+G11</f>
-        <v>0</v>
+        <v>19780</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="14"/>
@@ -14416,7 +14530,7 @@
       </c>
       <c r="G15" s="37" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!K1:K20)</f>
-        <v>0</v>
+        <v>9895.875</v>
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="14"/>
@@ -14441,7 +14555,7 @@
       <c r="A17" s="41"/>
       <c r="B17" s="43" t="str">
         <f aca="false">IF(G17&gt;0,"Net VAT to be PAID to Customs","Net VAT to be RECLIAMED from Customs")</f>
-        <v>Net VAT to be RECLIAMED from Customs</v>
+        <v>Net VAT to be PAID to Customs</v>
       </c>
       <c r="C17" s="43"/>
       <c r="D17" s="43"/>
@@ -14451,7 +14565,7 @@
       </c>
       <c r="G17" s="37" t="n">
         <f aca="false">G13-G15</f>
-        <v>0</v>
+        <v>9884.12500000001</v>
       </c>
       <c r="H17" s="13"/>
       <c r="I17" s="14"/>
@@ -14510,7 +14624,7 @@
       </c>
       <c r="G21" s="52" t="n">
         <f aca="false">IF(LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!M1:M20)&gt;0,(LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!E1:E20)+LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!G1:G20)),LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!E1:E20))</f>
-        <v>0</v>
+        <v>98899.9999999999</v>
       </c>
       <c r="H21" s="13"/>
       <c r="I21" s="14"/>
@@ -14539,7 +14653,7 @@
       </c>
       <c r="G23" s="52" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!I1:I20)</f>
-        <v>0</v>
+        <v>49479.375</v>
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="14"/>
@@ -14870,7 +14984,7 @@
       </c>
       <c r="G9" s="37" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!G1:G20)</f>
-        <v>0</v>
+        <v>16860</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="14"/>
@@ -14943,7 +15057,7 @@
       </c>
       <c r="G13" s="37" t="n">
         <f aca="false">G9+G11</f>
-        <v>0</v>
+        <v>16860</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="14"/>
@@ -14980,7 +15094,7 @@
       </c>
       <c r="G15" s="37" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!K1:K20)</f>
-        <v>0</v>
+        <v>2105.70833333333</v>
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="14"/>
@@ -15005,7 +15119,7 @@
       <c r="A17" s="41"/>
       <c r="B17" s="43" t="str">
         <f aca="false">IF(G17&gt;0,"Net VAT to be PAID to Customs","Net VAT to be RECLIAMED from Customs")</f>
-        <v>Net VAT to be RECLIAMED from Customs</v>
+        <v>Net VAT to be PAID to Customs</v>
       </c>
       <c r="C17" s="43"/>
       <c r="D17" s="43"/>
@@ -15015,7 +15129,7 @@
       </c>
       <c r="G17" s="37" t="n">
         <f aca="false">G13-G15</f>
-        <v>0</v>
+        <v>14754.2916666667</v>
       </c>
       <c r="H17" s="13"/>
       <c r="I17" s="14"/>
@@ -15074,7 +15188,7 @@
       </c>
       <c r="G21" s="52" t="n">
         <f aca="false">IF(LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!M1:M20)&gt;0,(LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!E1:E20)+LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!G1:G20)),LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!E1:E20))</f>
-        <v>0</v>
+        <v>84299.9999999999</v>
       </c>
       <c r="H21" s="13"/>
       <c r="I21" s="14"/>
@@ -15103,7 +15217,7 @@
       </c>
       <c r="G23" s="52" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!I1:I20)</f>
-        <v>0</v>
+        <v>10528.5416666667</v>
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="14"/>
@@ -15434,7 +15548,7 @@
       </c>
       <c r="G9" s="37" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!G1:G20)</f>
-        <v>0</v>
+        <v>11553.3333333333</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="14"/>
@@ -15507,7 +15621,7 @@
       </c>
       <c r="G13" s="37" t="n">
         <f aca="false">G9+G11</f>
-        <v>0</v>
+        <v>11553.3333333333</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="14"/>
@@ -15544,7 +15658,7 @@
       </c>
       <c r="G15" s="37" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!K1:K20)</f>
-        <v>0</v>
+        <v>1393.83333333333</v>
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="14"/>
@@ -15569,7 +15683,7 @@
       <c r="A17" s="41"/>
       <c r="B17" s="43" t="str">
         <f aca="false">IF(G17&gt;0,"Net VAT to be PAID to Customs","Net VAT to be RECLIAMED from Customs")</f>
-        <v>Net VAT to be RECLIAMED from Customs</v>
+        <v>Net VAT to be PAID to Customs</v>
       </c>
       <c r="C17" s="43"/>
       <c r="D17" s="43"/>
@@ -15579,7 +15693,7 @@
       </c>
       <c r="G17" s="37" t="n">
         <f aca="false">G13-G15</f>
-        <v>0</v>
+        <v>10159.5</v>
       </c>
       <c r="H17" s="13"/>
       <c r="I17" s="14"/>
@@ -15638,7 +15752,7 @@
       </c>
       <c r="G21" s="52" t="n">
         <f aca="false">IF(LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!M1:M20)&gt;0,(LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!E1:E20)+LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!G1:G20)),LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!E1:E20))</f>
-        <v>0</v>
+        <v>57766.6666666666</v>
       </c>
       <c r="H21" s="13"/>
       <c r="I21" s="14"/>
@@ -15667,7 +15781,7 @@
       </c>
       <c r="G23" s="52" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!I1:I20)</f>
-        <v>0</v>
+        <v>6969.16666666667</v>
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="14"/>
@@ -15931,22 +16045,22 @@
       </c>
       <c r="D4" s="86" t="n">
         <f aca="false">S02Y1!$H$1</f>
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="E4" s="87"/>
       <c r="F4" s="87" t="n">
         <f aca="false">S02Y1!$G$1</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="G4" s="87"/>
       <c r="H4" s="87" t="n">
         <f aca="false">P02Y1!$H$1</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="I4" s="87"/>
       <c r="J4" s="87" t="n">
         <f aca="false">P02Y1!$G$1</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K4" s="87"/>
       <c r="L4" s="88"/>
@@ -15968,22 +16082,22 @@
       </c>
       <c r="D5" s="86" t="n">
         <f aca="false">S03Y1!$H$1</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="E5" s="87"/>
       <c r="F5" s="87" t="n">
         <f aca="false">S03Y1!$G$1</f>
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G5" s="87"/>
       <c r="H5" s="87" t="n">
         <f aca="false">P03Y1!$H$1</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I5" s="87"/>
       <c r="J5" s="87" t="n">
         <f aca="false">P03Y1!$G$1</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K5" s="87"/>
       <c r="L5" s="88"/>
@@ -16005,35 +16119,35 @@
       </c>
       <c r="D6" s="86" t="n">
         <f aca="false">[2]Oct!$H$1</f>
-        <v>0</v>
+        <v>27833.3333333333</v>
       </c>
       <c r="E6" s="87" t="n">
         <f aca="false">SUM(D4:D6)</f>
-        <v>0</v>
+        <v>33833.3333333333</v>
       </c>
       <c r="F6" s="87" t="n">
         <f aca="false">[2]Oct!$G$1</f>
-        <v>0</v>
+        <v>5566.66666666667</v>
       </c>
       <c r="G6" s="87" t="n">
         <f aca="false">SUM(F4:F6)</f>
-        <v>0</v>
+        <v>6766.66666666667</v>
       </c>
       <c r="H6" s="87" t="n">
         <f aca="false">[3]Oct!$H$1</f>
-        <v>0</v>
+        <v>4259.375</v>
       </c>
       <c r="I6" s="87" t="n">
         <f aca="false">SUM(H4:H6)</f>
-        <v>0</v>
+        <v>5859.375</v>
       </c>
       <c r="J6" s="87" t="n">
         <f aca="false">[3]Oct!$G$1</f>
-        <v>0</v>
+        <v>851.875</v>
       </c>
       <c r="K6" s="87" t="n">
         <f aca="false">SUM(J4:J6)</f>
-        <v>0</v>
+        <v>1171.875</v>
       </c>
       <c r="L6" s="88"/>
       <c r="M6" s="89" t="n">
@@ -16054,35 +16168,35 @@
       </c>
       <c r="D7" s="86" t="n">
         <f aca="false">[2]Nov!$H$1</f>
-        <v>0</v>
+        <v>27433.3333333333</v>
       </c>
       <c r="E7" s="87" t="n">
         <f aca="false">SUM(D5:D7)</f>
-        <v>0</v>
+        <v>57266.6666666666</v>
       </c>
       <c r="F7" s="87" t="n">
         <f aca="false">[2]Nov!$G$1</f>
-        <v>0</v>
+        <v>5486.66666666667</v>
       </c>
       <c r="G7" s="87" t="n">
         <f aca="false">SUM(F5:F7)</f>
-        <v>0</v>
+        <v>11453.3333333333</v>
       </c>
       <c r="H7" s="87" t="n">
         <f aca="false">[3]Nov!$H$1</f>
-        <v>0</v>
+        <v>5312.5</v>
       </c>
       <c r="I7" s="87" t="n">
         <f aca="false">SUM(H5:H7)</f>
-        <v>0</v>
+        <v>10571.875</v>
       </c>
       <c r="J7" s="87" t="n">
         <f aca="false">[3]Nov!$G$1</f>
-        <v>0</v>
+        <v>1062.5</v>
       </c>
       <c r="K7" s="87" t="n">
         <f aca="false">SUM(J5:J7)</f>
-        <v>0</v>
+        <v>2114.375</v>
       </c>
       <c r="L7" s="88"/>
       <c r="M7" s="89" t="n">
@@ -16103,35 +16217,35 @@
       </c>
       <c r="D8" s="86" t="n">
         <f aca="false">[2]Dec!$H$1</f>
-        <v>0</v>
+        <v>29333.3333333333</v>
       </c>
       <c r="E8" s="87" t="n">
         <f aca="false">SUM(D6:D8)</f>
-        <v>0</v>
+        <v>84599.9999999999</v>
       </c>
       <c r="F8" s="87" t="n">
         <f aca="false">[2]Dec!$G$1</f>
-        <v>0</v>
+        <v>5866.66666666667</v>
       </c>
       <c r="G8" s="87" t="n">
         <f aca="false">SUM(F6:F8)</f>
-        <v>0</v>
+        <v>16920</v>
       </c>
       <c r="H8" s="87" t="n">
         <f aca="false">[3]Dec!$H$1</f>
-        <v>0</v>
+        <v>7547.5</v>
       </c>
       <c r="I8" s="87" t="n">
         <f aca="false">SUM(H6:H8)</f>
-        <v>0</v>
+        <v>17119.375</v>
       </c>
       <c r="J8" s="87" t="n">
         <f aca="false">[3]Dec!$G$1</f>
-        <v>0</v>
+        <v>1509.5</v>
       </c>
       <c r="K8" s="87" t="n">
         <f aca="false">SUM(J6:J8)</f>
-        <v>0</v>
+        <v>3423.875</v>
       </c>
       <c r="L8" s="88"/>
       <c r="M8" s="89" t="n">
@@ -16152,35 +16266,35 @@
       </c>
       <c r="D9" s="86" t="n">
         <f aca="false">[2]Jan!$H$1</f>
-        <v>0</v>
+        <v>28133.3333333333</v>
       </c>
       <c r="E9" s="87" t="n">
         <f aca="false">SUM(D7:D9)</f>
-        <v>0</v>
+        <v>84899.9999999999</v>
       </c>
       <c r="F9" s="87" t="n">
         <f aca="false">[2]Jan!$G$1</f>
-        <v>0</v>
+        <v>5626.66666666667</v>
       </c>
       <c r="G9" s="87" t="n">
         <f aca="false">SUM(F7:F9)</f>
-        <v>0</v>
+        <v>16980</v>
       </c>
       <c r="H9" s="87" t="n">
         <f aca="false">[3]Jan!$H$1</f>
-        <v>0</v>
+        <v>7549.375</v>
       </c>
       <c r="I9" s="87" t="n">
         <f aca="false">SUM(H7:H9)</f>
-        <v>0</v>
+        <v>20409.375</v>
       </c>
       <c r="J9" s="87" t="n">
         <f aca="false">[3]Jan!$G$1</f>
-        <v>0</v>
+        <v>1509.875</v>
       </c>
       <c r="K9" s="87" t="n">
         <f aca="false">SUM(J7:J9)</f>
-        <v>0</v>
+        <v>4081.875</v>
       </c>
       <c r="L9" s="88"/>
       <c r="M9" s="89" t="n">
@@ -16201,35 +16315,35 @@
       </c>
       <c r="D10" s="86" t="n">
         <f aca="false">[2]Feb!$H$1</f>
-        <v>0</v>
+        <v>30016.6666666667</v>
       </c>
       <c r="E10" s="87" t="n">
         <f aca="false">SUM(D8:D10)</f>
-        <v>0</v>
+        <v>87483.3333333333</v>
       </c>
       <c r="F10" s="87" t="n">
         <f aca="false">[2]Feb!$G$1</f>
-        <v>0</v>
+        <v>6003.33333333333</v>
       </c>
       <c r="G10" s="87" t="n">
         <f aca="false">SUM(F8:F10)</f>
-        <v>0</v>
+        <v>17496.6666666667</v>
       </c>
       <c r="H10" s="87" t="n">
         <f aca="false">[3]Feb!$H$1</f>
-        <v>0</v>
+        <v>3671.04166666667</v>
       </c>
       <c r="I10" s="87" t="n">
         <f aca="false">SUM(H8:H10)</f>
-        <v>0</v>
+        <v>18767.9166666667</v>
       </c>
       <c r="J10" s="87" t="n">
         <f aca="false">[3]Feb!$G$1</f>
-        <v>0</v>
+        <v>734.208333333333</v>
       </c>
       <c r="K10" s="87" t="n">
         <f aca="false">SUM(J8:J10)</f>
-        <v>0</v>
+        <v>3753.58333333333</v>
       </c>
       <c r="L10" s="88"/>
       <c r="M10" s="89" t="n">
@@ -16250,35 +16364,35 @@
       </c>
       <c r="D11" s="86" t="n">
         <f aca="false">[2]Mar!$H$1</f>
-        <v>0</v>
+        <v>28133.3333333333</v>
       </c>
       <c r="E11" s="87" t="n">
         <f aca="false">SUM(D9:D11)</f>
-        <v>0</v>
+        <v>86283.3333333333</v>
       </c>
       <c r="F11" s="87" t="n">
         <f aca="false">[2]Mar!$G$1</f>
-        <v>0</v>
+        <v>5626.66666666667</v>
       </c>
       <c r="G11" s="87" t="n">
         <f aca="false">SUM(F9:F11)</f>
-        <v>0</v>
+        <v>17256.6666666667</v>
       </c>
       <c r="H11" s="87" t="n">
         <f aca="false">[3]Mar!$H$1</f>
-        <v>0</v>
+        <v>4145.83333333333</v>
       </c>
       <c r="I11" s="87" t="n">
         <f aca="false">SUM(H9:H11)</f>
-        <v>0</v>
+        <v>15366.25</v>
       </c>
       <c r="J11" s="87" t="n">
         <f aca="false">[3]Mar!$G$1</f>
-        <v>0</v>
+        <v>829.166666666667</v>
       </c>
       <c r="K11" s="87" t="n">
         <f aca="false">SUM(J9:J11)</f>
-        <v>0</v>
+        <v>3073.25</v>
       </c>
       <c r="L11" s="88"/>
       <c r="M11" s="89" t="n">
@@ -16299,35 +16413,35 @@
       </c>
       <c r="D12" s="86" t="n">
         <f aca="false">[2]Apr!$H$1</f>
-        <v>0</v>
+        <v>42133.3333333333</v>
       </c>
       <c r="E12" s="87" t="n">
         <f aca="false">SUM(D10:D12)</f>
-        <v>0</v>
+        <v>100283.333333333</v>
       </c>
       <c r="F12" s="87" t="n">
         <f aca="false">[2]Apr!$G$1</f>
-        <v>0</v>
+        <v>8426.66666666667</v>
       </c>
       <c r="G12" s="87" t="n">
         <f aca="false">SUM(F10:F12)</f>
-        <v>0</v>
+        <v>20056.6666666667</v>
       </c>
       <c r="H12" s="87" t="n">
         <f aca="false">[3]Apr!$H$1</f>
-        <v>0</v>
+        <v>35838.125</v>
       </c>
       <c r="I12" s="87" t="n">
         <f aca="false">SUM(H10:H12)</f>
-        <v>0</v>
+        <v>43655</v>
       </c>
       <c r="J12" s="87" t="n">
         <f aca="false">[3]Apr!$G$1</f>
-        <v>0</v>
+        <v>7167.625</v>
       </c>
       <c r="K12" s="87" t="n">
         <f aca="false">SUM(J10:J12)</f>
-        <v>0</v>
+        <v>8731</v>
       </c>
       <c r="L12" s="88"/>
       <c r="M12" s="89" t="n">
@@ -16348,35 +16462,35 @@
       </c>
       <c r="D13" s="86" t="n">
         <f aca="false">[2]May!$H$1</f>
-        <v>0</v>
+        <v>29433.3333333333</v>
       </c>
       <c r="E13" s="87" t="n">
         <f aca="false">SUM(D11:D13)</f>
-        <v>0</v>
+        <v>99699.9999999999</v>
       </c>
       <c r="F13" s="87" t="n">
         <f aca="false">[2]May!$G$1</f>
-        <v>0</v>
+        <v>5886.66666666667</v>
       </c>
       <c r="G13" s="87" t="n">
         <f aca="false">SUM(F11:F13)</f>
-        <v>0</v>
+        <v>19940</v>
       </c>
       <c r="H13" s="87" t="n">
         <f aca="false">[3]May!$H$1</f>
-        <v>0</v>
+        <v>5765</v>
       </c>
       <c r="I13" s="87" t="n">
         <f aca="false">SUM(H11:H13)</f>
-        <v>0</v>
+        <v>45748.9583333333</v>
       </c>
       <c r="J13" s="87" t="n">
         <f aca="false">[3]May!$G$1</f>
-        <v>0</v>
+        <v>1153</v>
       </c>
       <c r="K13" s="87" t="n">
         <f aca="false">SUM(J11:J13)</f>
-        <v>0</v>
+        <v>9149.79166666667</v>
       </c>
       <c r="L13" s="88"/>
       <c r="M13" s="89" t="n">
@@ -16397,35 +16511,35 @@
       </c>
       <c r="D14" s="86" t="n">
         <f aca="false">[2]Jun!$H$1</f>
-        <v>0</v>
+        <v>27333.3333333333</v>
       </c>
       <c r="E14" s="87" t="n">
         <f aca="false">SUM(D12:D14)</f>
-        <v>0</v>
+        <v>98899.9999999999</v>
       </c>
       <c r="F14" s="87" t="n">
         <f aca="false">[2]Jun!$G$1</f>
-        <v>0</v>
+        <v>5466.66666666667</v>
       </c>
       <c r="G14" s="87" t="n">
         <f aca="false">SUM(F12:F14)</f>
-        <v>0</v>
+        <v>19780</v>
       </c>
       <c r="H14" s="87" t="n">
         <f aca="false">[3]Jun!$H$1</f>
-        <v>0</v>
+        <v>7876.25</v>
       </c>
       <c r="I14" s="87" t="n">
         <f aca="false">SUM(H12:H14)</f>
-        <v>0</v>
+        <v>49479.375</v>
       </c>
       <c r="J14" s="87" t="n">
         <f aca="false">[3]Jun!$G$1</f>
-        <v>0</v>
+        <v>1575.25</v>
       </c>
       <c r="K14" s="87" t="n">
         <f aca="false">SUM(J12:J14)</f>
-        <v>0</v>
+        <v>9895.875</v>
       </c>
       <c r="L14" s="88"/>
       <c r="M14" s="89" t="n">
@@ -16446,35 +16560,35 @@
       </c>
       <c r="D15" s="86" t="n">
         <f aca="false">[2]Jul!$H$1</f>
-        <v>0</v>
+        <v>29533.3333333333</v>
       </c>
       <c r="E15" s="87" t="n">
         <f aca="false">SUM(D13:D15)</f>
-        <v>0</v>
+        <v>86299.9999999999</v>
       </c>
       <c r="F15" s="87" t="n">
         <f aca="false">[2]Jul!$G$1</f>
-        <v>0</v>
+        <v>5906.66666666667</v>
       </c>
       <c r="G15" s="87" t="n">
         <f aca="false">SUM(F13:F15)</f>
-        <v>0</v>
+        <v>17260</v>
       </c>
       <c r="H15" s="87" t="n">
         <f aca="false">[3]Jul!$H$1</f>
-        <v>0</v>
+        <v>3759.375</v>
       </c>
       <c r="I15" s="87" t="n">
         <f aca="false">SUM(H13:H15)</f>
-        <v>0</v>
+        <v>17400.625</v>
       </c>
       <c r="J15" s="87" t="n">
         <f aca="false">[3]Jul!$G$1</f>
-        <v>0</v>
+        <v>751.875</v>
       </c>
       <c r="K15" s="87" t="n">
         <f aca="false">SUM(J13:J15)</f>
-        <v>0</v>
+        <v>3480.125</v>
       </c>
       <c r="L15" s="88"/>
       <c r="M15" s="89" t="n">
@@ -16495,35 +16609,35 @@
       </c>
       <c r="D16" s="86" t="n">
         <f aca="false">[2]Aug!$H$1</f>
-        <v>0</v>
+        <v>28633.3333333333</v>
       </c>
       <c r="E16" s="87" t="n">
         <f aca="false">SUM(D14:D16)</f>
-        <v>0</v>
+        <v>85499.9999999999</v>
       </c>
       <c r="F16" s="87" t="n">
         <f aca="false">[2]Aug!$G$1</f>
-        <v>0</v>
+        <v>5726.66666666667</v>
       </c>
       <c r="G16" s="87" t="n">
         <f aca="false">SUM(F14:F16)</f>
-        <v>0</v>
+        <v>17100</v>
       </c>
       <c r="H16" s="87" t="n">
         <f aca="false">[3]Aug!$H$1</f>
-        <v>0</v>
+        <v>3663.75</v>
       </c>
       <c r="I16" s="87" t="n">
         <f aca="false">SUM(H14:H16)</f>
-        <v>0</v>
+        <v>15299.375</v>
       </c>
       <c r="J16" s="87" t="n">
         <f aca="false">[3]Aug!$G$1</f>
-        <v>0</v>
+        <v>732.75</v>
       </c>
       <c r="K16" s="87" t="n">
         <f aca="false">SUM(J14:J16)</f>
-        <v>0</v>
+        <v>3059.875</v>
       </c>
       <c r="L16" s="88"/>
       <c r="M16" s="89" t="n">
@@ -16544,35 +16658,35 @@
       </c>
       <c r="D17" s="86" t="n">
         <f aca="false">[2]Sep!$H$1</f>
-        <v>0</v>
+        <v>26133.3333333333</v>
       </c>
       <c r="E17" s="87" t="n">
         <f aca="false">SUM(D15:D17)</f>
-        <v>0</v>
+        <v>84299.9999999999</v>
       </c>
       <c r="F17" s="87" t="n">
         <f aca="false">[2]Sep!$G$1</f>
-        <v>0</v>
+        <v>5226.66666666667</v>
       </c>
       <c r="G17" s="87" t="n">
         <f aca="false">SUM(F15:F17)</f>
-        <v>0</v>
+        <v>16860</v>
       </c>
       <c r="H17" s="87" t="n">
         <f aca="false">[3]Sep!$H$1</f>
-        <v>0</v>
+        <v>3105.41666666667</v>
       </c>
       <c r="I17" s="87" t="n">
         <f aca="false">SUM(H15:H17)</f>
-        <v>0</v>
+        <v>10528.5416666667</v>
       </c>
       <c r="J17" s="87" t="n">
         <f aca="false">[3]Sep!$G$1</f>
-        <v>0</v>
+        <v>621.083333333333</v>
       </c>
       <c r="K17" s="87" t="n">
         <f aca="false">SUM(J15:J17)</f>
-        <v>0</v>
+        <v>2105.70833333333</v>
       </c>
       <c r="L17" s="88"/>
       <c r="M17" s="89" t="n">
@@ -16593,35 +16707,35 @@
       </c>
       <c r="D18" s="86" t="n">
         <f aca="false">S04Y2!$H$1</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="E18" s="87" t="n">
         <f aca="false">SUM(D16:D18)</f>
-        <v>0</v>
+        <v>57766.6666666666</v>
       </c>
       <c r="F18" s="87" t="n">
         <f aca="false">S04Y2!$G$1</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G18" s="87" t="n">
         <f aca="false">SUM(F16:F18)</f>
-        <v>0</v>
+        <v>11553.3333333333</v>
       </c>
       <c r="H18" s="87" t="n">
         <f aca="false">P04Y2!$H$1</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I18" s="87" t="n">
         <f aca="false">SUM(H16:H18)</f>
-        <v>0</v>
+        <v>6969.16666666667</v>
       </c>
       <c r="J18" s="87" t="n">
         <f aca="false">P04Y2!$G$1</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K18" s="87" t="n">
         <f aca="false">SUM(J16:J18)</f>
-        <v>0</v>
+        <v>1393.83333333333</v>
       </c>
       <c r="L18" s="88"/>
       <c r="M18" s="89" t="n">
@@ -16642,35 +16756,35 @@
       </c>
       <c r="D19" s="86" t="n">
         <f aca="false">S05Y2!$H$1</f>
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="E19" s="87" t="n">
         <f aca="false">SUM(D17:D19)</f>
-        <v>0</v>
+        <v>30633.3333333333</v>
       </c>
       <c r="F19" s="87" t="n">
         <f aca="false">S05Y2!$G$1</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G19" s="87" t="n">
         <f aca="false">SUM(F17:F19)</f>
-        <v>0</v>
+        <v>6126.66666666667</v>
       </c>
       <c r="H19" s="87" t="n">
         <f aca="false">P05Y2!$H$1</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I19" s="87" t="n">
         <f aca="false">SUM(H17:H19)</f>
-        <v>0</v>
+        <v>3605.41666666667</v>
       </c>
       <c r="J19" s="87" t="n">
         <f aca="false">P05Y2!$G$1</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K19" s="87" t="n">
         <f aca="false">SUM(J17:J19)</f>
-        <v>0</v>
+        <v>721.083333333333</v>
       </c>
       <c r="L19" s="88"/>
       <c r="M19" s="89" t="n">
@@ -16736,15 +16850,15 @@
       <c r="E1" s="104"/>
       <c r="F1" s="105" t="n">
         <f aca="false">SUM(F5:F500)</f>
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="G1" s="105" t="n">
         <f aca="false">SUM(G5:G500)</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="H1" s="105" t="n">
         <f aca="false">SUM(H5:H500)</f>
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="2" s="106" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16798,13 +16912,25 @@
       <c r="H4" s="108"/>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G5" s="99" t="str">
+      <c r="A5" s="98" t="n">
+        <v>45883</v>
+      </c>
+      <c r="B5" s="99" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="100" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="99" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G5" s="99" t="n">
         <f aca="false">IF(G$4&gt;0,(IF(F5&lt;&gt;0,F5*G$4/100," ")),IF(F5&lt;&gt;0,F5*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H5" s="99" t="str">
+        <v>800</v>
+      </c>
+      <c r="H5" s="99" t="n">
         <f aca="false">IF((F5&lt;&gt;0),F5-G5," ")</f>
-        <v> </v>
+        <v>4000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18765,7 +18891,7 @@
     </row>
     <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="98" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -18820,15 +18946,15 @@
       <c r="E1" s="104"/>
       <c r="F1" s="105" t="n">
         <f aca="false">SUM(F5:F500)</f>
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="G1" s="105" t="n">
         <f aca="false">SUM(G5:G500)</f>
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H1" s="105" t="n">
         <f aca="false">SUM(H5:H500)</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="2" s="106" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18882,13 +19008,25 @@
       <c r="H4" s="108"/>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G5" s="99" t="str">
+      <c r="A5" s="98" t="n">
+        <v>45918</v>
+      </c>
+      <c r="B5" s="99" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="100" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="99" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G5" s="99" t="n">
         <f aca="false">IF(G$4&gt;0,(IF(F5&lt;&gt;0,F5*G$4/100," ")),IF(F5&lt;&gt;0,F5*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H5" s="99" t="str">
+        <v>400</v>
+      </c>
+      <c r="H5" s="99" t="n">
         <f aca="false">IF((F5&lt;&gt;0),F5-G5," ")</f>
-        <v> </v>
+        <v>2000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20849,7 +20987,7 @@
     </row>
     <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="98" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -20904,15 +21042,15 @@
       <c r="E1" s="104"/>
       <c r="F1" s="105" t="n">
         <f aca="false">SUM(F5:F500)</f>
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="G1" s="105" t="n">
         <f aca="false">SUM(G5:G500)</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H1" s="105" t="n">
         <f aca="false">SUM(H5:H500)</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="2" s="106" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20966,13 +21104,25 @@
       <c r="H4" s="108"/>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G5" s="99" t="str">
+      <c r="A5" s="98" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B5" s="99" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="100" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="99" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G5" s="99" t="n">
         <f aca="false">IF(G$4&gt;0,(IF(F5&lt;&gt;0,F5*G$4/100," ")),IF(F5&lt;&gt;0,F5*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H5" s="99" t="str">
+        <v>600</v>
+      </c>
+      <c r="H5" s="99" t="n">
         <f aca="false">IF((F5&lt;&gt;0),F5-G5," ")</f>
-        <v> </v>
+        <v>3000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22933,7 +23083,7 @@
     </row>
     <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="98" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/examples/ltd-latest/Vatreturns.xlsx
+++ b/examples/ltd-latest/Vatreturns.xlsx
@@ -15476,7 +15476,7 @@
       </c>
       <c r="F5" s="26"/>
       <c r="G5" s="27" t="n">
-        <v>46691</v>
+        <v>46721</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="14"/>
@@ -15511,7 +15511,7 @@
       <c r="F7" s="31"/>
       <c r="G7" s="32" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!C1:C20)</f>
-        <v>46721</v>
+        <v>46752</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="14"/>
@@ -15548,7 +15548,7 @@
       </c>
       <c r="G9" s="37" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!G1:G20)</f>
-        <v>11553.3333333333</v>
+        <v>6126.66666666667</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="14"/>
@@ -15621,7 +15621,7 @@
       </c>
       <c r="G13" s="37" t="n">
         <f aca="false">G9+G11</f>
-        <v>11553.3333333333</v>
+        <v>6126.66666666667</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="14"/>
@@ -15658,7 +15658,7 @@
       </c>
       <c r="G15" s="37" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!K1:K20)</f>
-        <v>1393.83333333333</v>
+        <v>721.083333333333</v>
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="14"/>
@@ -15693,7 +15693,7 @@
       </c>
       <c r="G17" s="37" t="n">
         <f aca="false">G13-G15</f>
-        <v>10159.5</v>
+        <v>5405.58333333334</v>
       </c>
       <c r="H17" s="13"/>
       <c r="I17" s="14"/>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="G21" s="52" t="n">
         <f aca="false">IF(LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!M1:M20)&gt;0,(LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!E1:E20)+LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!G1:G20)),LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!E1:E20))</f>
-        <v>57766.6666666666</v>
+        <v>30633.3333333333</v>
       </c>
       <c r="H21" s="13"/>
       <c r="I21" s="14"/>
@@ -15781,7 +15781,7 @@
       </c>
       <c r="G23" s="52" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!I1:I20)</f>
-        <v>6969.16666666667</v>
+        <v>3605.41666666667</v>
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="14"/>

--- a/examples/ltd-latest/Vatreturns.xlsx
+++ b/examples/ltd-latest/Vatreturns.xlsx
@@ -18,15 +18,17 @@
     <sheet name="S03Y1" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="S04Y2" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="S05Y2" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="P02Y1" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="P03Y1" sheetId="12" state="visible" r:id="rId14"/>
-    <sheet name="P04Y2" sheetId="13" state="visible" r:id="rId15"/>
-    <sheet name="P05Y2" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="S06Y2" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="P02Y1" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="P03Y1" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="P04Y2" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="P05Y2" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="P06Y2" sheetId="16" state="visible" r:id="rId18"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId17"/>
-    <externalReference r:id="rId18"/>
     <externalReference r:id="rId19"/>
+    <externalReference r:id="rId20"/>
+    <externalReference r:id="rId21"/>
   </externalReferences>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">VATQtr1!$A$1:$I$32</definedName>
@@ -50,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="62">
   <si>
     <t xml:space="preserve">Value  Added  Tax  Return</t>
   </si>
@@ -290,6 +292,9 @@
     <t xml:space="preserve">INV-1302</t>
   </si>
   <si>
+    <t xml:space="preserve">INV-1303</t>
+  </si>
+  <si>
     <t xml:space="preserve">Purchase Date</t>
   </si>
   <si>
@@ -330,6 +335,9 @@
   </si>
   <si>
     <t xml:space="preserve">BT-2605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WS-2606</t>
   </si>
 </sst>
 </file>
@@ -465,18 +473,18 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFCCFFFF"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFCCFFFF"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="1"/>
     </font>
     <font>
@@ -840,12 +848,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="true"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="169" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="true"/>
     </xf>
-    <xf numFmtId="169" fontId="18" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="true"/>
     </xf>
     <xf numFmtId="166" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
@@ -1347,6 +1355,11 @@
             <v>46752</v>
           </cell>
         </row>
+        <row r="40">
+          <cell r="B40">
+            <v>46783</v>
+          </cell>
+        </row>
       </sheetData>
     </sheetDataSet>
   </externalBook>
@@ -1687,10 +1700,10 @@
       <sheetData sheetId="9">
         <row r="1">
           <cell r="G1">
-            <v>1509.5</v>
+            <v>4109.5</v>
           </cell>
           <cell r="H1">
-            <v>7547.5</v>
+            <v>20547.5</v>
           </cell>
         </row>
       </sheetData>
@@ -1717,10 +1730,10 @@
       <sheetData sheetId="12">
         <row r="1">
           <cell r="G1">
-            <v>829.166666666667</v>
+            <v>2229.16666666667</v>
           </cell>
           <cell r="H1">
-            <v>4145.83333333333</v>
+            <v>11145.8333333333</v>
           </cell>
         </row>
       </sheetData>
@@ -2118,7 +2131,7 @@
       </c>
       <c r="G15" s="37" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!K1:K20)</f>
-        <v>3423.875</v>
+        <v>6023.875</v>
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="14"/>
@@ -2137,27 +2150,30 @@
       <c r="G16" s="40"/>
       <c r="H16" s="13"/>
       <c r="I16" s="14"/>
-      <c r="K16" s="42"/>
+      <c r="K16" s="15" t="n">
+        <f aca="false">Vatinterface!B20</f>
+        <v>46752</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="41"/>
-      <c r="B17" s="43" t="str">
+      <c r="B17" s="42" t="str">
         <f aca="false">IF(G17&gt;0,"Net VAT to be PAID to Customs","Net VAT to be RECLIAMED from Customs")</f>
         <v>Net VAT to be PAID to Customs</v>
       </c>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
       <c r="F17" s="36" t="n">
         <v>5</v>
       </c>
       <c r="G17" s="37" t="n">
         <f aca="false">G13-G15</f>
-        <v>13496.125</v>
+        <v>10896.125</v>
       </c>
       <c r="H17" s="13"/>
       <c r="I17" s="14"/>
-      <c r="K17" s="42"/>
+      <c r="K17" s="43"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="44"/>
@@ -2241,7 +2257,7 @@
       </c>
       <c r="G23" s="52" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!I1:I20)</f>
-        <v>17119.375</v>
+        <v>30119.375</v>
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="14"/>
@@ -2392,7 +2408,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G5" type="list">
-      <formula1>$K$2:$K$15</formula1>
+      <formula1>$K$2:$K$16</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -4510,75 +4526,73 @@
   <dimension ref="A1:H201"/>
   <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="118" width="8.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="119" width="19.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="120" width="12.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="121" width="14.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="122" width="5.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="123" width="10.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="123" width="9.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="123" width="10.66"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="9" style="119" width="9.15"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="98" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="99" width="20.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="100" width="12.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="101" width="7.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="99" width="9.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="99" width="8.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="99" width="9.66"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="9" style="102" width="9.15"/>
   </cols>
   <sheetData>
-    <row r="1" s="102" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" s="106" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="103" t="s">
         <v>29</v>
       </c>
       <c r="B1" s="103"/>
       <c r="C1" s="103"/>
-      <c r="D1" s="105" t="s">
+      <c r="D1" s="104" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="105"/>
+      <c r="E1" s="104"/>
       <c r="F1" s="105" t="n">
-        <f aca="false">SUM(F5:F200)</f>
-        <v>720</v>
+        <f aca="false">SUM(F5:F500)</f>
+        <v>1200</v>
       </c>
       <c r="G1" s="105" t="n">
-        <f aca="false">SUM(G5:G200)</f>
-        <v>120</v>
+        <f aca="false">SUM(G5:G500)</f>
+        <v>200</v>
       </c>
       <c r="H1" s="105" t="n">
-        <f aca="false">SUM(H5:H200)</f>
-        <v>600</v>
-      </c>
-    </row>
-    <row r="2" s="127" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">SUM(H5:H500)</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="2" s="106" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="107" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="108" t="str">
-        <f aca="false">IF((H1-SUM(O1:AK1)&lt;&gt;0),"COMPLETE EXPENSE ANALYSIS by inserting expense letter in col F","Supplier")</f>
-        <v>COMPLETE EXPENSE ANALYSIS by inserting expense letter in col F</v>
-      </c>
-      <c r="C2" s="110" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="124" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="125"/>
+        <v>31</v>
+      </c>
+      <c r="B2" s="108" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="109" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="109" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="110"/>
       <c r="F2" s="108" t="s">
-        <v>49</v>
-      </c>
-      <c r="G2" s="126" t="n">
-        <f aca="false">[3]OpeningCreditors!$G$2</f>
+        <v>35</v>
+      </c>
+      <c r="G2" s="111" t="n">
+        <f aca="false">[2]ClosingDebtors!$G$2</f>
         <v>20</v>
       </c>
       <c r="H2" s="108" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" s="128" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" s="112" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="107"/>
-      <c r="B3" s="107"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="125"/>
+      <c r="B3" s="108"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="110"/>
       <c r="F3" s="108"/>
       <c r="G3" s="108" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="H3" s="108"/>
     </row>
@@ -4586,2183 +4600,1989 @@
       <c r="A4" s="107"/>
       <c r="B4" s="107"/>
       <c r="C4" s="107"/>
-      <c r="D4" s="124"/>
-      <c r="E4" s="125"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="110"/>
       <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
+      <c r="G4" s="113" t="n">
+        <f aca="false">[2]ClosingDebtors!$G$4</f>
+        <v>0</v>
+      </c>
       <c r="H4" s="108"/>
     </row>
-    <row r="5" s="119" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="118" t="n">
-        <v>45889</v>
-      </c>
-      <c r="B5" s="122" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5" s="122"/>
-      <c r="F5" s="130" t="n">
-        <v>720</v>
-      </c>
-      <c r="G5" s="123" t="n">
-        <f aca="false">IF(F5&lt;&gt;0,F5*G$2/(100+G$2)," ")</f>
-        <v>120</v>
-      </c>
-      <c r="H5" s="123" t="n">
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="98" t="n">
+        <v>46367</v>
+      </c>
+      <c r="B5" s="99" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="100" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="99" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G5" s="99" t="n">
+        <f aca="false">IF(G$4&gt;0,(IF(F5&lt;&gt;0,F5*G$4/100," ")),IF(F5&lt;&gt;0,F5*G$2/(100+G$2)," "))</f>
+        <v>200</v>
+      </c>
+      <c r="H5" s="99" t="n">
         <f aca="false">IF((F5&lt;&gt;0),F5-G5," ")</f>
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E6" s="119"/>
-      <c r="G6" s="123" t="str">
-        <f aca="false">IF(F6&lt;&gt;0,F6*G$2/(100+G$2)," ")</f>
-        <v> </v>
-      </c>
-      <c r="H6" s="123" t="str">
+      <c r="G6" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F6&lt;&gt;0,F6*G$4/100," ")),IF(F6&lt;&gt;0,F6*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H6" s="99" t="str">
         <f aca="false">IF((F6&lt;&gt;0),F6-G6," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E7" s="119"/>
-      <c r="G7" s="123" t="str">
-        <f aca="false">IF(F7&lt;&gt;0,F7*G$2/(100+G$2)," ")</f>
-        <v> </v>
-      </c>
-      <c r="H7" s="123" t="str">
+      <c r="G7" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F7&lt;&gt;0,F7*G$4/100," ")),IF(F7&lt;&gt;0,F7*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H7" s="99" t="str">
         <f aca="false">IF((F7&lt;&gt;0),F7-G7," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E8" s="119"/>
-      <c r="G8" s="123" t="str">
-        <f aca="false">IF(F8&lt;&gt;0,F8*G$2/(100+G$2)," ")</f>
-        <v> </v>
-      </c>
-      <c r="H8" s="123" t="str">
+      <c r="G8" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F8&lt;&gt;0,F8*G$4/100," ")),IF(F8&lt;&gt;0,F8*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H8" s="99" t="str">
         <f aca="false">IF((F8&lt;&gt;0),F8-G8," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E9" s="119"/>
-      <c r="G9" s="123" t="str">
-        <f aca="false">IF(F9&lt;&gt;0,F9*G$2/(100+G$2)," ")</f>
-        <v> </v>
-      </c>
-      <c r="H9" s="123" t="str">
+      <c r="G9" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F9&lt;&gt;0,F9*G$4/100," ")),IF(F9&lt;&gt;0,F9*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H9" s="99" t="str">
         <f aca="false">IF((F9&lt;&gt;0),F9-G9," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E10" s="119"/>
-      <c r="G10" s="123" t="str">
-        <f aca="false">IF(F10&lt;&gt;0,F10*G$2/(100+G$2)," ")</f>
-        <v> </v>
-      </c>
-      <c r="H10" s="123" t="str">
+      <c r="G10" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F10&lt;&gt;0,F10*G$4/100," ")),IF(F10&lt;&gt;0,F10*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H10" s="99" t="str">
         <f aca="false">IF((F10&lt;&gt;0),F10-G10," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E11" s="119"/>
-      <c r="G11" s="123" t="str">
-        <f aca="false">IF(F11&lt;&gt;0,F11*G$2/(100+G$2)," ")</f>
-        <v> </v>
-      </c>
-      <c r="H11" s="123" t="str">
+      <c r="G11" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F11&lt;&gt;0,F11*G$4/100," ")),IF(F11&lt;&gt;0,F11*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H11" s="99" t="str">
         <f aca="false">IF((F11&lt;&gt;0),F11-G11," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E12" s="119"/>
-      <c r="G12" s="123" t="str">
-        <f aca="false">IF(F12&lt;&gt;0,F12*G$2/(100+G$2)," ")</f>
-        <v> </v>
-      </c>
-      <c r="H12" s="123" t="str">
+      <c r="G12" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F12&lt;&gt;0,F12*G$4/100," ")),IF(F12&lt;&gt;0,F12*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H12" s="99" t="str">
         <f aca="false">IF((F12&lt;&gt;0),F12-G12," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E13" s="119"/>
-      <c r="G13" s="123" t="str">
-        <f aca="false">IF(F13&lt;&gt;0,F13*G$2/(100+G$2)," ")</f>
-        <v> </v>
-      </c>
-      <c r="H13" s="123" t="str">
+      <c r="G13" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F13&lt;&gt;0,F13*G$4/100," ")),IF(F13&lt;&gt;0,F13*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H13" s="99" t="str">
         <f aca="false">IF((F13&lt;&gt;0),F13-G13," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E14" s="119"/>
-      <c r="G14" s="123" t="str">
-        <f aca="false">IF(F14&lt;&gt;0,F14*G$2/(100+G$2)," ")</f>
-        <v> </v>
-      </c>
-      <c r="H14" s="123" t="str">
+      <c r="G14" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F14&lt;&gt;0,F14*G$4/100," ")),IF(F14&lt;&gt;0,F14*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H14" s="99" t="str">
         <f aca="false">IF((F14&lt;&gt;0),F14-G14," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E15" s="119"/>
-      <c r="G15" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F15&lt;&gt;0,F15*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H15" s="123" t="str">
+      <c r="G15" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F15&lt;&gt;0,F15*G$4/100," ")),IF(F15&lt;&gt;0,F15*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H15" s="99" t="str">
         <f aca="false">IF((F15&lt;&gt;0),F15-G15," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E16" s="119"/>
-      <c r="G16" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F16&lt;&gt;0,F16*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H16" s="123" t="str">
+      <c r="G16" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F16&lt;&gt;0,F16*G$4/100," ")),IF(F16&lt;&gt;0,F16*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H16" s="99" t="str">
         <f aca="false">IF((F16&lt;&gt;0),F16-G16," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E17" s="119"/>
-      <c r="G17" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F17&lt;&gt;0,F17*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H17" s="123" t="str">
+      <c r="G17" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F17&lt;&gt;0,F17*G$4/100," ")),IF(F17&lt;&gt;0,F17*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H17" s="99" t="str">
         <f aca="false">IF((F17&lt;&gt;0),F17-G17," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="119"/>
-      <c r="G18" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F18&lt;&gt;0,F18*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H18" s="123" t="str">
+      <c r="G18" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F18&lt;&gt;0,F18*G$4/100," ")),IF(F18&lt;&gt;0,F18*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H18" s="99" t="str">
         <f aca="false">IF((F18&lt;&gt;0),F18-G18," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="119"/>
-      <c r="G19" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F19&lt;&gt;0,F19*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H19" s="123" t="str">
+      <c r="G19" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F19&lt;&gt;0,F19*G$4/100," ")),IF(F19&lt;&gt;0,F19*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H19" s="99" t="str">
         <f aca="false">IF((F19&lt;&gt;0),F19-G19," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E20" s="119"/>
-      <c r="G20" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F20&lt;&gt;0,F20*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H20" s="123" t="str">
+      <c r="G20" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F20&lt;&gt;0,F20*G$4/100," ")),IF(F20&lt;&gt;0,F20*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H20" s="99" t="str">
         <f aca="false">IF((F20&lt;&gt;0),F20-G20," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E21" s="119"/>
-      <c r="G21" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F21&lt;&gt;0,F21*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H21" s="123" t="str">
+      <c r="G21" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F21&lt;&gt;0,F21*G$4/100," ")),IF(F21&lt;&gt;0,F21*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H21" s="99" t="str">
         <f aca="false">IF((F21&lt;&gt;0),F21-G21," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D22" s="119"/>
-      <c r="E22" s="119"/>
-      <c r="G22" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F22&lt;&gt;0,F22*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H22" s="123" t="str">
+      <c r="G22" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F22&lt;&gt;0,F22*G$4/100," ")),IF(F22&lt;&gt;0,F22*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H22" s="99" t="str">
         <f aca="false">IF((F22&lt;&gt;0),F22-G22," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D23" s="131"/>
-      <c r="E23" s="119"/>
-      <c r="G23" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F23&lt;&gt;0,F23*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H23" s="123" t="str">
+      <c r="G23" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F23&lt;&gt;0,F23*G$4/100," ")),IF(F23&lt;&gt;0,F23*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H23" s="99" t="str">
         <f aca="false">IF((F23&lt;&gt;0),F23-G23," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E24" s="119"/>
-      <c r="G24" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F24&lt;&gt;0,F24*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H24" s="123" t="str">
+      <c r="G24" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F24&lt;&gt;0,F24*G$4/100," ")),IF(F24&lt;&gt;0,F24*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H24" s="99" t="str">
         <f aca="false">IF((F24&lt;&gt;0),F24-G24," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E25" s="119"/>
-      <c r="G25" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F25&lt;&gt;0,F25*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H25" s="123" t="str">
+      <c r="G25" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F25&lt;&gt;0,F25*G$4/100," ")),IF(F25&lt;&gt;0,F25*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H25" s="99" t="str">
         <f aca="false">IF((F25&lt;&gt;0),F25-G25," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E26" s="119"/>
-      <c r="G26" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F26&lt;&gt;0,F26*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H26" s="123" t="str">
+      <c r="G26" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F26&lt;&gt;0,F26*G$4/100," ")),IF(F26&lt;&gt;0,F26*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H26" s="99" t="str">
         <f aca="false">IF((F26&lt;&gt;0),F26-G26," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E27" s="119"/>
-      <c r="G27" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F27&lt;&gt;0,F27*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H27" s="123" t="str">
+      <c r="G27" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F27&lt;&gt;0,F27*G$4/100," ")),IF(F27&lt;&gt;0,F27*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H27" s="99" t="str">
         <f aca="false">IF((F27&lt;&gt;0),F27-G27," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E28" s="119"/>
-      <c r="G28" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F28&lt;&gt;0,F28*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H28" s="123" t="str">
+      <c r="G28" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F28&lt;&gt;0,F28*G$4/100," ")),IF(F28&lt;&gt;0,F28*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H28" s="99" t="str">
         <f aca="false">IF((F28&lt;&gt;0),F28-G28," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E29" s="119"/>
-      <c r="G29" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F29&lt;&gt;0,F29*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H29" s="123" t="str">
+      <c r="G29" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F29&lt;&gt;0,F29*G$4/100," ")),IF(F29&lt;&gt;0,F29*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H29" s="99" t="str">
         <f aca="false">IF((F29&lt;&gt;0),F29-G29," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E30" s="119"/>
-      <c r="G30" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F30&lt;&gt;0,F30*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H30" s="123" t="str">
+      <c r="G30" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F30&lt;&gt;0,F30*G$4/100," ")),IF(F30&lt;&gt;0,F30*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H30" s="99" t="str">
         <f aca="false">IF((F30&lt;&gt;0),F30-G30," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E31" s="119"/>
-      <c r="G31" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F31&lt;&gt;0,F31*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H31" s="123" t="str">
+      <c r="G31" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F31&lt;&gt;0,F31*G$4/100," ")),IF(F31&lt;&gt;0,F31*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H31" s="99" t="str">
         <f aca="false">IF((F31&lt;&gt;0),F31-G31," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E32" s="119"/>
-      <c r="G32" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F32&lt;&gt;0,F32*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H32" s="123" t="str">
+      <c r="G32" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F32&lt;&gt;0,F32*G$4/100," ")),IF(F32&lt;&gt;0,F32*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H32" s="99" t="str">
         <f aca="false">IF((F32&lt;&gt;0),F32-G32," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E33" s="119"/>
-      <c r="G33" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F33&lt;&gt;0,F33*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H33" s="123" t="str">
+      <c r="G33" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F33&lt;&gt;0,F33*G$4/100," ")),IF(F33&lt;&gt;0,F33*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H33" s="99" t="str">
         <f aca="false">IF((F33&lt;&gt;0),F33-G33," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E34" s="119"/>
-      <c r="G34" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F34&lt;&gt;0,F34*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H34" s="123" t="str">
+      <c r="G34" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F34&lt;&gt;0,F34*G$4/100," ")),IF(F34&lt;&gt;0,F34*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H34" s="99" t="str">
         <f aca="false">IF((F34&lt;&gt;0),F34-G34," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E35" s="119"/>
-      <c r="G35" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F35&lt;&gt;0,F35*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H35" s="123" t="str">
+      <c r="G35" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F35&lt;&gt;0,F35*G$4/100," ")),IF(F35&lt;&gt;0,F35*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H35" s="99" t="str">
         <f aca="false">IF((F35&lt;&gt;0),F35-G35," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E36" s="119"/>
-      <c r="G36" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F36&lt;&gt;0,F36*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H36" s="123" t="str">
+      <c r="G36" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F36&lt;&gt;0,F36*G$4/100," ")),IF(F36&lt;&gt;0,F36*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H36" s="99" t="str">
         <f aca="false">IF((F36&lt;&gt;0),F36-G36," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E37" s="119"/>
-      <c r="G37" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F37&lt;&gt;0,F37*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H37" s="123" t="str">
+      <c r="G37" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F37&lt;&gt;0,F37*G$4/100," ")),IF(F37&lt;&gt;0,F37*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H37" s="99" t="str">
         <f aca="false">IF((F37&lt;&gt;0),F37-G37," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E38" s="119"/>
-      <c r="G38" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F38&lt;&gt;0,F38*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H38" s="123" t="str">
+      <c r="G38" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F38&lt;&gt;0,F38*G$4/100," ")),IF(F38&lt;&gt;0,F38*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H38" s="99" t="str">
         <f aca="false">IF((F38&lt;&gt;0),F38-G38," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E39" s="119"/>
-      <c r="G39" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F39&lt;&gt;0,F39*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H39" s="123" t="str">
+      <c r="G39" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F39&lt;&gt;0,F39*G$4/100," ")),IF(F39&lt;&gt;0,F39*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H39" s="99" t="str">
         <f aca="false">IF((F39&lt;&gt;0),F39-G39," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E40" s="119"/>
-      <c r="G40" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F40&lt;&gt;0,F40*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H40" s="123" t="str">
+      <c r="G40" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F40&lt;&gt;0,F40*G$4/100," ")),IF(F40&lt;&gt;0,F40*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H40" s="99" t="str">
         <f aca="false">IF((F40&lt;&gt;0),F40-G40," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E41" s="119"/>
-      <c r="G41" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F41&lt;&gt;0,F41*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H41" s="123" t="str">
+      <c r="G41" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F41&lt;&gt;0,F41*G$4/100," ")),IF(F41&lt;&gt;0,F41*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H41" s="99" t="str">
         <f aca="false">IF((F41&lt;&gt;0),F41-G41," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E42" s="119"/>
-      <c r="G42" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F42&lt;&gt;0,F42*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H42" s="123" t="str">
+      <c r="G42" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F42&lt;&gt;0,F42*G$4/100," ")),IF(F42&lt;&gt;0,F42*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H42" s="99" t="str">
         <f aca="false">IF((F42&lt;&gt;0),F42-G42," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E43" s="119"/>
-      <c r="G43" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F43&lt;&gt;0,F43*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H43" s="123" t="str">
+      <c r="G43" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F43&lt;&gt;0,F43*G$4/100," ")),IF(F43&lt;&gt;0,F43*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H43" s="99" t="str">
         <f aca="false">IF((F43&lt;&gt;0),F43-G43," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E44" s="119"/>
-      <c r="G44" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F44&lt;&gt;0,F44*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H44" s="123" t="str">
+      <c r="G44" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F44&lt;&gt;0,F44*G$4/100," ")),IF(F44&lt;&gt;0,F44*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H44" s="99" t="str">
         <f aca="false">IF((F44&lt;&gt;0),F44-G44," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E45" s="119"/>
-      <c r="G45" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F45&lt;&gt;0,F45*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H45" s="123" t="str">
+      <c r="G45" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F45&lt;&gt;0,F45*G$4/100," ")),IF(F45&lt;&gt;0,F45*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H45" s="99" t="str">
         <f aca="false">IF((F45&lt;&gt;0),F45-G45," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E46" s="119"/>
-      <c r="G46" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F46&lt;&gt;0,F46*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H46" s="123" t="str">
+      <c r="G46" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F46&lt;&gt;0,F46*G$4/100," ")),IF(F46&lt;&gt;0,F46*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H46" s="99" t="str">
         <f aca="false">IF((F46&lt;&gt;0),F46-G46," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E47" s="119"/>
-      <c r="G47" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F47&lt;&gt;0,F47*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H47" s="123" t="str">
+      <c r="G47" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F47&lt;&gt;0,F47*G$4/100," ")),IF(F47&lt;&gt;0,F47*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H47" s="99" t="str">
         <f aca="false">IF((F47&lt;&gt;0),F47-G47," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E48" s="119"/>
-      <c r="G48" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F48&lt;&gt;0,F48*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H48" s="123" t="str">
+      <c r="G48" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F48&lt;&gt;0,F48*G$4/100," ")),IF(F48&lt;&gt;0,F48*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H48" s="99" t="str">
         <f aca="false">IF((F48&lt;&gt;0),F48-G48," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E49" s="119"/>
-      <c r="G49" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F49&lt;&gt;0,F49*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H49" s="123" t="str">
+      <c r="G49" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F49&lt;&gt;0,F49*G$4/100," ")),IF(F49&lt;&gt;0,F49*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H49" s="99" t="str">
         <f aca="false">IF((F49&lt;&gt;0),F49-G49," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E50" s="119"/>
-      <c r="G50" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F50&lt;&gt;0,F50*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H50" s="123" t="str">
+      <c r="G50" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F50&lt;&gt;0,F50*G$4/100," ")),IF(F50&lt;&gt;0,F50*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H50" s="99" t="str">
         <f aca="false">IF((F50&lt;&gt;0),F50-G50," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E51" s="119"/>
-      <c r="G51" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F51&lt;&gt;0,F51*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H51" s="123" t="str">
+      <c r="G51" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F51&lt;&gt;0,F51*G$4/100," ")),IF(F51&lt;&gt;0,F51*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H51" s="99" t="str">
         <f aca="false">IF((F51&lt;&gt;0),F51-G51," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E52" s="119"/>
-      <c r="G52" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F52&lt;&gt;0,F52*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H52" s="123" t="str">
+      <c r="G52" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F52&lt;&gt;0,F52*G$4/100," ")),IF(F52&lt;&gt;0,F52*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H52" s="99" t="str">
         <f aca="false">IF((F52&lt;&gt;0),F52-G52," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E53" s="119"/>
-      <c r="G53" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F53&lt;&gt;0,F53*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H53" s="123" t="str">
+      <c r="G53" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F53&lt;&gt;0,F53*G$4/100," ")),IF(F53&lt;&gt;0,F53*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H53" s="99" t="str">
         <f aca="false">IF((F53&lt;&gt;0),F53-G53," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E54" s="119"/>
-      <c r="G54" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F54&lt;&gt;0,F54*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H54" s="123" t="str">
+      <c r="G54" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F54&lt;&gt;0,F54*G$4/100," ")),IF(F54&lt;&gt;0,F54*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H54" s="99" t="str">
         <f aca="false">IF((F54&lt;&gt;0),F54-G54," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E55" s="119"/>
-      <c r="G55" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F55&lt;&gt;0,F55*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H55" s="123" t="str">
+      <c r="G55" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F55&lt;&gt;0,F55*G$4/100," ")),IF(F55&lt;&gt;0,F55*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H55" s="99" t="str">
         <f aca="false">IF((F55&lt;&gt;0),F55-G55," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E56" s="119"/>
-      <c r="G56" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F56&lt;&gt;0,F56*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H56" s="123" t="str">
+      <c r="G56" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F56&lt;&gt;0,F56*G$4/100," ")),IF(F56&lt;&gt;0,F56*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H56" s="99" t="str">
         <f aca="false">IF((F56&lt;&gt;0),F56-G56," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E57" s="119"/>
-      <c r="G57" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F57&lt;&gt;0,F57*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H57" s="123" t="str">
+      <c r="G57" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F57&lt;&gt;0,F57*G$4/100," ")),IF(F57&lt;&gt;0,F57*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H57" s="99" t="str">
         <f aca="false">IF((F57&lt;&gt;0),F57-G57," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E58" s="119"/>
-      <c r="G58" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F58&lt;&gt;0,F58*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H58" s="123" t="str">
+      <c r="G58" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F58&lt;&gt;0,F58*G$4/100," ")),IF(F58&lt;&gt;0,F58*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H58" s="99" t="str">
         <f aca="false">IF((F58&lt;&gt;0),F58-G58," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E59" s="119"/>
-      <c r="G59" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F59&lt;&gt;0,F59*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H59" s="123" t="str">
+      <c r="G59" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F59&lt;&gt;0,F59*G$4/100," ")),IF(F59&lt;&gt;0,F59*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H59" s="99" t="str">
         <f aca="false">IF((F59&lt;&gt;0),F59-G59," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E60" s="119"/>
-      <c r="G60" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F60&lt;&gt;0,F60*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H60" s="123" t="str">
+      <c r="G60" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F60&lt;&gt;0,F60*G$4/100," ")),IF(F60&lt;&gt;0,F60*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H60" s="99" t="str">
         <f aca="false">IF((F60&lt;&gt;0),F60-G60," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E61" s="119"/>
-      <c r="G61" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F61&lt;&gt;0,F61*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H61" s="123" t="str">
+      <c r="G61" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F61&lt;&gt;0,F61*G$4/100," ")),IF(F61&lt;&gt;0,F61*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H61" s="99" t="str">
         <f aca="false">IF((F61&lt;&gt;0),F61-G61," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E62" s="119"/>
-      <c r="G62" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F62&lt;&gt;0,F62*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H62" s="123" t="str">
+      <c r="G62" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F62&lt;&gt;0,F62*G$4/100," ")),IF(F62&lt;&gt;0,F62*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H62" s="99" t="str">
         <f aca="false">IF((F62&lt;&gt;0),F62-G62," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E63" s="119"/>
-      <c r="G63" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F63&lt;&gt;0,F63*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H63" s="123" t="str">
+      <c r="G63" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F63&lt;&gt;0,F63*G$4/100," ")),IF(F63&lt;&gt;0,F63*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H63" s="99" t="str">
         <f aca="false">IF((F63&lt;&gt;0),F63-G63," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E64" s="119"/>
-      <c r="G64" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F64&lt;&gt;0,F64*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H64" s="123" t="str">
+      <c r="G64" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F64&lt;&gt;0,F64*G$4/100," ")),IF(F64&lt;&gt;0,F64*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H64" s="99" t="str">
         <f aca="false">IF((F64&lt;&gt;0),F64-G64," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E65" s="119"/>
-      <c r="G65" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F65&lt;&gt;0,F65*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H65" s="123" t="str">
+      <c r="G65" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F65&lt;&gt;0,F65*G$4/100," ")),IF(F65&lt;&gt;0,F65*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H65" s="99" t="str">
         <f aca="false">IF((F65&lt;&gt;0),F65-G65," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E66" s="119"/>
-      <c r="G66" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F66&lt;&gt;0,F66*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H66" s="123" t="str">
+      <c r="G66" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F66&lt;&gt;0,F66*G$4/100," ")),IF(F66&lt;&gt;0,F66*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H66" s="99" t="str">
         <f aca="false">IF((F66&lt;&gt;0),F66-G66," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E67" s="119"/>
-      <c r="G67" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F67&lt;&gt;0,F67*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H67" s="123" t="str">
+      <c r="G67" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F67&lt;&gt;0,F67*G$4/100," ")),IF(F67&lt;&gt;0,F67*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H67" s="99" t="str">
         <f aca="false">IF((F67&lt;&gt;0),F67-G67," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E68" s="119"/>
-      <c r="G68" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F68&lt;&gt;0,F68*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H68" s="123" t="str">
+      <c r="G68" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F68&lt;&gt;0,F68*G$4/100," ")),IF(F68&lt;&gt;0,F68*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H68" s="99" t="str">
         <f aca="false">IF((F68&lt;&gt;0),F68-G68," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E69" s="119"/>
-      <c r="G69" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F69&lt;&gt;0,F69*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H69" s="123" t="str">
+      <c r="G69" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F69&lt;&gt;0,F69*G$4/100," ")),IF(F69&lt;&gt;0,F69*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H69" s="99" t="str">
         <f aca="false">IF((F69&lt;&gt;0),F69-G69," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E70" s="119"/>
-      <c r="G70" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F70&lt;&gt;0,F70*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H70" s="123" t="str">
+      <c r="G70" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F70&lt;&gt;0,F70*G$4/100," ")),IF(F70&lt;&gt;0,F70*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H70" s="99" t="str">
         <f aca="false">IF((F70&lt;&gt;0),F70-G70," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E71" s="119"/>
-      <c r="G71" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F71&lt;&gt;0,F71*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H71" s="123" t="str">
+      <c r="G71" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F71&lt;&gt;0,F71*G$4/100," ")),IF(F71&lt;&gt;0,F71*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H71" s="99" t="str">
         <f aca="false">IF((F71&lt;&gt;0),F71-G71," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E72" s="119"/>
-      <c r="G72" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F72&lt;&gt;0,F72*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H72" s="123" t="str">
+      <c r="G72" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F72&lt;&gt;0,F72*G$4/100," ")),IF(F72&lt;&gt;0,F72*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H72" s="99" t="str">
         <f aca="false">IF((F72&lt;&gt;0),F72-G72," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E73" s="119"/>
-      <c r="G73" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F73&lt;&gt;0,F73*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H73" s="123" t="str">
+      <c r="G73" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F73&lt;&gt;0,F73*G$4/100," ")),IF(F73&lt;&gt;0,F73*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H73" s="99" t="str">
         <f aca="false">IF((F73&lt;&gt;0),F73-G73," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E74" s="119"/>
-      <c r="G74" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F74&lt;&gt;0,F74*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H74" s="123" t="str">
+      <c r="G74" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F74&lt;&gt;0,F74*G$4/100," ")),IF(F74&lt;&gt;0,F74*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H74" s="99" t="str">
         <f aca="false">IF((F74&lt;&gt;0),F74-G74," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E75" s="119"/>
-      <c r="G75" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F75&lt;&gt;0,F75*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H75" s="123" t="str">
+      <c r="G75" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F75&lt;&gt;0,F75*G$4/100," ")),IF(F75&lt;&gt;0,F75*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H75" s="99" t="str">
         <f aca="false">IF((F75&lt;&gt;0),F75-G75," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E76" s="119"/>
-      <c r="G76" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F76&lt;&gt;0,F76*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H76" s="123" t="str">
+      <c r="G76" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F76&lt;&gt;0,F76*G$4/100," ")),IF(F76&lt;&gt;0,F76*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H76" s="99" t="str">
         <f aca="false">IF((F76&lt;&gt;0),F76-G76," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E77" s="119"/>
-      <c r="G77" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F77&lt;&gt;0,F77*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H77" s="123" t="str">
+      <c r="G77" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F77&lt;&gt;0,F77*G$4/100," ")),IF(F77&lt;&gt;0,F77*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H77" s="99" t="str">
         <f aca="false">IF((F77&lt;&gt;0),F77-G77," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E78" s="119"/>
-      <c r="G78" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F78&lt;&gt;0,F78*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H78" s="123" t="str">
+      <c r="G78" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F78&lt;&gt;0,F78*G$4/100," ")),IF(F78&lt;&gt;0,F78*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H78" s="99" t="str">
         <f aca="false">IF((F78&lt;&gt;0),F78-G78," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E79" s="119"/>
-      <c r="G79" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F79&lt;&gt;0,F79*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H79" s="123" t="str">
+      <c r="G79" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F79&lt;&gt;0,F79*G$4/100," ")),IF(F79&lt;&gt;0,F79*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H79" s="99" t="str">
         <f aca="false">IF((F79&lt;&gt;0),F79-G79," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E80" s="119"/>
-      <c r="G80" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F80&lt;&gt;0,F80*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H80" s="123" t="str">
+      <c r="G80" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F80&lt;&gt;0,F80*G$4/100," ")),IF(F80&lt;&gt;0,F80*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H80" s="99" t="str">
         <f aca="false">IF((F80&lt;&gt;0),F80-G80," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E81" s="119"/>
-      <c r="G81" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F81&lt;&gt;0,F81*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H81" s="123" t="str">
+      <c r="G81" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F81&lt;&gt;0,F81*G$4/100," ")),IF(F81&lt;&gt;0,F81*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H81" s="99" t="str">
         <f aca="false">IF((F81&lt;&gt;0),F81-G81," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E82" s="119"/>
-      <c r="G82" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F82&lt;&gt;0,F82*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H82" s="123" t="str">
+      <c r="G82" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F82&lt;&gt;0,F82*G$4/100," ")),IF(F82&lt;&gt;0,F82*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H82" s="99" t="str">
         <f aca="false">IF((F82&lt;&gt;0),F82-G82," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E83" s="119"/>
-      <c r="G83" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F83&lt;&gt;0,F83*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H83" s="123" t="str">
+      <c r="G83" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F83&lt;&gt;0,F83*G$4/100," ")),IF(F83&lt;&gt;0,F83*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H83" s="99" t="str">
         <f aca="false">IF((F83&lt;&gt;0),F83-G83," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E84" s="119"/>
-      <c r="G84" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F84&lt;&gt;0,F84*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H84" s="123" t="str">
+      <c r="G84" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F84&lt;&gt;0,F84*G$4/100," ")),IF(F84&lt;&gt;0,F84*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H84" s="99" t="str">
         <f aca="false">IF((F84&lt;&gt;0),F84-G84," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E85" s="119"/>
-      <c r="G85" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F85&lt;&gt;0,F85*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H85" s="123" t="str">
+      <c r="G85" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F85&lt;&gt;0,F85*G$4/100," ")),IF(F85&lt;&gt;0,F85*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H85" s="99" t="str">
         <f aca="false">IF((F85&lt;&gt;0),F85-G85," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E86" s="119"/>
-      <c r="G86" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F86&lt;&gt;0,F86*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H86" s="123" t="str">
+      <c r="G86" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F86&lt;&gt;0,F86*G$4/100," ")),IF(F86&lt;&gt;0,F86*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H86" s="99" t="str">
         <f aca="false">IF((F86&lt;&gt;0),F86-G86," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E87" s="119"/>
-      <c r="G87" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F87&lt;&gt;0,F87*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H87" s="123" t="str">
+      <c r="G87" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F87&lt;&gt;0,F87*G$4/100," ")),IF(F87&lt;&gt;0,F87*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H87" s="99" t="str">
         <f aca="false">IF((F87&lt;&gt;0),F87-G87," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E88" s="119"/>
-      <c r="G88" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F88&lt;&gt;0,F88*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H88" s="123" t="str">
+      <c r="G88" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F88&lt;&gt;0,F88*G$4/100," ")),IF(F88&lt;&gt;0,F88*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H88" s="99" t="str">
         <f aca="false">IF((F88&lt;&gt;0),F88-G88," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E89" s="119"/>
-      <c r="G89" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F89&lt;&gt;0,F89*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H89" s="123" t="str">
+      <c r="G89" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F89&lt;&gt;0,F89*G$4/100," ")),IF(F89&lt;&gt;0,F89*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H89" s="99" t="str">
         <f aca="false">IF((F89&lt;&gt;0),F89-G89," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E90" s="119"/>
-      <c r="G90" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F90&lt;&gt;0,F90*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H90" s="123" t="str">
+      <c r="G90" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F90&lt;&gt;0,F90*G$4/100," ")),IF(F90&lt;&gt;0,F90*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H90" s="99" t="str">
         <f aca="false">IF((F90&lt;&gt;0),F90-G90," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E91" s="119"/>
-      <c r="G91" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F91&lt;&gt;0,F91*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H91" s="123" t="str">
+      <c r="G91" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F91&lt;&gt;0,F91*G$4/100," ")),IF(F91&lt;&gt;0,F91*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H91" s="99" t="str">
         <f aca="false">IF((F91&lt;&gt;0),F91-G91," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E92" s="119"/>
-      <c r="G92" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F92&lt;&gt;0,F92*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H92" s="123" t="str">
+      <c r="G92" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F92&lt;&gt;0,F92*G$4/100," ")),IF(F92&lt;&gt;0,F92*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H92" s="99" t="str">
         <f aca="false">IF((F92&lt;&gt;0),F92-G92," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E93" s="119"/>
-      <c r="G93" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F93&lt;&gt;0,F93*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H93" s="123" t="str">
+      <c r="G93" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F93&lt;&gt;0,F93*G$4/100," ")),IF(F93&lt;&gt;0,F93*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H93" s="99" t="str">
         <f aca="false">IF((F93&lt;&gt;0),F93-G93," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E94" s="119"/>
-      <c r="G94" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F94&lt;&gt;0,F94*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H94" s="123" t="str">
+      <c r="G94" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F94&lt;&gt;0,F94*G$4/100," ")),IF(F94&lt;&gt;0,F94*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H94" s="99" t="str">
         <f aca="false">IF((F94&lt;&gt;0),F94-G94," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E95" s="119"/>
-      <c r="G95" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F95&lt;&gt;0,F95*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H95" s="123" t="str">
+      <c r="G95" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F95&lt;&gt;0,F95*G$4/100," ")),IF(F95&lt;&gt;0,F95*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H95" s="99" t="str">
         <f aca="false">IF((F95&lt;&gt;0),F95-G95," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E96" s="119"/>
-      <c r="G96" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F96&lt;&gt;0,F96*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H96" s="123" t="str">
+      <c r="G96" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F96&lt;&gt;0,F96*G$4/100," ")),IF(F96&lt;&gt;0,F96*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H96" s="99" t="str">
         <f aca="false">IF((F96&lt;&gt;0),F96-G96," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E97" s="119"/>
-      <c r="G97" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F97&lt;&gt;0,F97*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H97" s="123" t="str">
+      <c r="G97" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F97&lt;&gt;0,F97*G$4/100," ")),IF(F97&lt;&gt;0,F97*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H97" s="99" t="str">
         <f aca="false">IF((F97&lt;&gt;0),F97-G97," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E98" s="119"/>
-      <c r="G98" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F98&lt;&gt;0,F98*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H98" s="123" t="str">
+      <c r="G98" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F98&lt;&gt;0,F98*G$4/100," ")),IF(F98&lt;&gt;0,F98*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H98" s="99" t="str">
         <f aca="false">IF((F98&lt;&gt;0),F98-G98," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E99" s="119"/>
-      <c r="G99" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F99&lt;&gt;0,F99*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H99" s="123" t="str">
+      <c r="G99" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F99&lt;&gt;0,F99*G$4/100," ")),IF(F99&lt;&gt;0,F99*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H99" s="99" t="str">
         <f aca="false">IF((F99&lt;&gt;0),F99-G99," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E100" s="119"/>
-      <c r="G100" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F100&lt;&gt;0,F100*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H100" s="123" t="str">
+      <c r="G100" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F100&lt;&gt;0,F100*G$4/100," ")),IF(F100&lt;&gt;0,F100*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H100" s="99" t="str">
         <f aca="false">IF((F100&lt;&gt;0),F100-G100," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E101" s="119"/>
-      <c r="G101" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F101&lt;&gt;0,F101*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H101" s="123" t="str">
+      <c r="G101" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F101&lt;&gt;0,F101*G$4/100," ")),IF(F101&lt;&gt;0,F101*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H101" s="99" t="str">
         <f aca="false">IF((F101&lt;&gt;0),F101-G101," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E102" s="119"/>
-      <c r="G102" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F102&lt;&gt;0,F102*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H102" s="123" t="str">
+      <c r="G102" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F102&lt;&gt;0,F102*G$4/100," ")),IF(F102&lt;&gt;0,F102*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H102" s="99" t="str">
         <f aca="false">IF((F102&lt;&gt;0),F102-G102," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E103" s="119"/>
-      <c r="G103" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F103&lt;&gt;0,F103*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H103" s="123" t="str">
+      <c r="G103" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F103&lt;&gt;0,F103*G$4/100," ")),IF(F103&lt;&gt;0,F103*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H103" s="99" t="str">
         <f aca="false">IF((F103&lt;&gt;0),F103-G103," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E104" s="119"/>
-      <c r="G104" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F104&lt;&gt;0,F104*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H104" s="123" t="str">
+      <c r="G104" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F104&lt;&gt;0,F104*G$4/100," ")),IF(F104&lt;&gt;0,F104*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H104" s="99" t="str">
         <f aca="false">IF((F104&lt;&gt;0),F104-G104," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E105" s="119"/>
-      <c r="G105" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F105&lt;&gt;0,F105*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H105" s="123" t="str">
+      <c r="G105" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F105&lt;&gt;0,F105*G$4/100," ")),IF(F105&lt;&gt;0,F105*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H105" s="99" t="str">
         <f aca="false">IF((F105&lt;&gt;0),F105-G105," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E106" s="119"/>
-      <c r="G106" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F106&lt;&gt;0,F106*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H106" s="123" t="str">
+      <c r="G106" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F106&lt;&gt;0,F106*G$4/100," ")),IF(F106&lt;&gt;0,F106*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H106" s="99" t="str">
         <f aca="false">IF((F106&lt;&gt;0),F106-G106," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E107" s="119"/>
-      <c r="G107" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F107&lt;&gt;0,F107*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H107" s="123" t="str">
+      <c r="G107" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F107&lt;&gt;0,F107*G$4/100," ")),IF(F107&lt;&gt;0,F107*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H107" s="99" t="str">
         <f aca="false">IF((F107&lt;&gt;0),F107-G107," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E108" s="119"/>
-      <c r="G108" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F108&lt;&gt;0,F108*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H108" s="123" t="str">
+      <c r="G108" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F108&lt;&gt;0,F108*G$4/100," ")),IF(F108&lt;&gt;0,F108*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H108" s="99" t="str">
         <f aca="false">IF((F108&lt;&gt;0),F108-G108," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E109" s="119"/>
-      <c r="G109" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F109&lt;&gt;0,F109*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H109" s="123" t="str">
+      <c r="G109" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F109&lt;&gt;0,F109*G$4/100," ")),IF(F109&lt;&gt;0,F109*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H109" s="99" t="str">
         <f aca="false">IF((F109&lt;&gt;0),F109-G109," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E110" s="119"/>
-      <c r="G110" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F110&lt;&gt;0,F110*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H110" s="123" t="str">
+      <c r="G110" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F110&lt;&gt;0,F110*G$4/100," ")),IF(F110&lt;&gt;0,F110*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H110" s="99" t="str">
         <f aca="false">IF((F110&lt;&gt;0),F110-G110," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E111" s="119"/>
-      <c r="G111" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F111&lt;&gt;0,F111*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H111" s="123" t="str">
+      <c r="G111" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F111&lt;&gt;0,F111*G$4/100," ")),IF(F111&lt;&gt;0,F111*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H111" s="99" t="str">
         <f aca="false">IF((F111&lt;&gt;0),F111-G111," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E112" s="119"/>
-      <c r="G112" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F112&lt;&gt;0,F112*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H112" s="123" t="str">
+      <c r="G112" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F112&lt;&gt;0,F112*G$4/100," ")),IF(F112&lt;&gt;0,F112*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H112" s="99" t="str">
         <f aca="false">IF((F112&lt;&gt;0),F112-G112," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E113" s="119"/>
-      <c r="G113" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F113&lt;&gt;0,F113*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H113" s="123" t="str">
+      <c r="G113" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F113&lt;&gt;0,F113*G$4/100," ")),IF(F113&lt;&gt;0,F113*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H113" s="99" t="str">
         <f aca="false">IF((F113&lt;&gt;0),F113-G113," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E114" s="119"/>
-      <c r="G114" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F114&lt;&gt;0,F114*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H114" s="123" t="str">
+      <c r="G114" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F114&lt;&gt;0,F114*G$4/100," ")),IF(F114&lt;&gt;0,F114*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H114" s="99" t="str">
         <f aca="false">IF((F114&lt;&gt;0),F114-G114," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E115" s="119"/>
-      <c r="G115" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F115&lt;&gt;0,F115*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H115" s="123" t="str">
+      <c r="G115" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F115&lt;&gt;0,F115*G$4/100," ")),IF(F115&lt;&gt;0,F115*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H115" s="99" t="str">
         <f aca="false">IF((F115&lt;&gt;0),F115-G115," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E116" s="119"/>
-      <c r="G116" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F116&lt;&gt;0,F116*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H116" s="123" t="str">
+      <c r="G116" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F116&lt;&gt;0,F116*G$4/100," ")),IF(F116&lt;&gt;0,F116*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H116" s="99" t="str">
         <f aca="false">IF((F116&lt;&gt;0),F116-G116," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E117" s="119"/>
-      <c r="G117" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F117&lt;&gt;0,F117*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H117" s="123" t="str">
+      <c r="G117" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F117&lt;&gt;0,F117*G$4/100," ")),IF(F117&lt;&gt;0,F117*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H117" s="99" t="str">
         <f aca="false">IF((F117&lt;&gt;0),F117-G117," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E118" s="119"/>
-      <c r="G118" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F118&lt;&gt;0,F118*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H118" s="123" t="str">
+      <c r="G118" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F118&lt;&gt;0,F118*G$4/100," ")),IF(F118&lt;&gt;0,F118*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H118" s="99" t="str">
         <f aca="false">IF((F118&lt;&gt;0),F118-G118," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E119" s="119"/>
-      <c r="G119" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F119&lt;&gt;0,F119*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H119" s="123" t="str">
+      <c r="G119" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F119&lt;&gt;0,F119*G$4/100," ")),IF(F119&lt;&gt;0,F119*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H119" s="99" t="str">
         <f aca="false">IF((F119&lt;&gt;0),F119-G119," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E120" s="119"/>
-      <c r="G120" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F120&lt;&gt;0,F120*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H120" s="123" t="str">
+      <c r="G120" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F120&lt;&gt;0,F120*G$4/100," ")),IF(F120&lt;&gt;0,F120*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H120" s="99" t="str">
         <f aca="false">IF((F120&lt;&gt;0),F120-G120," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E121" s="119"/>
-      <c r="G121" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F121&lt;&gt;0,F121*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H121" s="123" t="str">
+      <c r="G121" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F121&lt;&gt;0,F121*G$4/100," ")),IF(F121&lt;&gt;0,F121*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H121" s="99" t="str">
         <f aca="false">IF((F121&lt;&gt;0),F121-G121," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E122" s="119"/>
-      <c r="G122" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F122&lt;&gt;0,F122*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H122" s="123" t="str">
+      <c r="G122" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F122&lt;&gt;0,F122*G$4/100," ")),IF(F122&lt;&gt;0,F122*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H122" s="99" t="str">
         <f aca="false">IF((F122&lt;&gt;0),F122-G122," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E123" s="119"/>
-      <c r="G123" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F123&lt;&gt;0,F123*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H123" s="123" t="str">
+      <c r="G123" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F123&lt;&gt;0,F123*G$4/100," ")),IF(F123&lt;&gt;0,F123*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H123" s="99" t="str">
         <f aca="false">IF((F123&lt;&gt;0),F123-G123," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E124" s="119"/>
-      <c r="G124" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F124&lt;&gt;0,F124*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H124" s="123" t="str">
+      <c r="G124" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F124&lt;&gt;0,F124*G$4/100," ")),IF(F124&lt;&gt;0,F124*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H124" s="99" t="str">
         <f aca="false">IF((F124&lt;&gt;0),F124-G124," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E125" s="119"/>
-      <c r="G125" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F125&lt;&gt;0,F125*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H125" s="123" t="str">
+      <c r="G125" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F125&lt;&gt;0,F125*G$4/100," ")),IF(F125&lt;&gt;0,F125*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H125" s="99" t="str">
         <f aca="false">IF((F125&lt;&gt;0),F125-G125," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E126" s="119"/>
-      <c r="G126" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F126&lt;&gt;0,F126*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H126" s="123" t="str">
+      <c r="G126" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F126&lt;&gt;0,F126*G$4/100," ")),IF(F126&lt;&gt;0,F126*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H126" s="99" t="str">
         <f aca="false">IF((F126&lt;&gt;0),F126-G126," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E127" s="119"/>
-      <c r="G127" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F127&lt;&gt;0,F127*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H127" s="123" t="str">
+      <c r="G127" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F127&lt;&gt;0,F127*G$4/100," ")),IF(F127&lt;&gt;0,F127*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H127" s="99" t="str">
         <f aca="false">IF((F127&lt;&gt;0),F127-G127," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E128" s="119"/>
-      <c r="G128" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F128&lt;&gt;0,F128*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H128" s="123" t="str">
+      <c r="G128" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F128&lt;&gt;0,F128*G$4/100," ")),IF(F128&lt;&gt;0,F128*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H128" s="99" t="str">
         <f aca="false">IF((F128&lt;&gt;0),F128-G128," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E129" s="119"/>
-      <c r="G129" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F129&lt;&gt;0,F129*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H129" s="123" t="str">
+      <c r="G129" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F129&lt;&gt;0,F129*G$4/100," ")),IF(F129&lt;&gt;0,F129*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H129" s="99" t="str">
         <f aca="false">IF((F129&lt;&gt;0),F129-G129," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E130" s="119"/>
-      <c r="G130" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F130&lt;&gt;0,F130*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H130" s="123" t="str">
+      <c r="G130" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F130&lt;&gt;0,F130*G$4/100," ")),IF(F130&lt;&gt;0,F130*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H130" s="99" t="str">
         <f aca="false">IF((F130&lt;&gt;0),F130-G130," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E131" s="119"/>
-      <c r="G131" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F131&lt;&gt;0,F131*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H131" s="123" t="str">
+      <c r="G131" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F131&lt;&gt;0,F131*G$4/100," ")),IF(F131&lt;&gt;0,F131*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H131" s="99" t="str">
         <f aca="false">IF((F131&lt;&gt;0),F131-G131," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E132" s="119"/>
-      <c r="G132" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F132&lt;&gt;0,F132*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H132" s="123" t="str">
+      <c r="G132" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F132&lt;&gt;0,F132*G$4/100," ")),IF(F132&lt;&gt;0,F132*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H132" s="99" t="str">
         <f aca="false">IF((F132&lt;&gt;0),F132-G132," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E133" s="119"/>
-      <c r="G133" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F133&lt;&gt;0,F133*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H133" s="123" t="str">
+      <c r="G133" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F133&lt;&gt;0,F133*G$4/100," ")),IF(F133&lt;&gt;0,F133*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H133" s="99" t="str">
         <f aca="false">IF((F133&lt;&gt;0),F133-G133," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E134" s="119"/>
-      <c r="G134" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F134&lt;&gt;0,F134*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H134" s="123" t="str">
+      <c r="G134" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F134&lt;&gt;0,F134*G$4/100," ")),IF(F134&lt;&gt;0,F134*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H134" s="99" t="str">
         <f aca="false">IF((F134&lt;&gt;0),F134-G134," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E135" s="119"/>
-      <c r="G135" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F135&lt;&gt;0,F135*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H135" s="123" t="str">
+      <c r="G135" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F135&lt;&gt;0,F135*G$4/100," ")),IF(F135&lt;&gt;0,F135*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H135" s="99" t="str">
         <f aca="false">IF((F135&lt;&gt;0),F135-G135," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E136" s="119"/>
-      <c r="G136" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F136&lt;&gt;0,F136*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H136" s="123" t="str">
+      <c r="G136" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F136&lt;&gt;0,F136*G$4/100," ")),IF(F136&lt;&gt;0,F136*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H136" s="99" t="str">
         <f aca="false">IF((F136&lt;&gt;0),F136-G136," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E137" s="119"/>
-      <c r="G137" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F137&lt;&gt;0,F137*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H137" s="123" t="str">
+      <c r="G137" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F137&lt;&gt;0,F137*G$4/100," ")),IF(F137&lt;&gt;0,F137*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H137" s="99" t="str">
         <f aca="false">IF((F137&lt;&gt;0),F137-G137," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E138" s="119"/>
-      <c r="G138" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F138&lt;&gt;0,F138*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H138" s="123" t="str">
+      <c r="G138" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F138&lt;&gt;0,F138*G$4/100," ")),IF(F138&lt;&gt;0,F138*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H138" s="99" t="str">
         <f aca="false">IF((F138&lt;&gt;0),F138-G138," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E139" s="119"/>
-      <c r="G139" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F139&lt;&gt;0,F139*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H139" s="123" t="str">
+      <c r="G139" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F139&lt;&gt;0,F139*G$4/100," ")),IF(F139&lt;&gt;0,F139*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H139" s="99" t="str">
         <f aca="false">IF((F139&lt;&gt;0),F139-G139," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E140" s="119"/>
-      <c r="G140" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F140&lt;&gt;0,F140*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H140" s="123" t="str">
+      <c r="G140" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F140&lt;&gt;0,F140*G$4/100," ")),IF(F140&lt;&gt;0,F140*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H140" s="99" t="str">
         <f aca="false">IF((F140&lt;&gt;0),F140-G140," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E141" s="119"/>
-      <c r="G141" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F141&lt;&gt;0,F141*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H141" s="123" t="str">
+      <c r="G141" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F141&lt;&gt;0,F141*G$4/100," ")),IF(F141&lt;&gt;0,F141*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H141" s="99" t="str">
         <f aca="false">IF((F141&lt;&gt;0),F141-G141," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E142" s="119"/>
-      <c r="G142" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F142&lt;&gt;0,F142*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H142" s="123" t="str">
+      <c r="G142" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F142&lt;&gt;0,F142*G$4/100," ")),IF(F142&lt;&gt;0,F142*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H142" s="99" t="str">
         <f aca="false">IF((F142&lt;&gt;0),F142-G142," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E143" s="119"/>
-      <c r="G143" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F143&lt;&gt;0,F143*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H143" s="123" t="str">
+      <c r="G143" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F143&lt;&gt;0,F143*G$4/100," ")),IF(F143&lt;&gt;0,F143*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H143" s="99" t="str">
         <f aca="false">IF((F143&lt;&gt;0),F143-G143," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E144" s="119"/>
-      <c r="G144" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F144&lt;&gt;0,F144*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H144" s="123" t="str">
+      <c r="G144" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F144&lt;&gt;0,F144*G$4/100," ")),IF(F144&lt;&gt;0,F144*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H144" s="99" t="str">
         <f aca="false">IF((F144&lt;&gt;0),F144-G144," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E145" s="119"/>
-      <c r="G145" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F145&lt;&gt;0,F145*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H145" s="123" t="str">
+      <c r="G145" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F145&lt;&gt;0,F145*G$4/100," ")),IF(F145&lt;&gt;0,F145*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H145" s="99" t="str">
         <f aca="false">IF((F145&lt;&gt;0),F145-G145," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E146" s="119"/>
-      <c r="G146" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F146&lt;&gt;0,F146*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H146" s="123" t="str">
+      <c r="G146" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F146&lt;&gt;0,F146*G$4/100," ")),IF(F146&lt;&gt;0,F146*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H146" s="99" t="str">
         <f aca="false">IF((F146&lt;&gt;0),F146-G146," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E147" s="119"/>
-      <c r="G147" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F147&lt;&gt;0,F147*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H147" s="123" t="str">
+      <c r="G147" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F147&lt;&gt;0,F147*G$4/100," ")),IF(F147&lt;&gt;0,F147*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H147" s="99" t="str">
         <f aca="false">IF((F147&lt;&gt;0),F147-G147," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E148" s="119"/>
-      <c r="G148" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F148&lt;&gt;0,F148*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H148" s="123" t="str">
+      <c r="G148" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F148&lt;&gt;0,F148*G$4/100," ")),IF(F148&lt;&gt;0,F148*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H148" s="99" t="str">
         <f aca="false">IF((F148&lt;&gt;0),F148-G148," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E149" s="119"/>
-      <c r="G149" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F149&lt;&gt;0,F149*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H149" s="123" t="str">
+      <c r="G149" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F149&lt;&gt;0,F149*G$4/100," ")),IF(F149&lt;&gt;0,F149*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H149" s="99" t="str">
         <f aca="false">IF((F149&lt;&gt;0),F149-G149," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E150" s="119"/>
-      <c r="G150" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F150&lt;&gt;0,F150*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H150" s="123" t="str">
+      <c r="G150" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F150&lt;&gt;0,F150*G$4/100," ")),IF(F150&lt;&gt;0,F150*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H150" s="99" t="str">
         <f aca="false">IF((F150&lt;&gt;0),F150-G150," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E151" s="119"/>
-      <c r="G151" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F151&lt;&gt;0,F151*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H151" s="123" t="str">
+      <c r="G151" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F151&lt;&gt;0,F151*G$4/100," ")),IF(F151&lt;&gt;0,F151*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H151" s="99" t="str">
         <f aca="false">IF((F151&lt;&gt;0),F151-G151," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E152" s="119"/>
-      <c r="G152" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F152&lt;&gt;0,F152*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H152" s="123" t="str">
+      <c r="G152" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F152&lt;&gt;0,F152*G$4/100," ")),IF(F152&lt;&gt;0,F152*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H152" s="99" t="str">
         <f aca="false">IF((F152&lt;&gt;0),F152-G152," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E153" s="119"/>
-      <c r="G153" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F153&lt;&gt;0,F153*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H153" s="123" t="str">
+      <c r="G153" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F153&lt;&gt;0,F153*G$4/100," ")),IF(F153&lt;&gt;0,F153*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H153" s="99" t="str">
         <f aca="false">IF((F153&lt;&gt;0),F153-G153," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E154" s="119"/>
-      <c r="G154" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F154&lt;&gt;0,F154*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H154" s="123" t="str">
+      <c r="G154" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F154&lt;&gt;0,F154*G$4/100," ")),IF(F154&lt;&gt;0,F154*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H154" s="99" t="str">
         <f aca="false">IF((F154&lt;&gt;0),F154-G154," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E155" s="119"/>
-      <c r="G155" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F155&lt;&gt;0,F155*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H155" s="123" t="str">
+      <c r="G155" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F155&lt;&gt;0,F155*G$4/100," ")),IF(F155&lt;&gt;0,F155*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H155" s="99" t="str">
         <f aca="false">IF((F155&lt;&gt;0),F155-G155," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E156" s="119"/>
-      <c r="G156" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F156&lt;&gt;0,F156*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H156" s="123" t="str">
+      <c r="G156" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F156&lt;&gt;0,F156*G$4/100," ")),IF(F156&lt;&gt;0,F156*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H156" s="99" t="str">
         <f aca="false">IF((F156&lt;&gt;0),F156-G156," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E157" s="119"/>
-      <c r="G157" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F157&lt;&gt;0,F157*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H157" s="123" t="str">
+      <c r="G157" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F157&lt;&gt;0,F157*G$4/100," ")),IF(F157&lt;&gt;0,F157*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H157" s="99" t="str">
         <f aca="false">IF((F157&lt;&gt;0),F157-G157," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E158" s="119"/>
-      <c r="G158" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F158&lt;&gt;0,F158*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H158" s="123" t="str">
+      <c r="G158" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F158&lt;&gt;0,F158*G$4/100," ")),IF(F158&lt;&gt;0,F158*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H158" s="99" t="str">
         <f aca="false">IF((F158&lt;&gt;0),F158-G158," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E159" s="119"/>
-      <c r="G159" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F159&lt;&gt;0,F159*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H159" s="123" t="str">
+      <c r="G159" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F159&lt;&gt;0,F159*G$4/100," ")),IF(F159&lt;&gt;0,F159*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H159" s="99" t="str">
         <f aca="false">IF((F159&lt;&gt;0),F159-G159," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E160" s="119"/>
-      <c r="G160" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F160&lt;&gt;0,F160*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H160" s="123" t="str">
+      <c r="G160" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F160&lt;&gt;0,F160*G$4/100," ")),IF(F160&lt;&gt;0,F160*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H160" s="99" t="str">
         <f aca="false">IF((F160&lt;&gt;0),F160-G160," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E161" s="119"/>
-      <c r="G161" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F161&lt;&gt;0,F161*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H161" s="123" t="str">
+      <c r="G161" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F161&lt;&gt;0,F161*G$4/100," ")),IF(F161&lt;&gt;0,F161*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H161" s="99" t="str">
         <f aca="false">IF((F161&lt;&gt;0),F161-G161," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E162" s="119"/>
-      <c r="G162" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F162&lt;&gt;0,F162*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H162" s="123" t="str">
+      <c r="G162" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F162&lt;&gt;0,F162*G$4/100," ")),IF(F162&lt;&gt;0,F162*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H162" s="99" t="str">
         <f aca="false">IF((F162&lt;&gt;0),F162-G162," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E163" s="119"/>
-      <c r="G163" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F163&lt;&gt;0,F163*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H163" s="123" t="str">
+      <c r="G163" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F163&lt;&gt;0,F163*G$4/100," ")),IF(F163&lt;&gt;0,F163*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H163" s="99" t="str">
         <f aca="false">IF((F163&lt;&gt;0),F163-G163," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E164" s="119"/>
-      <c r="G164" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F164&lt;&gt;0,F164*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H164" s="123" t="str">
+      <c r="G164" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F164&lt;&gt;0,F164*G$4/100," ")),IF(F164&lt;&gt;0,F164*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H164" s="99" t="str">
         <f aca="false">IF((F164&lt;&gt;0),F164-G164," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E165" s="119"/>
-      <c r="G165" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F165&lt;&gt;0,F165*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H165" s="123" t="str">
+      <c r="G165" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F165&lt;&gt;0,F165*G$4/100," ")),IF(F165&lt;&gt;0,F165*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H165" s="99" t="str">
         <f aca="false">IF((F165&lt;&gt;0),F165-G165," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E166" s="119"/>
-      <c r="G166" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F166&lt;&gt;0,F166*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H166" s="123" t="str">
+      <c r="G166" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F166&lt;&gt;0,F166*G$4/100," ")),IF(F166&lt;&gt;0,F166*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H166" s="99" t="str">
         <f aca="false">IF((F166&lt;&gt;0),F166-G166," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E167" s="119"/>
-      <c r="G167" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F167&lt;&gt;0,F167*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H167" s="123" t="str">
+      <c r="G167" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F167&lt;&gt;0,F167*G$4/100," ")),IF(F167&lt;&gt;0,F167*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H167" s="99" t="str">
         <f aca="false">IF((F167&lt;&gt;0),F167-G167," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E168" s="119"/>
-      <c r="G168" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F168&lt;&gt;0,F168*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H168" s="123" t="str">
+      <c r="G168" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F168&lt;&gt;0,F168*G$4/100," ")),IF(F168&lt;&gt;0,F168*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H168" s="99" t="str">
         <f aca="false">IF((F168&lt;&gt;0),F168-G168," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E169" s="119"/>
-      <c r="G169" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F169&lt;&gt;0,F169*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H169" s="123" t="str">
+      <c r="G169" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F169&lt;&gt;0,F169*G$4/100," ")),IF(F169&lt;&gt;0,F169*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H169" s="99" t="str">
         <f aca="false">IF((F169&lt;&gt;0),F169-G169," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E170" s="119"/>
-      <c r="G170" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F170&lt;&gt;0,F170*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H170" s="123" t="str">
+      <c r="G170" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F170&lt;&gt;0,F170*G$4/100," ")),IF(F170&lt;&gt;0,F170*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H170" s="99" t="str">
         <f aca="false">IF((F170&lt;&gt;0),F170-G170," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E171" s="119"/>
-      <c r="G171" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F171&lt;&gt;0,F171*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H171" s="123" t="str">
+      <c r="G171" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F171&lt;&gt;0,F171*G$4/100," ")),IF(F171&lt;&gt;0,F171*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H171" s="99" t="str">
         <f aca="false">IF((F171&lt;&gt;0),F171-G171," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E172" s="119"/>
-      <c r="G172" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F172&lt;&gt;0,F172*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H172" s="123" t="str">
+      <c r="G172" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F172&lt;&gt;0,F172*G$4/100," ")),IF(F172&lt;&gt;0,F172*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H172" s="99" t="str">
         <f aca="false">IF((F172&lt;&gt;0),F172-G172," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E173" s="119"/>
-      <c r="G173" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F173&lt;&gt;0,F173*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H173" s="123" t="str">
+      <c r="G173" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F173&lt;&gt;0,F173*G$4/100," ")),IF(F173&lt;&gt;0,F173*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H173" s="99" t="str">
         <f aca="false">IF((F173&lt;&gt;0),F173-G173," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E174" s="119"/>
-      <c r="G174" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F174&lt;&gt;0,F174*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H174" s="123" t="str">
+      <c r="G174" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F174&lt;&gt;0,F174*G$4/100," ")),IF(F174&lt;&gt;0,F174*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H174" s="99" t="str">
         <f aca="false">IF((F174&lt;&gt;0),F174-G174," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E175" s="119"/>
-      <c r="G175" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F175&lt;&gt;0,F175*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H175" s="123" t="str">
+      <c r="G175" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F175&lt;&gt;0,F175*G$4/100," ")),IF(F175&lt;&gt;0,F175*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H175" s="99" t="str">
         <f aca="false">IF((F175&lt;&gt;0),F175-G175," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E176" s="119"/>
-      <c r="G176" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F176&lt;&gt;0,F176*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H176" s="123" t="str">
+      <c r="G176" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F176&lt;&gt;0,F176*G$4/100," ")),IF(F176&lt;&gt;0,F176*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H176" s="99" t="str">
         <f aca="false">IF((F176&lt;&gt;0),F176-G176," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E177" s="119"/>
-      <c r="G177" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F177&lt;&gt;0,F177*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H177" s="123" t="str">
+      <c r="G177" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F177&lt;&gt;0,F177*G$4/100," ")),IF(F177&lt;&gt;0,F177*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H177" s="99" t="str">
         <f aca="false">IF((F177&lt;&gt;0),F177-G177," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E178" s="119"/>
-      <c r="G178" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F178&lt;&gt;0,F178*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H178" s="123" t="str">
+      <c r="G178" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F178&lt;&gt;0,F178*G$4/100," ")),IF(F178&lt;&gt;0,F178*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H178" s="99" t="str">
         <f aca="false">IF((F178&lt;&gt;0),F178-G178," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E179" s="119"/>
-      <c r="G179" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F179&lt;&gt;0,F179*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H179" s="123" t="str">
+      <c r="G179" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F179&lt;&gt;0,F179*G$4/100," ")),IF(F179&lt;&gt;0,F179*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H179" s="99" t="str">
         <f aca="false">IF((F179&lt;&gt;0),F179-G179," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E180" s="119"/>
-      <c r="G180" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F180&lt;&gt;0,F180*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H180" s="123" t="str">
+      <c r="G180" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F180&lt;&gt;0,F180*G$4/100," ")),IF(F180&lt;&gt;0,F180*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H180" s="99" t="str">
         <f aca="false">IF((F180&lt;&gt;0),F180-G180," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E181" s="119"/>
-      <c r="G181" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F181&lt;&gt;0,F181*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H181" s="123" t="str">
+      <c r="G181" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F181&lt;&gt;0,F181*G$4/100," ")),IF(F181&lt;&gt;0,F181*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H181" s="99" t="str">
         <f aca="false">IF((F181&lt;&gt;0),F181-G181," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E182" s="119"/>
-      <c r="G182" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F182&lt;&gt;0,F182*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H182" s="123" t="str">
+      <c r="G182" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F182&lt;&gt;0,F182*G$4/100," ")),IF(F182&lt;&gt;0,F182*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H182" s="99" t="str">
         <f aca="false">IF((F182&lt;&gt;0),F182-G182," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E183" s="119"/>
-      <c r="G183" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F183&lt;&gt;0,F183*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H183" s="123" t="str">
+      <c r="G183" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F183&lt;&gt;0,F183*G$4/100," ")),IF(F183&lt;&gt;0,F183*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H183" s="99" t="str">
         <f aca="false">IF((F183&lt;&gt;0),F183-G183," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E184" s="119"/>
-      <c r="G184" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F184&lt;&gt;0,F184*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H184" s="123" t="str">
+      <c r="G184" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F184&lt;&gt;0,F184*G$4/100," ")),IF(F184&lt;&gt;0,F184*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H184" s="99" t="str">
         <f aca="false">IF((F184&lt;&gt;0),F184-G184," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E185" s="119"/>
-      <c r="G185" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F185&lt;&gt;0,F185*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H185" s="123" t="str">
+      <c r="G185" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F185&lt;&gt;0,F185*G$4/100," ")),IF(F185&lt;&gt;0,F185*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H185" s="99" t="str">
         <f aca="false">IF((F185&lt;&gt;0),F185-G185," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E186" s="119"/>
-      <c r="G186" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F186&lt;&gt;0,F186*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H186" s="123" t="str">
+      <c r="G186" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F186&lt;&gt;0,F186*G$4/100," ")),IF(F186&lt;&gt;0,F186*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H186" s="99" t="str">
         <f aca="false">IF((F186&lt;&gt;0),F186-G186," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E187" s="119"/>
-      <c r="G187" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F187&lt;&gt;0,F187*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H187" s="123" t="str">
+      <c r="G187" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F187&lt;&gt;0,F187*G$4/100," ")),IF(F187&lt;&gt;0,F187*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H187" s="99" t="str">
         <f aca="false">IF((F187&lt;&gt;0),F187-G187," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E188" s="119"/>
-      <c r="G188" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F188&lt;&gt;0,F188*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H188" s="123" t="str">
+      <c r="G188" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F188&lt;&gt;0,F188*G$4/100," ")),IF(F188&lt;&gt;0,F188*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H188" s="99" t="str">
         <f aca="false">IF((F188&lt;&gt;0),F188-G188," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E189" s="119"/>
-      <c r="G189" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F189&lt;&gt;0,F189*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H189" s="123" t="str">
+      <c r="G189" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F189&lt;&gt;0,F189*G$4/100," ")),IF(F189&lt;&gt;0,F189*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H189" s="99" t="str">
         <f aca="false">IF((F189&lt;&gt;0),F189-G189," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E190" s="119"/>
-      <c r="G190" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F190&lt;&gt;0,F190*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H190" s="123" t="str">
+      <c r="G190" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F190&lt;&gt;0,F190*G$4/100," ")),IF(F190&lt;&gt;0,F190*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H190" s="99" t="str">
         <f aca="false">IF((F190&lt;&gt;0),F190-G190," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E191" s="119"/>
-      <c r="G191" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F191&lt;&gt;0,F191*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H191" s="123" t="str">
+      <c r="G191" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F191&lt;&gt;0,F191*G$4/100," ")),IF(F191&lt;&gt;0,F191*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H191" s="99" t="str">
         <f aca="false">IF((F191&lt;&gt;0),F191-G191," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E192" s="119"/>
-      <c r="G192" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F192&lt;&gt;0,F192*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H192" s="123" t="str">
+      <c r="G192" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F192&lt;&gt;0,F192*G$4/100," ")),IF(F192&lt;&gt;0,F192*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H192" s="99" t="str">
         <f aca="false">IF((F192&lt;&gt;0),F192-G192," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E193" s="119"/>
-      <c r="G193" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F193&lt;&gt;0,F193*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H193" s="123" t="str">
+      <c r="G193" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F193&lt;&gt;0,F193*G$4/100," ")),IF(F193&lt;&gt;0,F193*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H193" s="99" t="str">
         <f aca="false">IF((F193&lt;&gt;0),F193-G193," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E194" s="119"/>
-      <c r="G194" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F194&lt;&gt;0,F194*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H194" s="123" t="str">
+      <c r="G194" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F194&lt;&gt;0,F194*G$4/100," ")),IF(F194&lt;&gt;0,F194*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H194" s="99" t="str">
         <f aca="false">IF((F194&lt;&gt;0),F194-G194," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E195" s="119"/>
-      <c r="G195" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F195&lt;&gt;0,F195*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H195" s="123" t="str">
+      <c r="G195" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F195&lt;&gt;0,F195*G$4/100," ")),IF(F195&lt;&gt;0,F195*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H195" s="99" t="str">
         <f aca="false">IF((F195&lt;&gt;0),F195-G195," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E196" s="119"/>
-      <c r="G196" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F196&lt;&gt;0,F196*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H196" s="123" t="str">
+      <c r="G196" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F196&lt;&gt;0,F196*G$4/100," ")),IF(F196&lt;&gt;0,F196*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H196" s="99" t="str">
         <f aca="false">IF((F196&lt;&gt;0),F196-G196," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E197" s="119"/>
-      <c r="G197" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F197&lt;&gt;0,F197*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H197" s="123" t="str">
+      <c r="G197" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F197&lt;&gt;0,F197*G$4/100," ")),IF(F197&lt;&gt;0,F197*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H197" s="99" t="str">
         <f aca="false">IF((F197&lt;&gt;0),F197-G197," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E198" s="119"/>
-      <c r="G198" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F198&lt;&gt;0,F198*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H198" s="123" t="str">
+      <c r="G198" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F198&lt;&gt;0,F198*G$4/100," ")),IF(F198&lt;&gt;0,F198*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H198" s="99" t="str">
         <f aca="false">IF((F198&lt;&gt;0),F198-G198," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E199" s="119"/>
-      <c r="G199" s="123" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F199&lt;&gt;0,F199*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H199" s="123" t="str">
+      <c r="G199" s="99" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F199&lt;&gt;0,F199*G$4/100," ")),IF(F199&lt;&gt;0,F199*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H199" s="99" t="str">
         <f aca="false">IF((F199&lt;&gt;0),F199-G199," ")</f>
         <v> </v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="132"/>
-      <c r="B200" s="133"/>
-      <c r="C200" s="134"/>
-      <c r="D200" s="135"/>
-      <c r="E200" s="133"/>
-      <c r="F200" s="136"/>
-      <c r="G200" s="136" t="str">
-        <f aca="false">IF(G$4="X"," ",IF(F200&lt;&gt;0,F200*G$2/(100+G$2)," "))</f>
-        <v> </v>
-      </c>
-      <c r="H200" s="136" t="str">
+      <c r="A200" s="114"/>
+      <c r="B200" s="115"/>
+      <c r="C200" s="116"/>
+      <c r="D200" s="116"/>
+      <c r="E200" s="117"/>
+      <c r="F200" s="115"/>
+      <c r="G200" s="115" t="str">
+        <f aca="false">IF(G$4&gt;0,(IF(F200&lt;&gt;0,F200*G$4/100," ")),IF(F200&lt;&gt;0,F200*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H200" s="115" t="str">
         <f aca="false">IF((F200&lt;&gt;0),F200-G200," ")</f>
         <v> </v>
       </c>
@@ -6771,13 +6591,9 @@
       <c r="A201" s="98" t="s">
         <v>40</v>
       </c>
-      <c r="G201" s="123" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="A2:A4"/>
@@ -6787,7 +6603,6 @@
     <mergeCell ref="E2:E4"/>
     <mergeCell ref="F2:F4"/>
     <mergeCell ref="H2:H4"/>
-    <mergeCell ref="G3:G4"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6830,41 +6645,41 @@
       <c r="E1" s="105"/>
       <c r="F1" s="105" t="n">
         <f aca="false">SUM(F5:F200)</f>
-        <v>1200</v>
+        <v>720</v>
       </c>
       <c r="G1" s="105" t="n">
         <f aca="false">SUM(G5:G200)</f>
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="H1" s="105" t="n">
         <f aca="false">SUM(H5:H200)</f>
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="2" s="127" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="107" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B2" s="108" t="str">
         <f aca="false">IF((H1-SUM(O1:AK1)&lt;&gt;0),"COMPLETE EXPENSE ANALYSIS by inserting expense letter in col F","Supplier")</f>
         <v>COMPLETE EXPENSE ANALYSIS by inserting expense letter in col F</v>
       </c>
       <c r="C2" s="110" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D2" s="124" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E2" s="125"/>
       <c r="F2" s="108" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G2" s="126" t="n">
         <f aca="false">[3]OpeningCreditors!$G$2</f>
         <v>20</v>
       </c>
       <c r="H2" s="108" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" s="128" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6875,7 +6690,7 @@
       <c r="E3" s="125"/>
       <c r="F3" s="108"/>
       <c r="G3" s="108" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H3" s="108"/>
     </row>
@@ -6891,25 +6706,25 @@
     </row>
     <row r="5" s="119" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="118" t="n">
-        <v>45924</v>
+        <v>45889</v>
       </c>
       <c r="B5" s="122" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="129" t="s">
         <v>54</v>
-      </c>
-      <c r="C5" s="129" t="s">
-        <v>55</v>
       </c>
       <c r="D5" s="122"/>
       <c r="F5" s="130" t="n">
-        <v>1200</v>
+        <v>720</v>
       </c>
       <c r="G5" s="123" t="n">
         <f aca="false">IF(F5&lt;&gt;0,F5*G$2/(100+G$2)," ")</f>
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="H5" s="123" t="n">
         <f aca="false">IF((F5&lt;&gt;0),F5-G5," ")</f>
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9108,7 +8923,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="119" width="19.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="120" width="12.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="121" width="14.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="122" width="5.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="122" width="5.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="123" width="10.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="123" width="9.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="123" width="10.66"/>
@@ -9127,41 +8942,41 @@
       <c r="E1" s="105"/>
       <c r="F1" s="105" t="n">
         <f aca="false">SUM(F5:F200)</f>
-        <v>240</v>
+        <v>1200</v>
       </c>
       <c r="G1" s="105" t="n">
         <f aca="false">SUM(G5:G200)</f>
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="H1" s="105" t="n">
         <f aca="false">SUM(H5:H200)</f>
-        <v>200</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="2" s="127" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="107" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B2" s="108" t="str">
         <f aca="false">IF((H1-SUM(O1:AK1)&lt;&gt;0),"COMPLETE EXPENSE ANALYSIS by inserting expense letter in col F","Supplier")</f>
         <v>COMPLETE EXPENSE ANALYSIS by inserting expense letter in col F</v>
       </c>
       <c r="C2" s="110" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D2" s="124" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E2" s="125"/>
       <c r="F2" s="108" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G2" s="126" t="n">
-        <f aca="false">[3]ClosingCreditors!$G$2</f>
+        <f aca="false">[3]OpeningCreditors!$G$2</f>
         <v>20</v>
       </c>
       <c r="H2" s="108" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" s="128" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9172,7 +8987,7 @@
       <c r="E3" s="125"/>
       <c r="F3" s="108"/>
       <c r="G3" s="108" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H3" s="108"/>
     </row>
@@ -9188,25 +9003,25 @@
     </row>
     <row r="5" s="119" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="118" t="n">
-        <v>46310</v>
+        <v>45924</v>
       </c>
       <c r="B5" s="122" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="129" t="s">
         <v>56</v>
-      </c>
-      <c r="C5" s="129" t="s">
-        <v>57</v>
       </c>
       <c r="D5" s="122"/>
       <c r="F5" s="130" t="n">
-        <v>240</v>
+        <v>1200</v>
       </c>
       <c r="G5" s="123" t="n">
         <f aca="false">IF(F5&lt;&gt;0,F5*G$2/(100+G$2)," ")</f>
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="H5" s="123" t="n">
         <f aca="false">IF((F5&lt;&gt;0),F5-G5," ")</f>
-        <v>200</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11424,41 +11239,41 @@
       <c r="E1" s="105"/>
       <c r="F1" s="105" t="n">
         <f aca="false">SUM(F5:F200)</f>
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="G1" s="105" t="n">
         <f aca="false">SUM(G5:G200)</f>
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H1" s="105" t="n">
         <f aca="false">SUM(H5:H200)</f>
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" s="127" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="107" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B2" s="108" t="str">
         <f aca="false">IF((H1-SUM(O1:AK1)&lt;&gt;0),"COMPLETE EXPENSE ANALYSIS by inserting expense letter in col F","Supplier")</f>
         <v>COMPLETE EXPENSE ANALYSIS by inserting expense letter in col F</v>
       </c>
       <c r="C2" s="110" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D2" s="124" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E2" s="125"/>
       <c r="F2" s="108" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G2" s="126" t="n">
         <f aca="false">[3]ClosingCreditors!$G$2</f>
         <v>20</v>
       </c>
       <c r="H2" s="108" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" s="128" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11469,7 +11284,7 @@
       <c r="E3" s="125"/>
       <c r="F3" s="108"/>
       <c r="G3" s="108" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H3" s="108"/>
     </row>
@@ -11485,13 +11300,2310 @@
     </row>
     <row r="5" s="119" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="118" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B5" s="122" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="129" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="122"/>
+      <c r="F5" s="130" t="n">
+        <v>240</v>
+      </c>
+      <c r="G5" s="123" t="n">
+        <f aca="false">IF(F5&lt;&gt;0,F5*G$2/(100+G$2)," ")</f>
+        <v>40</v>
+      </c>
+      <c r="H5" s="123" t="n">
+        <f aca="false">IF((F5&lt;&gt;0),F5-G5," ")</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E6" s="119"/>
+      <c r="G6" s="123" t="str">
+        <f aca="false">IF(F6&lt;&gt;0,F6*G$2/(100+G$2)," ")</f>
+        <v> </v>
+      </c>
+      <c r="H6" s="123" t="str">
+        <f aca="false">IF((F6&lt;&gt;0),F6-G6," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E7" s="119"/>
+      <c r="G7" s="123" t="str">
+        <f aca="false">IF(F7&lt;&gt;0,F7*G$2/(100+G$2)," ")</f>
+        <v> </v>
+      </c>
+      <c r="H7" s="123" t="str">
+        <f aca="false">IF((F7&lt;&gt;0),F7-G7," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E8" s="119"/>
+      <c r="G8" s="123" t="str">
+        <f aca="false">IF(F8&lt;&gt;0,F8*G$2/(100+G$2)," ")</f>
+        <v> </v>
+      </c>
+      <c r="H8" s="123" t="str">
+        <f aca="false">IF((F8&lt;&gt;0),F8-G8," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E9" s="119"/>
+      <c r="G9" s="123" t="str">
+        <f aca="false">IF(F9&lt;&gt;0,F9*G$2/(100+G$2)," ")</f>
+        <v> </v>
+      </c>
+      <c r="H9" s="123" t="str">
+        <f aca="false">IF((F9&lt;&gt;0),F9-G9," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E10" s="119"/>
+      <c r="G10" s="123" t="str">
+        <f aca="false">IF(F10&lt;&gt;0,F10*G$2/(100+G$2)," ")</f>
+        <v> </v>
+      </c>
+      <c r="H10" s="123" t="str">
+        <f aca="false">IF((F10&lt;&gt;0),F10-G10," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E11" s="119"/>
+      <c r="G11" s="123" t="str">
+        <f aca="false">IF(F11&lt;&gt;0,F11*G$2/(100+G$2)," ")</f>
+        <v> </v>
+      </c>
+      <c r="H11" s="123" t="str">
+        <f aca="false">IF((F11&lt;&gt;0),F11-G11," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E12" s="119"/>
+      <c r="G12" s="123" t="str">
+        <f aca="false">IF(F12&lt;&gt;0,F12*G$2/(100+G$2)," ")</f>
+        <v> </v>
+      </c>
+      <c r="H12" s="123" t="str">
+        <f aca="false">IF((F12&lt;&gt;0),F12-G12," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E13" s="119"/>
+      <c r="G13" s="123" t="str">
+        <f aca="false">IF(F13&lt;&gt;0,F13*G$2/(100+G$2)," ")</f>
+        <v> </v>
+      </c>
+      <c r="H13" s="123" t="str">
+        <f aca="false">IF((F13&lt;&gt;0),F13-G13," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E14" s="119"/>
+      <c r="G14" s="123" t="str">
+        <f aca="false">IF(F14&lt;&gt;0,F14*G$2/(100+G$2)," ")</f>
+        <v> </v>
+      </c>
+      <c r="H14" s="123" t="str">
+        <f aca="false">IF((F14&lt;&gt;0),F14-G14," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E15" s="119"/>
+      <c r="G15" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F15&lt;&gt;0,F15*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H15" s="123" t="str">
+        <f aca="false">IF((F15&lt;&gt;0),F15-G15," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E16" s="119"/>
+      <c r="G16" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F16&lt;&gt;0,F16*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H16" s="123" t="str">
+        <f aca="false">IF((F16&lt;&gt;0),F16-G16," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E17" s="119"/>
+      <c r="G17" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F17&lt;&gt;0,F17*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H17" s="123" t="str">
+        <f aca="false">IF((F17&lt;&gt;0),F17-G17," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E18" s="119"/>
+      <c r="G18" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F18&lt;&gt;0,F18*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H18" s="123" t="str">
+        <f aca="false">IF((F18&lt;&gt;0),F18-G18," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E19" s="119"/>
+      <c r="G19" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F19&lt;&gt;0,F19*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H19" s="123" t="str">
+        <f aca="false">IF((F19&lt;&gt;0),F19-G19," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E20" s="119"/>
+      <c r="G20" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F20&lt;&gt;0,F20*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H20" s="123" t="str">
+        <f aca="false">IF((F20&lt;&gt;0),F20-G20," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E21" s="119"/>
+      <c r="G21" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F21&lt;&gt;0,F21*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H21" s="123" t="str">
+        <f aca="false">IF((F21&lt;&gt;0),F21-G21," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D22" s="119"/>
+      <c r="E22" s="119"/>
+      <c r="G22" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F22&lt;&gt;0,F22*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H22" s="123" t="str">
+        <f aca="false">IF((F22&lt;&gt;0),F22-G22," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D23" s="131"/>
+      <c r="E23" s="119"/>
+      <c r="G23" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F23&lt;&gt;0,F23*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H23" s="123" t="str">
+        <f aca="false">IF((F23&lt;&gt;0),F23-G23," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E24" s="119"/>
+      <c r="G24" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F24&lt;&gt;0,F24*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H24" s="123" t="str">
+        <f aca="false">IF((F24&lt;&gt;0),F24-G24," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E25" s="119"/>
+      <c r="G25" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F25&lt;&gt;0,F25*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H25" s="123" t="str">
+        <f aca="false">IF((F25&lt;&gt;0),F25-G25," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E26" s="119"/>
+      <c r="G26" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F26&lt;&gt;0,F26*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H26" s="123" t="str">
+        <f aca="false">IF((F26&lt;&gt;0),F26-G26," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E27" s="119"/>
+      <c r="G27" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F27&lt;&gt;0,F27*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H27" s="123" t="str">
+        <f aca="false">IF((F27&lt;&gt;0),F27-G27," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E28" s="119"/>
+      <c r="G28" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F28&lt;&gt;0,F28*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H28" s="123" t="str">
+        <f aca="false">IF((F28&lt;&gt;0),F28-G28," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E29" s="119"/>
+      <c r="G29" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F29&lt;&gt;0,F29*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H29" s="123" t="str">
+        <f aca="false">IF((F29&lt;&gt;0),F29-G29," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E30" s="119"/>
+      <c r="G30" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F30&lt;&gt;0,F30*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H30" s="123" t="str">
+        <f aca="false">IF((F30&lt;&gt;0),F30-G30," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E31" s="119"/>
+      <c r="G31" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F31&lt;&gt;0,F31*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H31" s="123" t="str">
+        <f aca="false">IF((F31&lt;&gt;0),F31-G31," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E32" s="119"/>
+      <c r="G32" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F32&lt;&gt;0,F32*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H32" s="123" t="str">
+        <f aca="false">IF((F32&lt;&gt;0),F32-G32," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E33" s="119"/>
+      <c r="G33" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F33&lt;&gt;0,F33*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H33" s="123" t="str">
+        <f aca="false">IF((F33&lt;&gt;0),F33-G33," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E34" s="119"/>
+      <c r="G34" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F34&lt;&gt;0,F34*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H34" s="123" t="str">
+        <f aca="false">IF((F34&lt;&gt;0),F34-G34," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E35" s="119"/>
+      <c r="G35" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F35&lt;&gt;0,F35*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H35" s="123" t="str">
+        <f aca="false">IF((F35&lt;&gt;0),F35-G35," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E36" s="119"/>
+      <c r="G36" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F36&lt;&gt;0,F36*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H36" s="123" t="str">
+        <f aca="false">IF((F36&lt;&gt;0),F36-G36," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E37" s="119"/>
+      <c r="G37" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F37&lt;&gt;0,F37*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H37" s="123" t="str">
+        <f aca="false">IF((F37&lt;&gt;0),F37-G37," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E38" s="119"/>
+      <c r="G38" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F38&lt;&gt;0,F38*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H38" s="123" t="str">
+        <f aca="false">IF((F38&lt;&gt;0),F38-G38," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E39" s="119"/>
+      <c r="G39" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F39&lt;&gt;0,F39*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H39" s="123" t="str">
+        <f aca="false">IF((F39&lt;&gt;0),F39-G39," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E40" s="119"/>
+      <c r="G40" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F40&lt;&gt;0,F40*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H40" s="123" t="str">
+        <f aca="false">IF((F40&lt;&gt;0),F40-G40," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E41" s="119"/>
+      <c r="G41" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F41&lt;&gt;0,F41*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H41" s="123" t="str">
+        <f aca="false">IF((F41&lt;&gt;0),F41-G41," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E42" s="119"/>
+      <c r="G42" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F42&lt;&gt;0,F42*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H42" s="123" t="str">
+        <f aca="false">IF((F42&lt;&gt;0),F42-G42," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E43" s="119"/>
+      <c r="G43" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F43&lt;&gt;0,F43*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H43" s="123" t="str">
+        <f aca="false">IF((F43&lt;&gt;0),F43-G43," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E44" s="119"/>
+      <c r="G44" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F44&lt;&gt;0,F44*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H44" s="123" t="str">
+        <f aca="false">IF((F44&lt;&gt;0),F44-G44," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E45" s="119"/>
+      <c r="G45" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F45&lt;&gt;0,F45*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H45" s="123" t="str">
+        <f aca="false">IF((F45&lt;&gt;0),F45-G45," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E46" s="119"/>
+      <c r="G46" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F46&lt;&gt;0,F46*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H46" s="123" t="str">
+        <f aca="false">IF((F46&lt;&gt;0),F46-G46," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E47" s="119"/>
+      <c r="G47" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F47&lt;&gt;0,F47*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H47" s="123" t="str">
+        <f aca="false">IF((F47&lt;&gt;0),F47-G47," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E48" s="119"/>
+      <c r="G48" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F48&lt;&gt;0,F48*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H48" s="123" t="str">
+        <f aca="false">IF((F48&lt;&gt;0),F48-G48," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E49" s="119"/>
+      <c r="G49" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F49&lt;&gt;0,F49*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H49" s="123" t="str">
+        <f aca="false">IF((F49&lt;&gt;0),F49-G49," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E50" s="119"/>
+      <c r="G50" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F50&lt;&gt;0,F50*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H50" s="123" t="str">
+        <f aca="false">IF((F50&lt;&gt;0),F50-G50," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E51" s="119"/>
+      <c r="G51" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F51&lt;&gt;0,F51*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H51" s="123" t="str">
+        <f aca="false">IF((F51&lt;&gt;0),F51-G51," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E52" s="119"/>
+      <c r="G52" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F52&lt;&gt;0,F52*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H52" s="123" t="str">
+        <f aca="false">IF((F52&lt;&gt;0),F52-G52," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E53" s="119"/>
+      <c r="G53" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F53&lt;&gt;0,F53*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H53" s="123" t="str">
+        <f aca="false">IF((F53&lt;&gt;0),F53-G53," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E54" s="119"/>
+      <c r="G54" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F54&lt;&gt;0,F54*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H54" s="123" t="str">
+        <f aca="false">IF((F54&lt;&gt;0),F54-G54," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E55" s="119"/>
+      <c r="G55" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F55&lt;&gt;0,F55*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H55" s="123" t="str">
+        <f aca="false">IF((F55&lt;&gt;0),F55-G55," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E56" s="119"/>
+      <c r="G56" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F56&lt;&gt;0,F56*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H56" s="123" t="str">
+        <f aca="false">IF((F56&lt;&gt;0),F56-G56," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E57" s="119"/>
+      <c r="G57" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F57&lt;&gt;0,F57*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H57" s="123" t="str">
+        <f aca="false">IF((F57&lt;&gt;0),F57-G57," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E58" s="119"/>
+      <c r="G58" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F58&lt;&gt;0,F58*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H58" s="123" t="str">
+        <f aca="false">IF((F58&lt;&gt;0),F58-G58," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E59" s="119"/>
+      <c r="G59" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F59&lt;&gt;0,F59*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H59" s="123" t="str">
+        <f aca="false">IF((F59&lt;&gt;0),F59-G59," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E60" s="119"/>
+      <c r="G60" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F60&lt;&gt;0,F60*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H60" s="123" t="str">
+        <f aca="false">IF((F60&lt;&gt;0),F60-G60," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E61" s="119"/>
+      <c r="G61" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F61&lt;&gt;0,F61*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H61" s="123" t="str">
+        <f aca="false">IF((F61&lt;&gt;0),F61-G61," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E62" s="119"/>
+      <c r="G62" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F62&lt;&gt;0,F62*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H62" s="123" t="str">
+        <f aca="false">IF((F62&lt;&gt;0),F62-G62," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E63" s="119"/>
+      <c r="G63" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F63&lt;&gt;0,F63*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H63" s="123" t="str">
+        <f aca="false">IF((F63&lt;&gt;0),F63-G63," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E64" s="119"/>
+      <c r="G64" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F64&lt;&gt;0,F64*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H64" s="123" t="str">
+        <f aca="false">IF((F64&lt;&gt;0),F64-G64," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E65" s="119"/>
+      <c r="G65" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F65&lt;&gt;0,F65*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H65" s="123" t="str">
+        <f aca="false">IF((F65&lt;&gt;0),F65-G65," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E66" s="119"/>
+      <c r="G66" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F66&lt;&gt;0,F66*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H66" s="123" t="str">
+        <f aca="false">IF((F66&lt;&gt;0),F66-G66," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E67" s="119"/>
+      <c r="G67" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F67&lt;&gt;0,F67*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H67" s="123" t="str">
+        <f aca="false">IF((F67&lt;&gt;0),F67-G67," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E68" s="119"/>
+      <c r="G68" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F68&lt;&gt;0,F68*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H68" s="123" t="str">
+        <f aca="false">IF((F68&lt;&gt;0),F68-G68," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E69" s="119"/>
+      <c r="G69" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F69&lt;&gt;0,F69*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H69" s="123" t="str">
+        <f aca="false">IF((F69&lt;&gt;0),F69-G69," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E70" s="119"/>
+      <c r="G70" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F70&lt;&gt;0,F70*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H70" s="123" t="str">
+        <f aca="false">IF((F70&lt;&gt;0),F70-G70," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E71" s="119"/>
+      <c r="G71" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F71&lt;&gt;0,F71*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H71" s="123" t="str">
+        <f aca="false">IF((F71&lt;&gt;0),F71-G71," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E72" s="119"/>
+      <c r="G72" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F72&lt;&gt;0,F72*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H72" s="123" t="str">
+        <f aca="false">IF((F72&lt;&gt;0),F72-G72," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E73" s="119"/>
+      <c r="G73" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F73&lt;&gt;0,F73*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H73" s="123" t="str">
+        <f aca="false">IF((F73&lt;&gt;0),F73-G73," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E74" s="119"/>
+      <c r="G74" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F74&lt;&gt;0,F74*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H74" s="123" t="str">
+        <f aca="false">IF((F74&lt;&gt;0),F74-G74," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E75" s="119"/>
+      <c r="G75" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F75&lt;&gt;0,F75*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H75" s="123" t="str">
+        <f aca="false">IF((F75&lt;&gt;0),F75-G75," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E76" s="119"/>
+      <c r="G76" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F76&lt;&gt;0,F76*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H76" s="123" t="str">
+        <f aca="false">IF((F76&lt;&gt;0),F76-G76," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E77" s="119"/>
+      <c r="G77" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F77&lt;&gt;0,F77*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H77" s="123" t="str">
+        <f aca="false">IF((F77&lt;&gt;0),F77-G77," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E78" s="119"/>
+      <c r="G78" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F78&lt;&gt;0,F78*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H78" s="123" t="str">
+        <f aca="false">IF((F78&lt;&gt;0),F78-G78," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E79" s="119"/>
+      <c r="G79" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F79&lt;&gt;0,F79*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H79" s="123" t="str">
+        <f aca="false">IF((F79&lt;&gt;0),F79-G79," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E80" s="119"/>
+      <c r="G80" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F80&lt;&gt;0,F80*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H80" s="123" t="str">
+        <f aca="false">IF((F80&lt;&gt;0),F80-G80," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E81" s="119"/>
+      <c r="G81" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F81&lt;&gt;0,F81*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H81" s="123" t="str">
+        <f aca="false">IF((F81&lt;&gt;0),F81-G81," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E82" s="119"/>
+      <c r="G82" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F82&lt;&gt;0,F82*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H82" s="123" t="str">
+        <f aca="false">IF((F82&lt;&gt;0),F82-G82," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E83" s="119"/>
+      <c r="G83" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F83&lt;&gt;0,F83*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H83" s="123" t="str">
+        <f aca="false">IF((F83&lt;&gt;0),F83-G83," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E84" s="119"/>
+      <c r="G84" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F84&lt;&gt;0,F84*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H84" s="123" t="str">
+        <f aca="false">IF((F84&lt;&gt;0),F84-G84," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E85" s="119"/>
+      <c r="G85" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F85&lt;&gt;0,F85*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H85" s="123" t="str">
+        <f aca="false">IF((F85&lt;&gt;0),F85-G85," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E86" s="119"/>
+      <c r="G86" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F86&lt;&gt;0,F86*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H86" s="123" t="str">
+        <f aca="false">IF((F86&lt;&gt;0),F86-G86," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E87" s="119"/>
+      <c r="G87" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F87&lt;&gt;0,F87*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H87" s="123" t="str">
+        <f aca="false">IF((F87&lt;&gt;0),F87-G87," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E88" s="119"/>
+      <c r="G88" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F88&lt;&gt;0,F88*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H88" s="123" t="str">
+        <f aca="false">IF((F88&lt;&gt;0),F88-G88," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E89" s="119"/>
+      <c r="G89" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F89&lt;&gt;0,F89*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H89" s="123" t="str">
+        <f aca="false">IF((F89&lt;&gt;0),F89-G89," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E90" s="119"/>
+      <c r="G90" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F90&lt;&gt;0,F90*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H90" s="123" t="str">
+        <f aca="false">IF((F90&lt;&gt;0),F90-G90," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E91" s="119"/>
+      <c r="G91" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F91&lt;&gt;0,F91*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H91" s="123" t="str">
+        <f aca="false">IF((F91&lt;&gt;0),F91-G91," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E92" s="119"/>
+      <c r="G92" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F92&lt;&gt;0,F92*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H92" s="123" t="str">
+        <f aca="false">IF((F92&lt;&gt;0),F92-G92," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E93" s="119"/>
+      <c r="G93" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F93&lt;&gt;0,F93*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H93" s="123" t="str">
+        <f aca="false">IF((F93&lt;&gt;0),F93-G93," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E94" s="119"/>
+      <c r="G94" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F94&lt;&gt;0,F94*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H94" s="123" t="str">
+        <f aca="false">IF((F94&lt;&gt;0),F94-G94," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E95" s="119"/>
+      <c r="G95" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F95&lt;&gt;0,F95*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H95" s="123" t="str">
+        <f aca="false">IF((F95&lt;&gt;0),F95-G95," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E96" s="119"/>
+      <c r="G96" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F96&lt;&gt;0,F96*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H96" s="123" t="str">
+        <f aca="false">IF((F96&lt;&gt;0),F96-G96," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E97" s="119"/>
+      <c r="G97" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F97&lt;&gt;0,F97*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H97" s="123" t="str">
+        <f aca="false">IF((F97&lt;&gt;0),F97-G97," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E98" s="119"/>
+      <c r="G98" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F98&lt;&gt;0,F98*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H98" s="123" t="str">
+        <f aca="false">IF((F98&lt;&gt;0),F98-G98," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E99" s="119"/>
+      <c r="G99" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F99&lt;&gt;0,F99*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H99" s="123" t="str">
+        <f aca="false">IF((F99&lt;&gt;0),F99-G99," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E100" s="119"/>
+      <c r="G100" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F100&lt;&gt;0,F100*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H100" s="123" t="str">
+        <f aca="false">IF((F100&lt;&gt;0),F100-G100," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E101" s="119"/>
+      <c r="G101" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F101&lt;&gt;0,F101*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H101" s="123" t="str">
+        <f aca="false">IF((F101&lt;&gt;0),F101-G101," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E102" s="119"/>
+      <c r="G102" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F102&lt;&gt;0,F102*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H102" s="123" t="str">
+        <f aca="false">IF((F102&lt;&gt;0),F102-G102," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E103" s="119"/>
+      <c r="G103" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F103&lt;&gt;0,F103*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H103" s="123" t="str">
+        <f aca="false">IF((F103&lt;&gt;0),F103-G103," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E104" s="119"/>
+      <c r="G104" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F104&lt;&gt;0,F104*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H104" s="123" t="str">
+        <f aca="false">IF((F104&lt;&gt;0),F104-G104," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E105" s="119"/>
+      <c r="G105" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F105&lt;&gt;0,F105*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H105" s="123" t="str">
+        <f aca="false">IF((F105&lt;&gt;0),F105-G105," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E106" s="119"/>
+      <c r="G106" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F106&lt;&gt;0,F106*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H106" s="123" t="str">
+        <f aca="false">IF((F106&lt;&gt;0),F106-G106," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E107" s="119"/>
+      <c r="G107" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F107&lt;&gt;0,F107*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H107" s="123" t="str">
+        <f aca="false">IF((F107&lt;&gt;0),F107-G107," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E108" s="119"/>
+      <c r="G108" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F108&lt;&gt;0,F108*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H108" s="123" t="str">
+        <f aca="false">IF((F108&lt;&gt;0),F108-G108," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E109" s="119"/>
+      <c r="G109" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F109&lt;&gt;0,F109*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H109" s="123" t="str">
+        <f aca="false">IF((F109&lt;&gt;0),F109-G109," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E110" s="119"/>
+      <c r="G110" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F110&lt;&gt;0,F110*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H110" s="123" t="str">
+        <f aca="false">IF((F110&lt;&gt;0),F110-G110," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E111" s="119"/>
+      <c r="G111" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F111&lt;&gt;0,F111*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H111" s="123" t="str">
+        <f aca="false">IF((F111&lt;&gt;0),F111-G111," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E112" s="119"/>
+      <c r="G112" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F112&lt;&gt;0,F112*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H112" s="123" t="str">
+        <f aca="false">IF((F112&lt;&gt;0),F112-G112," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E113" s="119"/>
+      <c r="G113" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F113&lt;&gt;0,F113*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H113" s="123" t="str">
+        <f aca="false">IF((F113&lt;&gt;0),F113-G113," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E114" s="119"/>
+      <c r="G114" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F114&lt;&gt;0,F114*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H114" s="123" t="str">
+        <f aca="false">IF((F114&lt;&gt;0),F114-G114," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E115" s="119"/>
+      <c r="G115" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F115&lt;&gt;0,F115*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H115" s="123" t="str">
+        <f aca="false">IF((F115&lt;&gt;0),F115-G115," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E116" s="119"/>
+      <c r="G116" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F116&lt;&gt;0,F116*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H116" s="123" t="str">
+        <f aca="false">IF((F116&lt;&gt;0),F116-G116," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E117" s="119"/>
+      <c r="G117" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F117&lt;&gt;0,F117*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H117" s="123" t="str">
+        <f aca="false">IF((F117&lt;&gt;0),F117-G117," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E118" s="119"/>
+      <c r="G118" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F118&lt;&gt;0,F118*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H118" s="123" t="str">
+        <f aca="false">IF((F118&lt;&gt;0),F118-G118," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E119" s="119"/>
+      <c r="G119" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F119&lt;&gt;0,F119*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H119" s="123" t="str">
+        <f aca="false">IF((F119&lt;&gt;0),F119-G119," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E120" s="119"/>
+      <c r="G120" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F120&lt;&gt;0,F120*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H120" s="123" t="str">
+        <f aca="false">IF((F120&lt;&gt;0),F120-G120," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E121" s="119"/>
+      <c r="G121" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F121&lt;&gt;0,F121*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H121" s="123" t="str">
+        <f aca="false">IF((F121&lt;&gt;0),F121-G121," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E122" s="119"/>
+      <c r="G122" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F122&lt;&gt;0,F122*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H122" s="123" t="str">
+        <f aca="false">IF((F122&lt;&gt;0),F122-G122," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E123" s="119"/>
+      <c r="G123" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F123&lt;&gt;0,F123*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H123" s="123" t="str">
+        <f aca="false">IF((F123&lt;&gt;0),F123-G123," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E124" s="119"/>
+      <c r="G124" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F124&lt;&gt;0,F124*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H124" s="123" t="str">
+        <f aca="false">IF((F124&lt;&gt;0),F124-G124," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E125" s="119"/>
+      <c r="G125" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F125&lt;&gt;0,F125*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H125" s="123" t="str">
+        <f aca="false">IF((F125&lt;&gt;0),F125-G125," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E126" s="119"/>
+      <c r="G126" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F126&lt;&gt;0,F126*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H126" s="123" t="str">
+        <f aca="false">IF((F126&lt;&gt;0),F126-G126," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E127" s="119"/>
+      <c r="G127" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F127&lt;&gt;0,F127*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H127" s="123" t="str">
+        <f aca="false">IF((F127&lt;&gt;0),F127-G127," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E128" s="119"/>
+      <c r="G128" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F128&lt;&gt;0,F128*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H128" s="123" t="str">
+        <f aca="false">IF((F128&lt;&gt;0),F128-G128," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E129" s="119"/>
+      <c r="G129" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F129&lt;&gt;0,F129*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H129" s="123" t="str">
+        <f aca="false">IF((F129&lt;&gt;0),F129-G129," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E130" s="119"/>
+      <c r="G130" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F130&lt;&gt;0,F130*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H130" s="123" t="str">
+        <f aca="false">IF((F130&lt;&gt;0),F130-G130," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E131" s="119"/>
+      <c r="G131" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F131&lt;&gt;0,F131*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H131" s="123" t="str">
+        <f aca="false">IF((F131&lt;&gt;0),F131-G131," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E132" s="119"/>
+      <c r="G132" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F132&lt;&gt;0,F132*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H132" s="123" t="str">
+        <f aca="false">IF((F132&lt;&gt;0),F132-G132," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E133" s="119"/>
+      <c r="G133" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F133&lt;&gt;0,F133*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H133" s="123" t="str">
+        <f aca="false">IF((F133&lt;&gt;0),F133-G133," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E134" s="119"/>
+      <c r="G134" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F134&lt;&gt;0,F134*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H134" s="123" t="str">
+        <f aca="false">IF((F134&lt;&gt;0),F134-G134," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E135" s="119"/>
+      <c r="G135" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F135&lt;&gt;0,F135*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H135" s="123" t="str">
+        <f aca="false">IF((F135&lt;&gt;0),F135-G135," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E136" s="119"/>
+      <c r="G136" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F136&lt;&gt;0,F136*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H136" s="123" t="str">
+        <f aca="false">IF((F136&lt;&gt;0),F136-G136," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E137" s="119"/>
+      <c r="G137" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F137&lt;&gt;0,F137*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H137" s="123" t="str">
+        <f aca="false">IF((F137&lt;&gt;0),F137-G137," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E138" s="119"/>
+      <c r="G138" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F138&lt;&gt;0,F138*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H138" s="123" t="str">
+        <f aca="false">IF((F138&lt;&gt;0),F138-G138," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E139" s="119"/>
+      <c r="G139" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F139&lt;&gt;0,F139*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H139" s="123" t="str">
+        <f aca="false">IF((F139&lt;&gt;0),F139-G139," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E140" s="119"/>
+      <c r="G140" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F140&lt;&gt;0,F140*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H140" s="123" t="str">
+        <f aca="false">IF((F140&lt;&gt;0),F140-G140," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E141" s="119"/>
+      <c r="G141" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F141&lt;&gt;0,F141*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H141" s="123" t="str">
+        <f aca="false">IF((F141&lt;&gt;0),F141-G141," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E142" s="119"/>
+      <c r="G142" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F142&lt;&gt;0,F142*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H142" s="123" t="str">
+        <f aca="false">IF((F142&lt;&gt;0),F142-G142," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E143" s="119"/>
+      <c r="G143" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F143&lt;&gt;0,F143*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H143" s="123" t="str">
+        <f aca="false">IF((F143&lt;&gt;0),F143-G143," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E144" s="119"/>
+      <c r="G144" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F144&lt;&gt;0,F144*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H144" s="123" t="str">
+        <f aca="false">IF((F144&lt;&gt;0),F144-G144," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E145" s="119"/>
+      <c r="G145" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F145&lt;&gt;0,F145*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H145" s="123" t="str">
+        <f aca="false">IF((F145&lt;&gt;0),F145-G145," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E146" s="119"/>
+      <c r="G146" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F146&lt;&gt;0,F146*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H146" s="123" t="str">
+        <f aca="false">IF((F146&lt;&gt;0),F146-G146," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E147" s="119"/>
+      <c r="G147" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F147&lt;&gt;0,F147*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H147" s="123" t="str">
+        <f aca="false">IF((F147&lt;&gt;0),F147-G147," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E148" s="119"/>
+      <c r="G148" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F148&lt;&gt;0,F148*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H148" s="123" t="str">
+        <f aca="false">IF((F148&lt;&gt;0),F148-G148," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E149" s="119"/>
+      <c r="G149" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F149&lt;&gt;0,F149*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H149" s="123" t="str">
+        <f aca="false">IF((F149&lt;&gt;0),F149-G149," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E150" s="119"/>
+      <c r="G150" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F150&lt;&gt;0,F150*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H150" s="123" t="str">
+        <f aca="false">IF((F150&lt;&gt;0),F150-G150," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E151" s="119"/>
+      <c r="G151" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F151&lt;&gt;0,F151*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H151" s="123" t="str">
+        <f aca="false">IF((F151&lt;&gt;0),F151-G151," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E152" s="119"/>
+      <c r="G152" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F152&lt;&gt;0,F152*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H152" s="123" t="str">
+        <f aca="false">IF((F152&lt;&gt;0),F152-G152," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E153" s="119"/>
+      <c r="G153" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F153&lt;&gt;0,F153*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H153" s="123" t="str">
+        <f aca="false">IF((F153&lt;&gt;0),F153-G153," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E154" s="119"/>
+      <c r="G154" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F154&lt;&gt;0,F154*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H154" s="123" t="str">
+        <f aca="false">IF((F154&lt;&gt;0),F154-G154," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E155" s="119"/>
+      <c r="G155" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F155&lt;&gt;0,F155*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H155" s="123" t="str">
+        <f aca="false">IF((F155&lt;&gt;0),F155-G155," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E156" s="119"/>
+      <c r="G156" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F156&lt;&gt;0,F156*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H156" s="123" t="str">
+        <f aca="false">IF((F156&lt;&gt;0),F156-G156," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E157" s="119"/>
+      <c r="G157" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F157&lt;&gt;0,F157*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H157" s="123" t="str">
+        <f aca="false">IF((F157&lt;&gt;0),F157-G157," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E158" s="119"/>
+      <c r="G158" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F158&lt;&gt;0,F158*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H158" s="123" t="str">
+        <f aca="false">IF((F158&lt;&gt;0),F158-G158," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E159" s="119"/>
+      <c r="G159" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F159&lt;&gt;0,F159*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H159" s="123" t="str">
+        <f aca="false">IF((F159&lt;&gt;0),F159-G159," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E160" s="119"/>
+      <c r="G160" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F160&lt;&gt;0,F160*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H160" s="123" t="str">
+        <f aca="false">IF((F160&lt;&gt;0),F160-G160," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E161" s="119"/>
+      <c r="G161" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F161&lt;&gt;0,F161*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H161" s="123" t="str">
+        <f aca="false">IF((F161&lt;&gt;0),F161-G161," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E162" s="119"/>
+      <c r="G162" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F162&lt;&gt;0,F162*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H162" s="123" t="str">
+        <f aca="false">IF((F162&lt;&gt;0),F162-G162," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E163" s="119"/>
+      <c r="G163" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F163&lt;&gt;0,F163*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H163" s="123" t="str">
+        <f aca="false">IF((F163&lt;&gt;0),F163-G163," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E164" s="119"/>
+      <c r="G164" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F164&lt;&gt;0,F164*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H164" s="123" t="str">
+        <f aca="false">IF((F164&lt;&gt;0),F164-G164," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E165" s="119"/>
+      <c r="G165" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F165&lt;&gt;0,F165*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H165" s="123" t="str">
+        <f aca="false">IF((F165&lt;&gt;0),F165-G165," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E166" s="119"/>
+      <c r="G166" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F166&lt;&gt;0,F166*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H166" s="123" t="str">
+        <f aca="false">IF((F166&lt;&gt;0),F166-G166," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E167" s="119"/>
+      <c r="G167" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F167&lt;&gt;0,F167*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H167" s="123" t="str">
+        <f aca="false">IF((F167&lt;&gt;0),F167-G167," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E168" s="119"/>
+      <c r="G168" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F168&lt;&gt;0,F168*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H168" s="123" t="str">
+        <f aca="false">IF((F168&lt;&gt;0),F168-G168," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E169" s="119"/>
+      <c r="G169" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F169&lt;&gt;0,F169*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H169" s="123" t="str">
+        <f aca="false">IF((F169&lt;&gt;0),F169-G169," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E170" s="119"/>
+      <c r="G170" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F170&lt;&gt;0,F170*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H170" s="123" t="str">
+        <f aca="false">IF((F170&lt;&gt;0),F170-G170," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E171" s="119"/>
+      <c r="G171" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F171&lt;&gt;0,F171*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H171" s="123" t="str">
+        <f aca="false">IF((F171&lt;&gt;0),F171-G171," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E172" s="119"/>
+      <c r="G172" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F172&lt;&gt;0,F172*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H172" s="123" t="str">
+        <f aca="false">IF((F172&lt;&gt;0),F172-G172," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E173" s="119"/>
+      <c r="G173" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F173&lt;&gt;0,F173*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H173" s="123" t="str">
+        <f aca="false">IF((F173&lt;&gt;0),F173-G173," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E174" s="119"/>
+      <c r="G174" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F174&lt;&gt;0,F174*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H174" s="123" t="str">
+        <f aca="false">IF((F174&lt;&gt;0),F174-G174," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E175" s="119"/>
+      <c r="G175" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F175&lt;&gt;0,F175*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H175" s="123" t="str">
+        <f aca="false">IF((F175&lt;&gt;0),F175-G175," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E176" s="119"/>
+      <c r="G176" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F176&lt;&gt;0,F176*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H176" s="123" t="str">
+        <f aca="false">IF((F176&lt;&gt;0),F176-G176," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E177" s="119"/>
+      <c r="G177" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F177&lt;&gt;0,F177*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H177" s="123" t="str">
+        <f aca="false">IF((F177&lt;&gt;0),F177-G177," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E178" s="119"/>
+      <c r="G178" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F178&lt;&gt;0,F178*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H178" s="123" t="str">
+        <f aca="false">IF((F178&lt;&gt;0),F178-G178," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E179" s="119"/>
+      <c r="G179" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F179&lt;&gt;0,F179*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H179" s="123" t="str">
+        <f aca="false">IF((F179&lt;&gt;0),F179-G179," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E180" s="119"/>
+      <c r="G180" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F180&lt;&gt;0,F180*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H180" s="123" t="str">
+        <f aca="false">IF((F180&lt;&gt;0),F180-G180," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E181" s="119"/>
+      <c r="G181" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F181&lt;&gt;0,F181*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H181" s="123" t="str">
+        <f aca="false">IF((F181&lt;&gt;0),F181-G181," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E182" s="119"/>
+      <c r="G182" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F182&lt;&gt;0,F182*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H182" s="123" t="str">
+        <f aca="false">IF((F182&lt;&gt;0),F182-G182," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E183" s="119"/>
+      <c r="G183" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F183&lt;&gt;0,F183*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H183" s="123" t="str">
+        <f aca="false">IF((F183&lt;&gt;0),F183-G183," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E184" s="119"/>
+      <c r="G184" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F184&lt;&gt;0,F184*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H184" s="123" t="str">
+        <f aca="false">IF((F184&lt;&gt;0),F184-G184," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E185" s="119"/>
+      <c r="G185" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F185&lt;&gt;0,F185*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H185" s="123" t="str">
+        <f aca="false">IF((F185&lt;&gt;0),F185-G185," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E186" s="119"/>
+      <c r="G186" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F186&lt;&gt;0,F186*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H186" s="123" t="str">
+        <f aca="false">IF((F186&lt;&gt;0),F186-G186," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E187" s="119"/>
+      <c r="G187" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F187&lt;&gt;0,F187*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H187" s="123" t="str">
+        <f aca="false">IF((F187&lt;&gt;0),F187-G187," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E188" s="119"/>
+      <c r="G188" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F188&lt;&gt;0,F188*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H188" s="123" t="str">
+        <f aca="false">IF((F188&lt;&gt;0),F188-G188," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E189" s="119"/>
+      <c r="G189" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F189&lt;&gt;0,F189*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H189" s="123" t="str">
+        <f aca="false">IF((F189&lt;&gt;0),F189-G189," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E190" s="119"/>
+      <c r="G190" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F190&lt;&gt;0,F190*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H190" s="123" t="str">
+        <f aca="false">IF((F190&lt;&gt;0),F190-G190," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E191" s="119"/>
+      <c r="G191" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F191&lt;&gt;0,F191*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H191" s="123" t="str">
+        <f aca="false">IF((F191&lt;&gt;0),F191-G191," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E192" s="119"/>
+      <c r="G192" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F192&lt;&gt;0,F192*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H192" s="123" t="str">
+        <f aca="false">IF((F192&lt;&gt;0),F192-G192," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E193" s="119"/>
+      <c r="G193" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F193&lt;&gt;0,F193*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H193" s="123" t="str">
+        <f aca="false">IF((F193&lt;&gt;0),F193-G193," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E194" s="119"/>
+      <c r="G194" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F194&lt;&gt;0,F194*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H194" s="123" t="str">
+        <f aca="false">IF((F194&lt;&gt;0),F194-G194," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E195" s="119"/>
+      <c r="G195" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F195&lt;&gt;0,F195*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H195" s="123" t="str">
+        <f aca="false">IF((F195&lt;&gt;0),F195-G195," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E196" s="119"/>
+      <c r="G196" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F196&lt;&gt;0,F196*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H196" s="123" t="str">
+        <f aca="false">IF((F196&lt;&gt;0),F196-G196," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E197" s="119"/>
+      <c r="G197" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F197&lt;&gt;0,F197*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H197" s="123" t="str">
+        <f aca="false">IF((F197&lt;&gt;0),F197-G197," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E198" s="119"/>
+      <c r="G198" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F198&lt;&gt;0,F198*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H198" s="123" t="str">
+        <f aca="false">IF((F198&lt;&gt;0),F198-G198," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E199" s="119"/>
+      <c r="G199" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F199&lt;&gt;0,F199*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H199" s="123" t="str">
+        <f aca="false">IF((F199&lt;&gt;0),F199-G199," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="132"/>
+      <c r="B200" s="133"/>
+      <c r="C200" s="134"/>
+      <c r="D200" s="135"/>
+      <c r="E200" s="133"/>
+      <c r="F200" s="136"/>
+      <c r="G200" s="136" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F200&lt;&gt;0,F200*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H200" s="136" t="str">
+        <f aca="false">IF((F200&lt;&gt;0),F200-G200," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="98" t="s">
+        <v>40</v>
+      </c>
+      <c r="G201" s="123" t="e">
+        <f aca="false">NA()</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="G3:G4"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H201"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="118" width="8.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="119" width="19.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="120" width="12.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="121" width="14.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="122" width="5.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="123" width="10.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="123" width="9.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="123" width="10.66"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="9" style="119" width="9.15"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="102" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="103" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105" t="n">
+        <f aca="false">SUM(F5:F200)</f>
+        <v>360</v>
+      </c>
+      <c r="G1" s="105" t="n">
+        <f aca="false">SUM(G5:G200)</f>
+        <v>60</v>
+      </c>
+      <c r="H1" s="105" t="n">
+        <f aca="false">SUM(H5:H200)</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" s="127" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="107" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="108" t="str">
+        <f aca="false">IF((H1-SUM(O1:AK1)&lt;&gt;0),"COMPLETE EXPENSE ANALYSIS by inserting expense letter in col F","Supplier")</f>
+        <v>COMPLETE EXPENSE ANALYSIS by inserting expense letter in col F</v>
+      </c>
+      <c r="C2" s="110" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="124" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="125"/>
+      <c r="F2" s="108" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" s="126" t="n">
+        <f aca="false">[3]ClosingCreditors!$G$2</f>
+        <v>20</v>
+      </c>
+      <c r="H2" s="108" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" s="128" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="107"/>
+      <c r="B3" s="107"/>
+      <c r="C3" s="107"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="108" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" s="108"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="107"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="124"/>
+      <c r="E4" s="125"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="108"/>
+    </row>
+    <row r="5" s="119" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="118" t="n">
         <v>46345</v>
       </c>
       <c r="B5" s="122" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C5" s="129" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D5" s="122"/>
       <c r="F5" s="130" t="n">
@@ -11504,6 +13616,2303 @@
       <c r="H5" s="123" t="n">
         <f aca="false">IF((F5&lt;&gt;0),F5-G5," ")</f>
         <v>300</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E6" s="119"/>
+      <c r="G6" s="123" t="str">
+        <f aca="false">IF(F6&lt;&gt;0,F6*G$2/(100+G$2)," ")</f>
+        <v> </v>
+      </c>
+      <c r="H6" s="123" t="str">
+        <f aca="false">IF((F6&lt;&gt;0),F6-G6," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E7" s="119"/>
+      <c r="G7" s="123" t="str">
+        <f aca="false">IF(F7&lt;&gt;0,F7*G$2/(100+G$2)," ")</f>
+        <v> </v>
+      </c>
+      <c r="H7" s="123" t="str">
+        <f aca="false">IF((F7&lt;&gt;0),F7-G7," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E8" s="119"/>
+      <c r="G8" s="123" t="str">
+        <f aca="false">IF(F8&lt;&gt;0,F8*G$2/(100+G$2)," ")</f>
+        <v> </v>
+      </c>
+      <c r="H8" s="123" t="str">
+        <f aca="false">IF((F8&lt;&gt;0),F8-G8," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E9" s="119"/>
+      <c r="G9" s="123" t="str">
+        <f aca="false">IF(F9&lt;&gt;0,F9*G$2/(100+G$2)," ")</f>
+        <v> </v>
+      </c>
+      <c r="H9" s="123" t="str">
+        <f aca="false">IF((F9&lt;&gt;0),F9-G9," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E10" s="119"/>
+      <c r="G10" s="123" t="str">
+        <f aca="false">IF(F10&lt;&gt;0,F10*G$2/(100+G$2)," ")</f>
+        <v> </v>
+      </c>
+      <c r="H10" s="123" t="str">
+        <f aca="false">IF((F10&lt;&gt;0),F10-G10," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E11" s="119"/>
+      <c r="G11" s="123" t="str">
+        <f aca="false">IF(F11&lt;&gt;0,F11*G$2/(100+G$2)," ")</f>
+        <v> </v>
+      </c>
+      <c r="H11" s="123" t="str">
+        <f aca="false">IF((F11&lt;&gt;0),F11-G11," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E12" s="119"/>
+      <c r="G12" s="123" t="str">
+        <f aca="false">IF(F12&lt;&gt;0,F12*G$2/(100+G$2)," ")</f>
+        <v> </v>
+      </c>
+      <c r="H12" s="123" t="str">
+        <f aca="false">IF((F12&lt;&gt;0),F12-G12," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E13" s="119"/>
+      <c r="G13" s="123" t="str">
+        <f aca="false">IF(F13&lt;&gt;0,F13*G$2/(100+G$2)," ")</f>
+        <v> </v>
+      </c>
+      <c r="H13" s="123" t="str">
+        <f aca="false">IF((F13&lt;&gt;0),F13-G13," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E14" s="119"/>
+      <c r="G14" s="123" t="str">
+        <f aca="false">IF(F14&lt;&gt;0,F14*G$2/(100+G$2)," ")</f>
+        <v> </v>
+      </c>
+      <c r="H14" s="123" t="str">
+        <f aca="false">IF((F14&lt;&gt;0),F14-G14," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E15" s="119"/>
+      <c r="G15" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F15&lt;&gt;0,F15*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H15" s="123" t="str">
+        <f aca="false">IF((F15&lt;&gt;0),F15-G15," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E16" s="119"/>
+      <c r="G16" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F16&lt;&gt;0,F16*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H16" s="123" t="str">
+        <f aca="false">IF((F16&lt;&gt;0),F16-G16," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E17" s="119"/>
+      <c r="G17" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F17&lt;&gt;0,F17*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H17" s="123" t="str">
+        <f aca="false">IF((F17&lt;&gt;0),F17-G17," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E18" s="119"/>
+      <c r="G18" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F18&lt;&gt;0,F18*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H18" s="123" t="str">
+        <f aca="false">IF((F18&lt;&gt;0),F18-G18," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E19" s="119"/>
+      <c r="G19" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F19&lt;&gt;0,F19*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H19" s="123" t="str">
+        <f aca="false">IF((F19&lt;&gt;0),F19-G19," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E20" s="119"/>
+      <c r="G20" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F20&lt;&gt;0,F20*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H20" s="123" t="str">
+        <f aca="false">IF((F20&lt;&gt;0),F20-G20," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E21" s="119"/>
+      <c r="G21" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F21&lt;&gt;0,F21*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H21" s="123" t="str">
+        <f aca="false">IF((F21&lt;&gt;0),F21-G21," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D22" s="119"/>
+      <c r="E22" s="119"/>
+      <c r="G22" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F22&lt;&gt;0,F22*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H22" s="123" t="str">
+        <f aca="false">IF((F22&lt;&gt;0),F22-G22," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D23" s="131"/>
+      <c r="E23" s="119"/>
+      <c r="G23" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F23&lt;&gt;0,F23*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H23" s="123" t="str">
+        <f aca="false">IF((F23&lt;&gt;0),F23-G23," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E24" s="119"/>
+      <c r="G24" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F24&lt;&gt;0,F24*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H24" s="123" t="str">
+        <f aca="false">IF((F24&lt;&gt;0),F24-G24," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E25" s="119"/>
+      <c r="G25" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F25&lt;&gt;0,F25*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H25" s="123" t="str">
+        <f aca="false">IF((F25&lt;&gt;0),F25-G25," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E26" s="119"/>
+      <c r="G26" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F26&lt;&gt;0,F26*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H26" s="123" t="str">
+        <f aca="false">IF((F26&lt;&gt;0),F26-G26," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E27" s="119"/>
+      <c r="G27" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F27&lt;&gt;0,F27*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H27" s="123" t="str">
+        <f aca="false">IF((F27&lt;&gt;0),F27-G27," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E28" s="119"/>
+      <c r="G28" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F28&lt;&gt;0,F28*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H28" s="123" t="str">
+        <f aca="false">IF((F28&lt;&gt;0),F28-G28," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E29" s="119"/>
+      <c r="G29" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F29&lt;&gt;0,F29*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H29" s="123" t="str">
+        <f aca="false">IF((F29&lt;&gt;0),F29-G29," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E30" s="119"/>
+      <c r="G30" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F30&lt;&gt;0,F30*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H30" s="123" t="str">
+        <f aca="false">IF((F30&lt;&gt;0),F30-G30," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E31" s="119"/>
+      <c r="G31" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F31&lt;&gt;0,F31*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H31" s="123" t="str">
+        <f aca="false">IF((F31&lt;&gt;0),F31-G31," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E32" s="119"/>
+      <c r="G32" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F32&lt;&gt;0,F32*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H32" s="123" t="str">
+        <f aca="false">IF((F32&lt;&gt;0),F32-G32," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E33" s="119"/>
+      <c r="G33" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F33&lt;&gt;0,F33*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H33" s="123" t="str">
+        <f aca="false">IF((F33&lt;&gt;0),F33-G33," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E34" s="119"/>
+      <c r="G34" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F34&lt;&gt;0,F34*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H34" s="123" t="str">
+        <f aca="false">IF((F34&lt;&gt;0),F34-G34," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E35" s="119"/>
+      <c r="G35" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F35&lt;&gt;0,F35*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H35" s="123" t="str">
+        <f aca="false">IF((F35&lt;&gt;0),F35-G35," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E36" s="119"/>
+      <c r="G36" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F36&lt;&gt;0,F36*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H36" s="123" t="str">
+        <f aca="false">IF((F36&lt;&gt;0),F36-G36," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E37" s="119"/>
+      <c r="G37" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F37&lt;&gt;0,F37*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H37" s="123" t="str">
+        <f aca="false">IF((F37&lt;&gt;0),F37-G37," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E38" s="119"/>
+      <c r="G38" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F38&lt;&gt;0,F38*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H38" s="123" t="str">
+        <f aca="false">IF((F38&lt;&gt;0),F38-G38," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E39" s="119"/>
+      <c r="G39" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F39&lt;&gt;0,F39*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H39" s="123" t="str">
+        <f aca="false">IF((F39&lt;&gt;0),F39-G39," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E40" s="119"/>
+      <c r="G40" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F40&lt;&gt;0,F40*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H40" s="123" t="str">
+        <f aca="false">IF((F40&lt;&gt;0),F40-G40," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E41" s="119"/>
+      <c r="G41" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F41&lt;&gt;0,F41*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H41" s="123" t="str">
+        <f aca="false">IF((F41&lt;&gt;0),F41-G41," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E42" s="119"/>
+      <c r="G42" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F42&lt;&gt;0,F42*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H42" s="123" t="str">
+        <f aca="false">IF((F42&lt;&gt;0),F42-G42," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E43" s="119"/>
+      <c r="G43" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F43&lt;&gt;0,F43*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H43" s="123" t="str">
+        <f aca="false">IF((F43&lt;&gt;0),F43-G43," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E44" s="119"/>
+      <c r="G44" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F44&lt;&gt;0,F44*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H44" s="123" t="str">
+        <f aca="false">IF((F44&lt;&gt;0),F44-G44," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E45" s="119"/>
+      <c r="G45" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F45&lt;&gt;0,F45*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H45" s="123" t="str">
+        <f aca="false">IF((F45&lt;&gt;0),F45-G45," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E46" s="119"/>
+      <c r="G46" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F46&lt;&gt;0,F46*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H46" s="123" t="str">
+        <f aca="false">IF((F46&lt;&gt;0),F46-G46," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E47" s="119"/>
+      <c r="G47" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F47&lt;&gt;0,F47*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H47" s="123" t="str">
+        <f aca="false">IF((F47&lt;&gt;0),F47-G47," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E48" s="119"/>
+      <c r="G48" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F48&lt;&gt;0,F48*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H48" s="123" t="str">
+        <f aca="false">IF((F48&lt;&gt;0),F48-G48," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E49" s="119"/>
+      <c r="G49" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F49&lt;&gt;0,F49*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H49" s="123" t="str">
+        <f aca="false">IF((F49&lt;&gt;0),F49-G49," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E50" s="119"/>
+      <c r="G50" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F50&lt;&gt;0,F50*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H50" s="123" t="str">
+        <f aca="false">IF((F50&lt;&gt;0),F50-G50," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E51" s="119"/>
+      <c r="G51" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F51&lt;&gt;0,F51*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H51" s="123" t="str">
+        <f aca="false">IF((F51&lt;&gt;0),F51-G51," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E52" s="119"/>
+      <c r="G52" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F52&lt;&gt;0,F52*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H52" s="123" t="str">
+        <f aca="false">IF((F52&lt;&gt;0),F52-G52," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E53" s="119"/>
+      <c r="G53" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F53&lt;&gt;0,F53*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H53" s="123" t="str">
+        <f aca="false">IF((F53&lt;&gt;0),F53-G53," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E54" s="119"/>
+      <c r="G54" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F54&lt;&gt;0,F54*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H54" s="123" t="str">
+        <f aca="false">IF((F54&lt;&gt;0),F54-G54," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E55" s="119"/>
+      <c r="G55" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F55&lt;&gt;0,F55*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H55" s="123" t="str">
+        <f aca="false">IF((F55&lt;&gt;0),F55-G55," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E56" s="119"/>
+      <c r="G56" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F56&lt;&gt;0,F56*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H56" s="123" t="str">
+        <f aca="false">IF((F56&lt;&gt;0),F56-G56," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E57" s="119"/>
+      <c r="G57" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F57&lt;&gt;0,F57*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H57" s="123" t="str">
+        <f aca="false">IF((F57&lt;&gt;0),F57-G57," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E58" s="119"/>
+      <c r="G58" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F58&lt;&gt;0,F58*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H58" s="123" t="str">
+        <f aca="false">IF((F58&lt;&gt;0),F58-G58," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E59" s="119"/>
+      <c r="G59" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F59&lt;&gt;0,F59*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H59" s="123" t="str">
+        <f aca="false">IF((F59&lt;&gt;0),F59-G59," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E60" s="119"/>
+      <c r="G60" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F60&lt;&gt;0,F60*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H60" s="123" t="str">
+        <f aca="false">IF((F60&lt;&gt;0),F60-G60," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E61" s="119"/>
+      <c r="G61" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F61&lt;&gt;0,F61*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H61" s="123" t="str">
+        <f aca="false">IF((F61&lt;&gt;0),F61-G61," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E62" s="119"/>
+      <c r="G62" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F62&lt;&gt;0,F62*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H62" s="123" t="str">
+        <f aca="false">IF((F62&lt;&gt;0),F62-G62," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E63" s="119"/>
+      <c r="G63" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F63&lt;&gt;0,F63*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H63" s="123" t="str">
+        <f aca="false">IF((F63&lt;&gt;0),F63-G63," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E64" s="119"/>
+      <c r="G64" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F64&lt;&gt;0,F64*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H64" s="123" t="str">
+        <f aca="false">IF((F64&lt;&gt;0),F64-G64," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E65" s="119"/>
+      <c r="G65" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F65&lt;&gt;0,F65*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H65" s="123" t="str">
+        <f aca="false">IF((F65&lt;&gt;0),F65-G65," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E66" s="119"/>
+      <c r="G66" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F66&lt;&gt;0,F66*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H66" s="123" t="str">
+        <f aca="false">IF((F66&lt;&gt;0),F66-G66," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E67" s="119"/>
+      <c r="G67" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F67&lt;&gt;0,F67*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H67" s="123" t="str">
+        <f aca="false">IF((F67&lt;&gt;0),F67-G67," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E68" s="119"/>
+      <c r="G68" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F68&lt;&gt;0,F68*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H68" s="123" t="str">
+        <f aca="false">IF((F68&lt;&gt;0),F68-G68," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E69" s="119"/>
+      <c r="G69" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F69&lt;&gt;0,F69*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H69" s="123" t="str">
+        <f aca="false">IF((F69&lt;&gt;0),F69-G69," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E70" s="119"/>
+      <c r="G70" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F70&lt;&gt;0,F70*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H70" s="123" t="str">
+        <f aca="false">IF((F70&lt;&gt;0),F70-G70," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E71" s="119"/>
+      <c r="G71" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F71&lt;&gt;0,F71*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H71" s="123" t="str">
+        <f aca="false">IF((F71&lt;&gt;0),F71-G71," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E72" s="119"/>
+      <c r="G72" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F72&lt;&gt;0,F72*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H72" s="123" t="str">
+        <f aca="false">IF((F72&lt;&gt;0),F72-G72," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E73" s="119"/>
+      <c r="G73" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F73&lt;&gt;0,F73*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H73" s="123" t="str">
+        <f aca="false">IF((F73&lt;&gt;0),F73-G73," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E74" s="119"/>
+      <c r="G74" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F74&lt;&gt;0,F74*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H74" s="123" t="str">
+        <f aca="false">IF((F74&lt;&gt;0),F74-G74," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E75" s="119"/>
+      <c r="G75" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F75&lt;&gt;0,F75*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H75" s="123" t="str">
+        <f aca="false">IF((F75&lt;&gt;0),F75-G75," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E76" s="119"/>
+      <c r="G76" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F76&lt;&gt;0,F76*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H76" s="123" t="str">
+        <f aca="false">IF((F76&lt;&gt;0),F76-G76," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E77" s="119"/>
+      <c r="G77" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F77&lt;&gt;0,F77*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H77" s="123" t="str">
+        <f aca="false">IF((F77&lt;&gt;0),F77-G77," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E78" s="119"/>
+      <c r="G78" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F78&lt;&gt;0,F78*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H78" s="123" t="str">
+        <f aca="false">IF((F78&lt;&gt;0),F78-G78," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E79" s="119"/>
+      <c r="G79" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F79&lt;&gt;0,F79*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H79" s="123" t="str">
+        <f aca="false">IF((F79&lt;&gt;0),F79-G79," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E80" s="119"/>
+      <c r="G80" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F80&lt;&gt;0,F80*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H80" s="123" t="str">
+        <f aca="false">IF((F80&lt;&gt;0),F80-G80," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E81" s="119"/>
+      <c r="G81" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F81&lt;&gt;0,F81*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H81" s="123" t="str">
+        <f aca="false">IF((F81&lt;&gt;0),F81-G81," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E82" s="119"/>
+      <c r="G82" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F82&lt;&gt;0,F82*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H82" s="123" t="str">
+        <f aca="false">IF((F82&lt;&gt;0),F82-G82," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E83" s="119"/>
+      <c r="G83" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F83&lt;&gt;0,F83*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H83" s="123" t="str">
+        <f aca="false">IF((F83&lt;&gt;0),F83-G83," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E84" s="119"/>
+      <c r="G84" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F84&lt;&gt;0,F84*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H84" s="123" t="str">
+        <f aca="false">IF((F84&lt;&gt;0),F84-G84," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E85" s="119"/>
+      <c r="G85" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F85&lt;&gt;0,F85*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H85" s="123" t="str">
+        <f aca="false">IF((F85&lt;&gt;0),F85-G85," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E86" s="119"/>
+      <c r="G86" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F86&lt;&gt;0,F86*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H86" s="123" t="str">
+        <f aca="false">IF((F86&lt;&gt;0),F86-G86," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E87" s="119"/>
+      <c r="G87" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F87&lt;&gt;0,F87*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H87" s="123" t="str">
+        <f aca="false">IF((F87&lt;&gt;0),F87-G87," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E88" s="119"/>
+      <c r="G88" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F88&lt;&gt;0,F88*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H88" s="123" t="str">
+        <f aca="false">IF((F88&lt;&gt;0),F88-G88," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E89" s="119"/>
+      <c r="G89" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F89&lt;&gt;0,F89*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H89" s="123" t="str">
+        <f aca="false">IF((F89&lt;&gt;0),F89-G89," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E90" s="119"/>
+      <c r="G90" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F90&lt;&gt;0,F90*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H90" s="123" t="str">
+        <f aca="false">IF((F90&lt;&gt;0),F90-G90," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E91" s="119"/>
+      <c r="G91" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F91&lt;&gt;0,F91*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H91" s="123" t="str">
+        <f aca="false">IF((F91&lt;&gt;0),F91-G91," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E92" s="119"/>
+      <c r="G92" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F92&lt;&gt;0,F92*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H92" s="123" t="str">
+        <f aca="false">IF((F92&lt;&gt;0),F92-G92," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E93" s="119"/>
+      <c r="G93" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F93&lt;&gt;0,F93*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H93" s="123" t="str">
+        <f aca="false">IF((F93&lt;&gt;0),F93-G93," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E94" s="119"/>
+      <c r="G94" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F94&lt;&gt;0,F94*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H94" s="123" t="str">
+        <f aca="false">IF((F94&lt;&gt;0),F94-G94," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E95" s="119"/>
+      <c r="G95" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F95&lt;&gt;0,F95*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H95" s="123" t="str">
+        <f aca="false">IF((F95&lt;&gt;0),F95-G95," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E96" s="119"/>
+      <c r="G96" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F96&lt;&gt;0,F96*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H96" s="123" t="str">
+        <f aca="false">IF((F96&lt;&gt;0),F96-G96," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E97" s="119"/>
+      <c r="G97" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F97&lt;&gt;0,F97*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H97" s="123" t="str">
+        <f aca="false">IF((F97&lt;&gt;0),F97-G97," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E98" s="119"/>
+      <c r="G98" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F98&lt;&gt;0,F98*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H98" s="123" t="str">
+        <f aca="false">IF((F98&lt;&gt;0),F98-G98," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E99" s="119"/>
+      <c r="G99" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F99&lt;&gt;0,F99*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H99" s="123" t="str">
+        <f aca="false">IF((F99&lt;&gt;0),F99-G99," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E100" s="119"/>
+      <c r="G100" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F100&lt;&gt;0,F100*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H100" s="123" t="str">
+        <f aca="false">IF((F100&lt;&gt;0),F100-G100," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E101" s="119"/>
+      <c r="G101" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F101&lt;&gt;0,F101*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H101" s="123" t="str">
+        <f aca="false">IF((F101&lt;&gt;0),F101-G101," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E102" s="119"/>
+      <c r="G102" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F102&lt;&gt;0,F102*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H102" s="123" t="str">
+        <f aca="false">IF((F102&lt;&gt;0),F102-G102," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E103" s="119"/>
+      <c r="G103" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F103&lt;&gt;0,F103*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H103" s="123" t="str">
+        <f aca="false">IF((F103&lt;&gt;0),F103-G103," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E104" s="119"/>
+      <c r="G104" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F104&lt;&gt;0,F104*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H104" s="123" t="str">
+        <f aca="false">IF((F104&lt;&gt;0),F104-G104," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E105" s="119"/>
+      <c r="G105" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F105&lt;&gt;0,F105*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H105" s="123" t="str">
+        <f aca="false">IF((F105&lt;&gt;0),F105-G105," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E106" s="119"/>
+      <c r="G106" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F106&lt;&gt;0,F106*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H106" s="123" t="str">
+        <f aca="false">IF((F106&lt;&gt;0),F106-G106," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E107" s="119"/>
+      <c r="G107" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F107&lt;&gt;0,F107*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H107" s="123" t="str">
+        <f aca="false">IF((F107&lt;&gt;0),F107-G107," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E108" s="119"/>
+      <c r="G108" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F108&lt;&gt;0,F108*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H108" s="123" t="str">
+        <f aca="false">IF((F108&lt;&gt;0),F108-G108," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E109" s="119"/>
+      <c r="G109" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F109&lt;&gt;0,F109*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H109" s="123" t="str">
+        <f aca="false">IF((F109&lt;&gt;0),F109-G109," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E110" s="119"/>
+      <c r="G110" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F110&lt;&gt;0,F110*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H110" s="123" t="str">
+        <f aca="false">IF((F110&lt;&gt;0),F110-G110," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E111" s="119"/>
+      <c r="G111" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F111&lt;&gt;0,F111*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H111" s="123" t="str">
+        <f aca="false">IF((F111&lt;&gt;0),F111-G111," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E112" s="119"/>
+      <c r="G112" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F112&lt;&gt;0,F112*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H112" s="123" t="str">
+        <f aca="false">IF((F112&lt;&gt;0),F112-G112," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E113" s="119"/>
+      <c r="G113" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F113&lt;&gt;0,F113*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H113" s="123" t="str">
+        <f aca="false">IF((F113&lt;&gt;0),F113-G113," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E114" s="119"/>
+      <c r="G114" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F114&lt;&gt;0,F114*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H114" s="123" t="str">
+        <f aca="false">IF((F114&lt;&gt;0),F114-G114," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E115" s="119"/>
+      <c r="G115" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F115&lt;&gt;0,F115*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H115" s="123" t="str">
+        <f aca="false">IF((F115&lt;&gt;0),F115-G115," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E116" s="119"/>
+      <c r="G116" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F116&lt;&gt;0,F116*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H116" s="123" t="str">
+        <f aca="false">IF((F116&lt;&gt;0),F116-G116," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E117" s="119"/>
+      <c r="G117" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F117&lt;&gt;0,F117*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H117" s="123" t="str">
+        <f aca="false">IF((F117&lt;&gt;0),F117-G117," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E118" s="119"/>
+      <c r="G118" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F118&lt;&gt;0,F118*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H118" s="123" t="str">
+        <f aca="false">IF((F118&lt;&gt;0),F118-G118," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E119" s="119"/>
+      <c r="G119" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F119&lt;&gt;0,F119*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H119" s="123" t="str">
+        <f aca="false">IF((F119&lt;&gt;0),F119-G119," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E120" s="119"/>
+      <c r="G120" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F120&lt;&gt;0,F120*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H120" s="123" t="str">
+        <f aca="false">IF((F120&lt;&gt;0),F120-G120," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E121" s="119"/>
+      <c r="G121" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F121&lt;&gt;0,F121*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H121" s="123" t="str">
+        <f aca="false">IF((F121&lt;&gt;0),F121-G121," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E122" s="119"/>
+      <c r="G122" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F122&lt;&gt;0,F122*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H122" s="123" t="str">
+        <f aca="false">IF((F122&lt;&gt;0),F122-G122," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E123" s="119"/>
+      <c r="G123" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F123&lt;&gt;0,F123*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H123" s="123" t="str">
+        <f aca="false">IF((F123&lt;&gt;0),F123-G123," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E124" s="119"/>
+      <c r="G124" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F124&lt;&gt;0,F124*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H124" s="123" t="str">
+        <f aca="false">IF((F124&lt;&gt;0),F124-G124," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E125" s="119"/>
+      <c r="G125" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F125&lt;&gt;0,F125*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H125" s="123" t="str">
+        <f aca="false">IF((F125&lt;&gt;0),F125-G125," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E126" s="119"/>
+      <c r="G126" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F126&lt;&gt;0,F126*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H126" s="123" t="str">
+        <f aca="false">IF((F126&lt;&gt;0),F126-G126," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E127" s="119"/>
+      <c r="G127" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F127&lt;&gt;0,F127*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H127" s="123" t="str">
+        <f aca="false">IF((F127&lt;&gt;0),F127-G127," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E128" s="119"/>
+      <c r="G128" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F128&lt;&gt;0,F128*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H128" s="123" t="str">
+        <f aca="false">IF((F128&lt;&gt;0),F128-G128," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E129" s="119"/>
+      <c r="G129" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F129&lt;&gt;0,F129*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H129" s="123" t="str">
+        <f aca="false">IF((F129&lt;&gt;0),F129-G129," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E130" s="119"/>
+      <c r="G130" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F130&lt;&gt;0,F130*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H130" s="123" t="str">
+        <f aca="false">IF((F130&lt;&gt;0),F130-G130," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E131" s="119"/>
+      <c r="G131" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F131&lt;&gt;0,F131*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H131" s="123" t="str">
+        <f aca="false">IF((F131&lt;&gt;0),F131-G131," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E132" s="119"/>
+      <c r="G132" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F132&lt;&gt;0,F132*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H132" s="123" t="str">
+        <f aca="false">IF((F132&lt;&gt;0),F132-G132," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E133" s="119"/>
+      <c r="G133" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F133&lt;&gt;0,F133*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H133" s="123" t="str">
+        <f aca="false">IF((F133&lt;&gt;0),F133-G133," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E134" s="119"/>
+      <c r="G134" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F134&lt;&gt;0,F134*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H134" s="123" t="str">
+        <f aca="false">IF((F134&lt;&gt;0),F134-G134," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E135" s="119"/>
+      <c r="G135" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F135&lt;&gt;0,F135*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H135" s="123" t="str">
+        <f aca="false">IF((F135&lt;&gt;0),F135-G135," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E136" s="119"/>
+      <c r="G136" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F136&lt;&gt;0,F136*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H136" s="123" t="str">
+        <f aca="false">IF((F136&lt;&gt;0),F136-G136," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E137" s="119"/>
+      <c r="G137" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F137&lt;&gt;0,F137*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H137" s="123" t="str">
+        <f aca="false">IF((F137&lt;&gt;0),F137-G137," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E138" s="119"/>
+      <c r="G138" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F138&lt;&gt;0,F138*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H138" s="123" t="str">
+        <f aca="false">IF((F138&lt;&gt;0),F138-G138," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E139" s="119"/>
+      <c r="G139" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F139&lt;&gt;0,F139*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H139" s="123" t="str">
+        <f aca="false">IF((F139&lt;&gt;0),F139-G139," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E140" s="119"/>
+      <c r="G140" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F140&lt;&gt;0,F140*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H140" s="123" t="str">
+        <f aca="false">IF((F140&lt;&gt;0),F140-G140," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E141" s="119"/>
+      <c r="G141" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F141&lt;&gt;0,F141*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H141" s="123" t="str">
+        <f aca="false">IF((F141&lt;&gt;0),F141-G141," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E142" s="119"/>
+      <c r="G142" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F142&lt;&gt;0,F142*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H142" s="123" t="str">
+        <f aca="false">IF((F142&lt;&gt;0),F142-G142," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E143" s="119"/>
+      <c r="G143" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F143&lt;&gt;0,F143*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H143" s="123" t="str">
+        <f aca="false">IF((F143&lt;&gt;0),F143-G143," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E144" s="119"/>
+      <c r="G144" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F144&lt;&gt;0,F144*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H144" s="123" t="str">
+        <f aca="false">IF((F144&lt;&gt;0),F144-G144," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E145" s="119"/>
+      <c r="G145" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F145&lt;&gt;0,F145*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H145" s="123" t="str">
+        <f aca="false">IF((F145&lt;&gt;0),F145-G145," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E146" s="119"/>
+      <c r="G146" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F146&lt;&gt;0,F146*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H146" s="123" t="str">
+        <f aca="false">IF((F146&lt;&gt;0),F146-G146," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E147" s="119"/>
+      <c r="G147" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F147&lt;&gt;0,F147*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H147" s="123" t="str">
+        <f aca="false">IF((F147&lt;&gt;0),F147-G147," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E148" s="119"/>
+      <c r="G148" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F148&lt;&gt;0,F148*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H148" s="123" t="str">
+        <f aca="false">IF((F148&lt;&gt;0),F148-G148," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E149" s="119"/>
+      <c r="G149" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F149&lt;&gt;0,F149*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H149" s="123" t="str">
+        <f aca="false">IF((F149&lt;&gt;0),F149-G149," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E150" s="119"/>
+      <c r="G150" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F150&lt;&gt;0,F150*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H150" s="123" t="str">
+        <f aca="false">IF((F150&lt;&gt;0),F150-G150," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E151" s="119"/>
+      <c r="G151" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F151&lt;&gt;0,F151*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H151" s="123" t="str">
+        <f aca="false">IF((F151&lt;&gt;0),F151-G151," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E152" s="119"/>
+      <c r="G152" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F152&lt;&gt;0,F152*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H152" s="123" t="str">
+        <f aca="false">IF((F152&lt;&gt;0),F152-G152," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E153" s="119"/>
+      <c r="G153" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F153&lt;&gt;0,F153*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H153" s="123" t="str">
+        <f aca="false">IF((F153&lt;&gt;0),F153-G153," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E154" s="119"/>
+      <c r="G154" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F154&lt;&gt;0,F154*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H154" s="123" t="str">
+        <f aca="false">IF((F154&lt;&gt;0),F154-G154," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E155" s="119"/>
+      <c r="G155" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F155&lt;&gt;0,F155*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H155" s="123" t="str">
+        <f aca="false">IF((F155&lt;&gt;0),F155-G155," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E156" s="119"/>
+      <c r="G156" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F156&lt;&gt;0,F156*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H156" s="123" t="str">
+        <f aca="false">IF((F156&lt;&gt;0),F156-G156," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E157" s="119"/>
+      <c r="G157" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F157&lt;&gt;0,F157*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H157" s="123" t="str">
+        <f aca="false">IF((F157&lt;&gt;0),F157-G157," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E158" s="119"/>
+      <c r="G158" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F158&lt;&gt;0,F158*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H158" s="123" t="str">
+        <f aca="false">IF((F158&lt;&gt;0),F158-G158," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E159" s="119"/>
+      <c r="G159" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F159&lt;&gt;0,F159*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H159" s="123" t="str">
+        <f aca="false">IF((F159&lt;&gt;0),F159-G159," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E160" s="119"/>
+      <c r="G160" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F160&lt;&gt;0,F160*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H160" s="123" t="str">
+        <f aca="false">IF((F160&lt;&gt;0),F160-G160," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E161" s="119"/>
+      <c r="G161" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F161&lt;&gt;0,F161*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H161" s="123" t="str">
+        <f aca="false">IF((F161&lt;&gt;0),F161-G161," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E162" s="119"/>
+      <c r="G162" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F162&lt;&gt;0,F162*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H162" s="123" t="str">
+        <f aca="false">IF((F162&lt;&gt;0),F162-G162," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E163" s="119"/>
+      <c r="G163" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F163&lt;&gt;0,F163*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H163" s="123" t="str">
+        <f aca="false">IF((F163&lt;&gt;0),F163-G163," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E164" s="119"/>
+      <c r="G164" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F164&lt;&gt;0,F164*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H164" s="123" t="str">
+        <f aca="false">IF((F164&lt;&gt;0),F164-G164," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E165" s="119"/>
+      <c r="G165" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F165&lt;&gt;0,F165*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H165" s="123" t="str">
+        <f aca="false">IF((F165&lt;&gt;0),F165-G165," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E166" s="119"/>
+      <c r="G166" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F166&lt;&gt;0,F166*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H166" s="123" t="str">
+        <f aca="false">IF((F166&lt;&gt;0),F166-G166," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E167" s="119"/>
+      <c r="G167" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F167&lt;&gt;0,F167*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H167" s="123" t="str">
+        <f aca="false">IF((F167&lt;&gt;0),F167-G167," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E168" s="119"/>
+      <c r="G168" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F168&lt;&gt;0,F168*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H168" s="123" t="str">
+        <f aca="false">IF((F168&lt;&gt;0),F168-G168," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E169" s="119"/>
+      <c r="G169" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F169&lt;&gt;0,F169*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H169" s="123" t="str">
+        <f aca="false">IF((F169&lt;&gt;0),F169-G169," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E170" s="119"/>
+      <c r="G170" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F170&lt;&gt;0,F170*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H170" s="123" t="str">
+        <f aca="false">IF((F170&lt;&gt;0),F170-G170," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E171" s="119"/>
+      <c r="G171" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F171&lt;&gt;0,F171*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H171" s="123" t="str">
+        <f aca="false">IF((F171&lt;&gt;0),F171-G171," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E172" s="119"/>
+      <c r="G172" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F172&lt;&gt;0,F172*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H172" s="123" t="str">
+        <f aca="false">IF((F172&lt;&gt;0),F172-G172," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E173" s="119"/>
+      <c r="G173" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F173&lt;&gt;0,F173*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H173" s="123" t="str">
+        <f aca="false">IF((F173&lt;&gt;0),F173-G173," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E174" s="119"/>
+      <c r="G174" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F174&lt;&gt;0,F174*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H174" s="123" t="str">
+        <f aca="false">IF((F174&lt;&gt;0),F174-G174," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E175" s="119"/>
+      <c r="G175" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F175&lt;&gt;0,F175*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H175" s="123" t="str">
+        <f aca="false">IF((F175&lt;&gt;0),F175-G175," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E176" s="119"/>
+      <c r="G176" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F176&lt;&gt;0,F176*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H176" s="123" t="str">
+        <f aca="false">IF((F176&lt;&gt;0),F176-G176," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E177" s="119"/>
+      <c r="G177" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F177&lt;&gt;0,F177*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H177" s="123" t="str">
+        <f aca="false">IF((F177&lt;&gt;0),F177-G177," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E178" s="119"/>
+      <c r="G178" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F178&lt;&gt;0,F178*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H178" s="123" t="str">
+        <f aca="false">IF((F178&lt;&gt;0),F178-G178," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E179" s="119"/>
+      <c r="G179" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F179&lt;&gt;0,F179*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H179" s="123" t="str">
+        <f aca="false">IF((F179&lt;&gt;0),F179-G179," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E180" s="119"/>
+      <c r="G180" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F180&lt;&gt;0,F180*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H180" s="123" t="str">
+        <f aca="false">IF((F180&lt;&gt;0),F180-G180," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E181" s="119"/>
+      <c r="G181" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F181&lt;&gt;0,F181*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H181" s="123" t="str">
+        <f aca="false">IF((F181&lt;&gt;0),F181-G181," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E182" s="119"/>
+      <c r="G182" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F182&lt;&gt;0,F182*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H182" s="123" t="str">
+        <f aca="false">IF((F182&lt;&gt;0),F182-G182," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E183" s="119"/>
+      <c r="G183" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F183&lt;&gt;0,F183*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H183" s="123" t="str">
+        <f aca="false">IF((F183&lt;&gt;0),F183-G183," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E184" s="119"/>
+      <c r="G184" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F184&lt;&gt;0,F184*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H184" s="123" t="str">
+        <f aca="false">IF((F184&lt;&gt;0),F184-G184," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E185" s="119"/>
+      <c r="G185" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F185&lt;&gt;0,F185*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H185" s="123" t="str">
+        <f aca="false">IF((F185&lt;&gt;0),F185-G185," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E186" s="119"/>
+      <c r="G186" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F186&lt;&gt;0,F186*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H186" s="123" t="str">
+        <f aca="false">IF((F186&lt;&gt;0),F186-G186," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E187" s="119"/>
+      <c r="G187" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F187&lt;&gt;0,F187*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H187" s="123" t="str">
+        <f aca="false">IF((F187&lt;&gt;0),F187-G187," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E188" s="119"/>
+      <c r="G188" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F188&lt;&gt;0,F188*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H188" s="123" t="str">
+        <f aca="false">IF((F188&lt;&gt;0),F188-G188," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E189" s="119"/>
+      <c r="G189" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F189&lt;&gt;0,F189*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H189" s="123" t="str">
+        <f aca="false">IF((F189&lt;&gt;0),F189-G189," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E190" s="119"/>
+      <c r="G190" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F190&lt;&gt;0,F190*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H190" s="123" t="str">
+        <f aca="false">IF((F190&lt;&gt;0),F190-G190," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E191" s="119"/>
+      <c r="G191" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F191&lt;&gt;0,F191*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H191" s="123" t="str">
+        <f aca="false">IF((F191&lt;&gt;0),F191-G191," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E192" s="119"/>
+      <c r="G192" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F192&lt;&gt;0,F192*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H192" s="123" t="str">
+        <f aca="false">IF((F192&lt;&gt;0),F192-G192," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E193" s="119"/>
+      <c r="G193" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F193&lt;&gt;0,F193*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H193" s="123" t="str">
+        <f aca="false">IF((F193&lt;&gt;0),F193-G193," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E194" s="119"/>
+      <c r="G194" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F194&lt;&gt;0,F194*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H194" s="123" t="str">
+        <f aca="false">IF((F194&lt;&gt;0),F194-G194," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E195" s="119"/>
+      <c r="G195" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F195&lt;&gt;0,F195*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H195" s="123" t="str">
+        <f aca="false">IF((F195&lt;&gt;0),F195-G195," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E196" s="119"/>
+      <c r="G196" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F196&lt;&gt;0,F196*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H196" s="123" t="str">
+        <f aca="false">IF((F196&lt;&gt;0),F196-G196," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E197" s="119"/>
+      <c r="G197" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F197&lt;&gt;0,F197*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H197" s="123" t="str">
+        <f aca="false">IF((F197&lt;&gt;0),F197-G197," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E198" s="119"/>
+      <c r="G198" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F198&lt;&gt;0,F198*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H198" s="123" t="str">
+        <f aca="false">IF((F198&lt;&gt;0),F198-G198," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E199" s="119"/>
+      <c r="G199" s="123" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F199&lt;&gt;0,F199*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H199" s="123" t="str">
+        <f aca="false">IF((F199&lt;&gt;0),F199-G199," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="132"/>
+      <c r="B200" s="133"/>
+      <c r="C200" s="134"/>
+      <c r="D200" s="135"/>
+      <c r="E200" s="133"/>
+      <c r="F200" s="136"/>
+      <c r="G200" s="136" t="str">
+        <f aca="false">IF(G$4="X"," ",IF(F200&lt;&gt;0,F200*G$2/(100+G$2)," "))</f>
+        <v> </v>
+      </c>
+      <c r="H200" s="136" t="str">
+        <f aca="false">IF((F200&lt;&gt;0),F200-G200," ")</f>
+        <v> </v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="98" t="s">
+        <v>40</v>
+      </c>
+      <c r="G201" s="123" t="e">
+        <f aca="false">NA()</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="G3:G4"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H201"/>
+  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="118" width="8.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="119" width="19.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="120" width="12.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="121" width="14.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="122" width="5.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="123" width="10.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="123" width="9.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="123" width="10.66"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="9" style="119" width="9.15"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="102" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="103" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105" t="n">
+        <f aca="false">SUM(F5:F200)</f>
+        <v>480</v>
+      </c>
+      <c r="G1" s="105" t="n">
+        <f aca="false">SUM(G5:G200)</f>
+        <v>80</v>
+      </c>
+      <c r="H1" s="105" t="n">
+        <f aca="false">SUM(H5:H200)</f>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="2" s="127" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="107" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="108" t="str">
+        <f aca="false">IF((H1-SUM(O1:AK1)&lt;&gt;0),"COMPLETE EXPENSE ANALYSIS by inserting expense letter in col F","Supplier")</f>
+        <v>COMPLETE EXPENSE ANALYSIS by inserting expense letter in col F</v>
+      </c>
+      <c r="C2" s="110" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="124" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="125"/>
+      <c r="F2" s="108" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" s="126" t="n">
+        <f aca="false">[3]ClosingCreditors!$G$2</f>
+        <v>20</v>
+      </c>
+      <c r="H2" s="108" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" s="128" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="107"/>
+      <c r="B3" s="107"/>
+      <c r="C3" s="107"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="108" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" s="108"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="107"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="124"/>
+      <c r="E4" s="125"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="108"/>
+    </row>
+    <row r="5" s="119" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="118" t="n">
+        <v>46372</v>
+      </c>
+      <c r="B5" s="122" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="129" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="122"/>
+      <c r="F5" s="130" t="n">
+        <v>480</v>
+      </c>
+      <c r="G5" s="123" t="n">
+        <f aca="false">IF(F5&lt;&gt;0,F5*G$2/(100+G$2)," ")</f>
+        <v>80</v>
+      </c>
+      <c r="H5" s="123" t="n">
+        <f aca="false">IF((F5&lt;&gt;0),F5-G5," ")</f>
+        <v>400</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13966,7 +18375,7 @@
       </c>
       <c r="G15" s="37" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!K1:K20)</f>
-        <v>3073.25</v>
+        <v>4473.25</v>
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="14"/>
@@ -13985,27 +18394,30 @@
       <c r="G16" s="40"/>
       <c r="H16" s="13"/>
       <c r="I16" s="14"/>
-      <c r="K16" s="42"/>
+      <c r="K16" s="15" t="n">
+        <f aca="false">Vatinterface!B20</f>
+        <v>46752</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="41"/>
-      <c r="B17" s="43" t="str">
+      <c r="B17" s="42" t="str">
         <f aca="false">IF(G17&gt;0,"Net VAT to be PAID to Customs","Net VAT to be RECLIAMED from Customs")</f>
         <v>Net VAT to be PAID to Customs</v>
       </c>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
       <c r="F17" s="36" t="n">
         <v>5</v>
       </c>
       <c r="G17" s="37" t="n">
         <f aca="false">G13-G15</f>
-        <v>14183.4166666667</v>
+        <v>12783.4166666667</v>
       </c>
       <c r="H17" s="13"/>
       <c r="I17" s="14"/>
-      <c r="K17" s="42"/>
+      <c r="K17" s="43"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="44"/>
@@ -14089,7 +18501,7 @@
       </c>
       <c r="G23" s="52" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!I1:I20)</f>
-        <v>15366.25</v>
+        <v>22366.25</v>
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="14"/>
@@ -14240,7 +18652,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G5" type="list">
-      <formula1>$K$2:$K$15</formula1>
+      <formula1>$K$2:$K$16</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -14549,17 +18961,20 @@
       <c r="G16" s="40"/>
       <c r="H16" s="13"/>
       <c r="I16" s="14"/>
-      <c r="K16" s="42"/>
+      <c r="K16" s="15" t="n">
+        <f aca="false">Vatinterface!B20</f>
+        <v>46752</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="41"/>
-      <c r="B17" s="43" t="str">
+      <c r="B17" s="42" t="str">
         <f aca="false">IF(G17&gt;0,"Net VAT to be PAID to Customs","Net VAT to be RECLIAMED from Customs")</f>
         <v>Net VAT to be PAID to Customs</v>
       </c>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
       <c r="F17" s="36" t="n">
         <v>5</v>
       </c>
@@ -14569,7 +18984,7 @@
       </c>
       <c r="H17" s="13"/>
       <c r="I17" s="14"/>
-      <c r="K17" s="42"/>
+      <c r="K17" s="43"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="44"/>
@@ -14804,7 +19219,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G5" type="list">
-      <formula1>$K$2:$K$15</formula1>
+      <formula1>$K$2:$K$16</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -15113,17 +19528,20 @@
       <c r="G16" s="40"/>
       <c r="H16" s="13"/>
       <c r="I16" s="14"/>
-      <c r="K16" s="42"/>
+      <c r="K16" s="15" t="n">
+        <f aca="false">Vatinterface!B20</f>
+        <v>46752</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="41"/>
-      <c r="B17" s="43" t="str">
+      <c r="B17" s="42" t="str">
         <f aca="false">IF(G17&gt;0,"Net VAT to be PAID to Customs","Net VAT to be RECLIAMED from Customs")</f>
         <v>Net VAT to be PAID to Customs</v>
       </c>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
       <c r="F17" s="36" t="n">
         <v>5</v>
       </c>
@@ -15133,7 +19551,7 @@
       </c>
       <c r="H17" s="13"/>
       <c r="I17" s="14"/>
-      <c r="K17" s="42"/>
+      <c r="K17" s="43"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="44"/>
@@ -15368,7 +19786,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G5" type="list">
-      <formula1>$K$2:$K$15</formula1>
+      <formula1>$K$2:$K$16</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -15476,7 +19894,7 @@
       </c>
       <c r="F5" s="26"/>
       <c r="G5" s="27" t="n">
-        <v>46721</v>
+        <v>46752</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="14"/>
@@ -15511,7 +19929,7 @@
       <c r="F7" s="31"/>
       <c r="G7" s="32" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!C1:C20)</f>
-        <v>46752</v>
+        <v>46783</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="14"/>
@@ -15548,7 +19966,7 @@
       </c>
       <c r="G9" s="37" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!G1:G20)</f>
-        <v>6126.66666666667</v>
+        <v>1100</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="14"/>
@@ -15621,7 +20039,7 @@
       </c>
       <c r="G13" s="37" t="n">
         <f aca="false">G9+G11</f>
-        <v>6126.66666666667</v>
+        <v>1100</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="14"/>
@@ -15658,7 +20076,7 @@
       </c>
       <c r="G15" s="37" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!K1:K20)</f>
-        <v>721.083333333333</v>
+        <v>180</v>
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="14"/>
@@ -15677,27 +20095,30 @@
       <c r="G16" s="40"/>
       <c r="H16" s="13"/>
       <c r="I16" s="14"/>
-      <c r="K16" s="42"/>
+      <c r="K16" s="15" t="n">
+        <f aca="false">Vatinterface!B20</f>
+        <v>46752</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="41"/>
-      <c r="B17" s="43" t="str">
+      <c r="B17" s="42" t="str">
         <f aca="false">IF(G17&gt;0,"Net VAT to be PAID to Customs","Net VAT to be RECLIAMED from Customs")</f>
         <v>Net VAT to be PAID to Customs</v>
       </c>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
       <c r="F17" s="36" t="n">
         <v>5</v>
       </c>
       <c r="G17" s="37" t="n">
         <f aca="false">G13-G15</f>
-        <v>5405.58333333334</v>
+        <v>920</v>
       </c>
       <c r="H17" s="13"/>
       <c r="I17" s="14"/>
-      <c r="K17" s="42"/>
+      <c r="K17" s="43"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="44"/>
@@ -15752,7 +20173,7 @@
       </c>
       <c r="G21" s="52" t="n">
         <f aca="false">IF(LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!M1:M20)&gt;0,(LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!E1:E20)+LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!G1:G20)),LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!E1:E20))</f>
-        <v>30633.3333333333</v>
+        <v>5500</v>
       </c>
       <c r="H21" s="13"/>
       <c r="I21" s="14"/>
@@ -15781,7 +20202,7 @@
       </c>
       <c r="G23" s="52" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!I1:I20)</f>
-        <v>3605.41666666667</v>
+        <v>900</v>
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="14"/>
@@ -15932,7 +20353,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G5" type="list">
-      <formula1>$K$2:$K$15</formula1>
+      <formula1>$K$2:$K$16</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -15951,7 +20372,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="63" width="1.99"/>
@@ -16233,19 +20654,19 @@
       </c>
       <c r="H8" s="87" t="n">
         <f aca="false">[3]Dec!$H$1</f>
-        <v>7547.5</v>
+        <v>20547.5</v>
       </c>
       <c r="I8" s="87" t="n">
         <f aca="false">SUM(H6:H8)</f>
-        <v>17119.375</v>
+        <v>30119.375</v>
       </c>
       <c r="J8" s="87" t="n">
         <f aca="false">[3]Dec!$G$1</f>
-        <v>1509.5</v>
+        <v>4109.5</v>
       </c>
       <c r="K8" s="87" t="n">
         <f aca="false">SUM(J6:J8)</f>
-        <v>3423.875</v>
+        <v>6023.875</v>
       </c>
       <c r="L8" s="88"/>
       <c r="M8" s="89" t="n">
@@ -16286,7 +20707,7 @@
       </c>
       <c r="I9" s="87" t="n">
         <f aca="false">SUM(H7:H9)</f>
-        <v>20409.375</v>
+        <v>33409.375</v>
       </c>
       <c r="J9" s="87" t="n">
         <f aca="false">[3]Jan!$G$1</f>
@@ -16294,7 +20715,7 @@
       </c>
       <c r="K9" s="87" t="n">
         <f aca="false">SUM(J7:J9)</f>
-        <v>4081.875</v>
+        <v>6681.875</v>
       </c>
       <c r="L9" s="88"/>
       <c r="M9" s="89" t="n">
@@ -16335,7 +20756,7 @@
       </c>
       <c r="I10" s="87" t="n">
         <f aca="false">SUM(H8:H10)</f>
-        <v>18767.9166666667</v>
+        <v>31767.9166666667</v>
       </c>
       <c r="J10" s="87" t="n">
         <f aca="false">[3]Feb!$G$1</f>
@@ -16343,7 +20764,7 @@
       </c>
       <c r="K10" s="87" t="n">
         <f aca="false">SUM(J8:J10)</f>
-        <v>3753.58333333333</v>
+        <v>6353.58333333333</v>
       </c>
       <c r="L10" s="88"/>
       <c r="M10" s="89" t="n">
@@ -16380,19 +20801,19 @@
       </c>
       <c r="H11" s="87" t="n">
         <f aca="false">[3]Mar!$H$1</f>
-        <v>4145.83333333333</v>
+        <v>11145.8333333333</v>
       </c>
       <c r="I11" s="87" t="n">
         <f aca="false">SUM(H9:H11)</f>
-        <v>15366.25</v>
+        <v>22366.25</v>
       </c>
       <c r="J11" s="87" t="n">
         <f aca="false">[3]Mar!$G$1</f>
-        <v>829.166666666667</v>
+        <v>2229.16666666667</v>
       </c>
       <c r="K11" s="87" t="n">
         <f aca="false">SUM(J9:J11)</f>
-        <v>3073.25</v>
+        <v>4473.25</v>
       </c>
       <c r="L11" s="88"/>
       <c r="M11" s="89" t="n">
@@ -16433,7 +20854,7 @@
       </c>
       <c r="I12" s="87" t="n">
         <f aca="false">SUM(H10:H12)</f>
-        <v>43655</v>
+        <v>50655</v>
       </c>
       <c r="J12" s="87" t="n">
         <f aca="false">[3]Apr!$G$1</f>
@@ -16441,7 +20862,7 @@
       </c>
       <c r="K12" s="87" t="n">
         <f aca="false">SUM(J10:J12)</f>
-        <v>8731</v>
+        <v>10131</v>
       </c>
       <c r="L12" s="88"/>
       <c r="M12" s="89" t="n">
@@ -16482,7 +20903,7 @@
       </c>
       <c r="I13" s="87" t="n">
         <f aca="false">SUM(H11:H13)</f>
-        <v>45748.9583333333</v>
+        <v>52748.9583333333</v>
       </c>
       <c r="J13" s="87" t="n">
         <f aca="false">[3]May!$G$1</f>
@@ -16490,7 +20911,7 @@
       </c>
       <c r="K13" s="87" t="n">
         <f aca="false">SUM(J11:J13)</f>
-        <v>9149.79166666667</v>
+        <v>10549.7916666667</v>
       </c>
       <c r="L13" s="88"/>
       <c r="M13" s="89" t="n">
@@ -16750,7 +21171,7 @@
         <f aca="false">[1]Admin!$B$36</f>
         <v>46721</v>
       </c>
-      <c r="C19" s="91" t="n">
+      <c r="C19" s="85" t="n">
         <f aca="false">[1]Admin!$B$38</f>
         <v>46752</v>
       </c>
@@ -16793,21 +21214,70 @@
       </c>
       <c r="N19" s="90"/>
     </row>
-    <row r="20" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="92"/>
-      <c r="B20" s="93"/>
-      <c r="C20" s="93"/>
-      <c r="D20" s="94"/>
-      <c r="E20" s="94"/>
-      <c r="F20" s="94"/>
-      <c r="G20" s="94"/>
-      <c r="H20" s="94"/>
-      <c r="I20" s="94"/>
-      <c r="J20" s="94"/>
-      <c r="K20" s="94"/>
-      <c r="L20" s="95"/>
-      <c r="M20" s="96"/>
-      <c r="N20" s="97"/>
+    <row r="20" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="84"/>
+      <c r="B20" s="85" t="n">
+        <f aca="false">[1]Admin!$B$38</f>
+        <v>46752</v>
+      </c>
+      <c r="C20" s="91" t="n">
+        <f aca="false">[1]Admin!$B$40</f>
+        <v>46783</v>
+      </c>
+      <c r="D20" s="86" t="n">
+        <f aca="false">S06Y2!$H$1</f>
+        <v>1000</v>
+      </c>
+      <c r="E20" s="87" t="n">
+        <f aca="false">SUM(D18:D20)</f>
+        <v>5500</v>
+      </c>
+      <c r="F20" s="87" t="n">
+        <f aca="false">S06Y2!$G$1</f>
+        <v>200</v>
+      </c>
+      <c r="G20" s="87" t="n">
+        <f aca="false">SUM(F18:F20)</f>
+        <v>1100</v>
+      </c>
+      <c r="H20" s="87" t="n">
+        <f aca="false">P06Y2!$H$1</f>
+        <v>400</v>
+      </c>
+      <c r="I20" s="87" t="n">
+        <f aca="false">SUM(H18:H20)</f>
+        <v>900</v>
+      </c>
+      <c r="J20" s="87" t="n">
+        <f aca="false">P06Y2!$G$1</f>
+        <v>80</v>
+      </c>
+      <c r="K20" s="87" t="n">
+        <f aca="false">SUM(J18:J20)</f>
+        <v>180</v>
+      </c>
+      <c r="L20" s="88"/>
+      <c r="M20" s="89" t="n">
+        <f aca="false">IF([2]Sep!$G$4&gt;0,[2]Sep!$G$4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N20" s="90"/>
+    </row>
+    <row r="21" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="92"/>
+      <c r="B21" s="93"/>
+      <c r="C21" s="93"/>
+      <c r="D21" s="94"/>
+      <c r="E21" s="94"/>
+      <c r="F21" s="94"/>
+      <c r="G21" s="94"/>
+      <c r="H21" s="94"/>
+      <c r="I21" s="94"/>
+      <c r="J21" s="94"/>
+      <c r="K21" s="94"/>
+      <c r="L21" s="95"/>
+      <c r="M21" s="96"/>
+      <c r="N21" s="97"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>

--- a/examples/ltd-latest/Vatreturns.xlsx
+++ b/examples/ltd-latest/Vatreturns.xlsx
@@ -1272,92 +1272,92 @@
       <sheetData sheetId="11">
         <row r="6">
           <cell r="B6">
-            <v>46265</v>
+            <v>46295</v>
           </cell>
         </row>
         <row r="8">
           <cell r="B8">
-            <v>46295</v>
+            <v>46326</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>46326</v>
+            <v>46356</v>
           </cell>
         </row>
         <row r="12">
           <cell r="B12">
-            <v>46356</v>
+            <v>46387</v>
           </cell>
         </row>
         <row r="14">
           <cell r="B14">
-            <v>46387</v>
+            <v>46418</v>
           </cell>
         </row>
         <row r="16">
           <cell r="B16">
-            <v>46418</v>
+            <v>46446</v>
           </cell>
         </row>
         <row r="18">
           <cell r="B18">
-            <v>46446</v>
+            <v>46477</v>
           </cell>
         </row>
         <row r="20">
           <cell r="B20">
-            <v>46477</v>
+            <v>46507</v>
           </cell>
         </row>
         <row r="22">
           <cell r="B22">
-            <v>46507</v>
+            <v>46538</v>
           </cell>
         </row>
         <row r="24">
           <cell r="B24">
-            <v>46538</v>
+            <v>46568</v>
           </cell>
         </row>
         <row r="26">
           <cell r="B26">
-            <v>46568</v>
+            <v>46599</v>
           </cell>
         </row>
         <row r="28">
           <cell r="B28">
-            <v>46599</v>
+            <v>46630</v>
           </cell>
         </row>
         <row r="30">
           <cell r="B30">
-            <v>46630</v>
+            <v>46660</v>
           </cell>
         </row>
         <row r="32">
           <cell r="B32">
-            <v>46660</v>
+            <v>46691</v>
           </cell>
         </row>
         <row r="34">
           <cell r="B34">
-            <v>46691</v>
+            <v>46721</v>
           </cell>
         </row>
         <row r="36">
           <cell r="B36">
-            <v>46721</v>
+            <v>46752</v>
           </cell>
         </row>
         <row r="38">
           <cell r="B38">
-            <v>46752</v>
+            <v>46783</v>
           </cell>
         </row>
         <row r="40">
           <cell r="B40">
-            <v>46783</v>
+            <v>46812</v>
           </cell>
         </row>
       </sheetData>
@@ -1401,6 +1401,21 @@
       <sheetData sheetId="1">
         <row r="1">
           <cell r="G1">
+            <v>5626.66666666667</v>
+          </cell>
+          <cell r="H1">
+            <v>28133.3333333333</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="G4">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2">
+        <row r="1">
+          <cell r="G1">
             <v>8426.66666666667</v>
           </cell>
           <cell r="H1">
@@ -1413,7 +1428,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2">
+      <sheetData sheetId="3">
         <row r="1">
           <cell r="G1">
             <v>5886.66666666667</v>
@@ -1428,7 +1443,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="3">
+      <sheetData sheetId="4">
         <row r="1">
           <cell r="G1">
             <v>5466.66666666667</v>
@@ -1443,7 +1458,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="4">
+      <sheetData sheetId="5">
         <row r="1">
           <cell r="G1">
             <v>5906.66666666667</v>
@@ -1458,7 +1473,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="5">
+      <sheetData sheetId="6">
         <row r="1">
           <cell r="G1">
             <v>5726.66666666667</v>
@@ -1473,7 +1488,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="6">
+      <sheetData sheetId="7">
         <row r="1">
           <cell r="G1">
             <v>5226.66666666667</v>
@@ -1488,7 +1503,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="7">
+      <sheetData sheetId="8">
         <row r="1">
           <cell r="G1">
             <v>5566.66666666667</v>
@@ -1497,8 +1512,13 @@
             <v>27833.3333333333</v>
           </cell>
         </row>
+        <row r="4">
+          <cell r="G4">
+            <v>0</v>
+          </cell>
+        </row>
       </sheetData>
-      <sheetData sheetId="8">
+      <sheetData sheetId="9">
         <row r="1">
           <cell r="G1">
             <v>5486.66666666667</v>
@@ -1513,7 +1533,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="9">
+      <sheetData sheetId="10">
         <row r="1">
           <cell r="G1">
             <v>5866.66666666667</v>
@@ -1528,7 +1548,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="10">
+      <sheetData sheetId="11">
         <row r="1">
           <cell r="G1">
             <v>5626.66666666667</v>
@@ -1543,28 +1563,13 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="11">
+      <sheetData sheetId="12">
         <row r="1">
           <cell r="G1">
             <v>6003.33333333333</v>
           </cell>
           <cell r="H1">
             <v>30016.6666666667</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="G4">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="12">
-        <row r="1">
-          <cell r="G1">
-            <v>5626.66666666667</v>
-          </cell>
-          <cell r="H1">
-            <v>28133.3333333333</v>
           </cell>
         </row>
         <row r="4">
@@ -1620,6 +1625,16 @@
       <sheetData sheetId="1">
         <row r="1">
           <cell r="G1">
+            <v>2229.16666666667</v>
+          </cell>
+          <cell r="H1">
+            <v>11145.8333333333</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2">
+        <row r="1">
+          <cell r="G1">
             <v>7167.625</v>
           </cell>
           <cell r="H1">
@@ -1627,7 +1642,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2">
+      <sheetData sheetId="3">
         <row r="1">
           <cell r="G1">
             <v>1153</v>
@@ -1637,7 +1652,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="3">
+      <sheetData sheetId="4">
         <row r="1">
           <cell r="G1">
             <v>1575.25</v>
@@ -1647,7 +1662,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="4">
+      <sheetData sheetId="5">
         <row r="1">
           <cell r="G1">
             <v>751.875</v>
@@ -1657,7 +1672,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="5">
+      <sheetData sheetId="6">
         <row r="1">
           <cell r="G1">
             <v>732.75</v>
@@ -1667,7 +1682,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="6">
+      <sheetData sheetId="7">
         <row r="1">
           <cell r="G1">
             <v>621.083333333333</v>
@@ -1677,7 +1692,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="7">
+      <sheetData sheetId="8">
         <row r="1">
           <cell r="G1">
             <v>851.875</v>
@@ -1687,7 +1702,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="8">
+      <sheetData sheetId="9">
         <row r="1">
           <cell r="G1">
             <v>1062.5</v>
@@ -1697,7 +1712,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="9">
+      <sheetData sheetId="10">
         <row r="1">
           <cell r="G1">
             <v>4109.5</v>
@@ -1707,7 +1722,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="10">
+      <sheetData sheetId="11">
         <row r="1">
           <cell r="G1">
             <v>1509.875</v>
@@ -1717,23 +1732,13 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="11">
+      <sheetData sheetId="12">
         <row r="1">
           <cell r="G1">
             <v>734.208333333333</v>
           </cell>
           <cell r="H1">
             <v>3671.04166666667</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="12">
-        <row r="1">
-          <cell r="G1">
-            <v>2229.16666666667</v>
-          </cell>
-          <cell r="H1">
-            <v>11145.8333333333</v>
           </cell>
         </row>
       </sheetData>
@@ -1902,7 +1907,7 @@
       <c r="I2" s="14"/>
       <c r="K2" s="15" t="n">
         <f aca="false">Vatinterface!B6</f>
-        <v>46326</v>
+        <v>46356</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1919,7 +1924,7 @@
       <c r="I3" s="14"/>
       <c r="K3" s="15" t="n">
         <f aca="false">Vatinterface!B7</f>
-        <v>46356</v>
+        <v>46387</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1936,7 +1941,7 @@
       <c r="I4" s="14"/>
       <c r="K4" s="15" t="n">
         <f aca="false">Vatinterface!B8</f>
-        <v>46387</v>
+        <v>46418</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1949,13 +1954,13 @@
       </c>
       <c r="F5" s="26"/>
       <c r="G5" s="27" t="n">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="14"/>
       <c r="K5" s="15" t="n">
         <f aca="false">Vatinterface!B9</f>
-        <v>46418</v>
+        <v>46446</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1970,7 +1975,7 @@
       <c r="I6" s="14"/>
       <c r="K6" s="15" t="n">
         <f aca="false">Vatinterface!B10</f>
-        <v>46446</v>
+        <v>46477</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1984,13 +1989,13 @@
       <c r="F7" s="31"/>
       <c r="G7" s="32" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!C1:C20)</f>
-        <v>46418</v>
+        <v>46446</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="14"/>
       <c r="K7" s="15" t="n">
         <f aca="false">Vatinterface!B11</f>
-        <v>46477</v>
+        <v>46507</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2005,7 +2010,7 @@
       <c r="I8" s="14"/>
       <c r="K8" s="15" t="n">
         <f aca="false">Vatinterface!B12</f>
-        <v>46507</v>
+        <v>46538</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2027,7 +2032,7 @@
       <c r="I9" s="14"/>
       <c r="K9" s="15" t="n">
         <f aca="false">Vatinterface!B13</f>
-        <v>46538</v>
+        <v>46568</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2042,7 +2047,7 @@
       <c r="I10" s="14"/>
       <c r="K10" s="15" t="n">
         <f aca="false">Vatinterface!B14</f>
-        <v>46568</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2063,7 +2068,7 @@
       <c r="I11" s="14"/>
       <c r="K11" s="15" t="n">
         <f aca="false">Vatinterface!B15</f>
-        <v>46599</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2078,7 +2083,7 @@
       <c r="I12" s="14"/>
       <c r="K12" s="15" t="n">
         <f aca="false">Vatinterface!B16</f>
-        <v>46630</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2100,7 +2105,7 @@
       <c r="I13" s="14"/>
       <c r="K13" s="15" t="n">
         <f aca="false">Vatinterface!B17</f>
-        <v>46660</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2115,7 +2120,7 @@
       <c r="I14" s="14"/>
       <c r="K14" s="15" t="n">
         <f aca="false">Vatinterface!B18</f>
-        <v>46691</v>
+        <v>46721</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2137,7 +2142,7 @@
       <c r="I15" s="14"/>
       <c r="K15" s="15" t="n">
         <f aca="false">Vatinterface!B19</f>
-        <v>46721</v>
+        <v>46752</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2152,7 +2157,7 @@
       <c r="I16" s="14"/>
       <c r="K16" s="15" t="n">
         <f aca="false">Vatinterface!B20</f>
-        <v>46752</v>
+        <v>46783</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2515,7 +2520,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="98" t="n">
-        <v>46338</v>
+        <v>46368</v>
       </c>
       <c r="B5" s="99" t="s">
         <v>44</v>
@@ -4611,7 +4616,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="98" t="n">
-        <v>46367</v>
+        <v>46398</v>
       </c>
       <c r="B5" s="99" t="s">
         <v>41</v>
@@ -6706,7 +6711,7 @@
     </row>
     <row r="5" s="119" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="118" t="n">
-        <v>45889</v>
+        <v>45920</v>
       </c>
       <c r="B5" s="122" t="s">
         <v>53</v>
@@ -8882,10 +8887,6 @@
     <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="98" t="s">
         <v>40</v>
-      </c>
-      <c r="G201" s="123" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
       </c>
     </row>
   </sheetData>
@@ -9003,7 +9004,7 @@
     </row>
     <row r="5" s="119" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="118" t="n">
-        <v>45924</v>
+        <v>45954</v>
       </c>
       <c r="B5" s="122" t="s">
         <v>55</v>
@@ -11179,10 +11180,6 @@
     <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="98" t="s">
         <v>40</v>
-      </c>
-      <c r="G201" s="123" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
       </c>
     </row>
   </sheetData>
@@ -11300,7 +11297,7 @@
     </row>
     <row r="5" s="119" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="118" t="n">
-        <v>46310</v>
+        <v>46341</v>
       </c>
       <c r="B5" s="122" t="s">
         <v>57</v>
@@ -13476,10 +13473,6 @@
     <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="98" t="s">
         <v>40</v>
-      </c>
-      <c r="G201" s="123" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
       </c>
     </row>
   </sheetData>
@@ -13597,7 +13590,7 @@
     </row>
     <row r="5" s="119" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="118" t="n">
-        <v>46345</v>
+        <v>46375</v>
       </c>
       <c r="B5" s="122" t="s">
         <v>59</v>
@@ -15773,10 +15766,6 @@
     <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="98" t="s">
         <v>40</v>
-      </c>
-      <c r="G201" s="123" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
       </c>
     </row>
   </sheetData>
@@ -15894,7 +15883,7 @@
     </row>
     <row r="5" s="119" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="118" t="n">
-        <v>46372</v>
+        <v>46403</v>
       </c>
       <c r="B5" s="122" t="s">
         <v>55</v>
@@ -18070,10 +18059,6 @@
     <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="98" t="s">
         <v>40</v>
-      </c>
-      <c r="G201" s="123" t="e">
-        <f aca="false">NA()</f>
-        <v>#N/A</v>
       </c>
     </row>
   </sheetData>
@@ -18146,7 +18131,7 @@
       <c r="I2" s="14"/>
       <c r="K2" s="15" t="n">
         <f aca="false">Vatinterface!B6</f>
-        <v>46326</v>
+        <v>46356</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18163,7 +18148,7 @@
       <c r="I3" s="14"/>
       <c r="K3" s="15" t="n">
         <f aca="false">Vatinterface!B7</f>
-        <v>46356</v>
+        <v>46387</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18180,7 +18165,7 @@
       <c r="I4" s="14"/>
       <c r="K4" s="15" t="n">
         <f aca="false">Vatinterface!B8</f>
-        <v>46387</v>
+        <v>46418</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18193,13 +18178,13 @@
       </c>
       <c r="F5" s="26"/>
       <c r="G5" s="27" t="n">
-        <v>46477</v>
+        <v>46507</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="14"/>
       <c r="K5" s="15" t="n">
         <f aca="false">Vatinterface!B9</f>
-        <v>46418</v>
+        <v>46446</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18214,7 +18199,7 @@
       <c r="I6" s="14"/>
       <c r="K6" s="15" t="n">
         <f aca="false">Vatinterface!B10</f>
-        <v>46446</v>
+        <v>46477</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18228,13 +18213,13 @@
       <c r="F7" s="31"/>
       <c r="G7" s="32" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!C1:C20)</f>
-        <v>46507</v>
+        <v>46538</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="14"/>
       <c r="K7" s="15" t="n">
         <f aca="false">Vatinterface!B11</f>
-        <v>46477</v>
+        <v>46507</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18249,7 +18234,7 @@
       <c r="I8" s="14"/>
       <c r="K8" s="15" t="n">
         <f aca="false">Vatinterface!B12</f>
-        <v>46507</v>
+        <v>46538</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18271,7 +18256,7 @@
       <c r="I9" s="14"/>
       <c r="K9" s="15" t="n">
         <f aca="false">Vatinterface!B13</f>
-        <v>46538</v>
+        <v>46568</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18286,7 +18271,7 @@
       <c r="I10" s="14"/>
       <c r="K10" s="15" t="n">
         <f aca="false">Vatinterface!B14</f>
-        <v>46568</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18307,7 +18292,7 @@
       <c r="I11" s="14"/>
       <c r="K11" s="15" t="n">
         <f aca="false">Vatinterface!B15</f>
-        <v>46599</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18322,7 +18307,7 @@
       <c r="I12" s="14"/>
       <c r="K12" s="15" t="n">
         <f aca="false">Vatinterface!B16</f>
-        <v>46630</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18344,7 +18329,7 @@
       <c r="I13" s="14"/>
       <c r="K13" s="15" t="n">
         <f aca="false">Vatinterface!B17</f>
-        <v>46660</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18359,7 +18344,7 @@
       <c r="I14" s="14"/>
       <c r="K14" s="15" t="n">
         <f aca="false">Vatinterface!B18</f>
-        <v>46691</v>
+        <v>46721</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18381,7 +18366,7 @@
       <c r="I15" s="14"/>
       <c r="K15" s="15" t="n">
         <f aca="false">Vatinterface!B19</f>
-        <v>46721</v>
+        <v>46752</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18396,7 +18381,7 @@
       <c r="I16" s="14"/>
       <c r="K16" s="15" t="n">
         <f aca="false">Vatinterface!B20</f>
-        <v>46752</v>
+        <v>46783</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18713,7 +18698,7 @@
       <c r="I2" s="14"/>
       <c r="K2" s="15" t="n">
         <f aca="false">Vatinterface!B6</f>
-        <v>46326</v>
+        <v>46356</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18730,7 +18715,7 @@
       <c r="I3" s="14"/>
       <c r="K3" s="15" t="n">
         <f aca="false">Vatinterface!B7</f>
-        <v>46356</v>
+        <v>46387</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18747,7 +18732,7 @@
       <c r="I4" s="14"/>
       <c r="K4" s="15" t="n">
         <f aca="false">Vatinterface!B8</f>
-        <v>46387</v>
+        <v>46418</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18760,13 +18745,13 @@
       </c>
       <c r="F5" s="26"/>
       <c r="G5" s="27" t="n">
-        <v>46568</v>
+        <v>46599</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="14"/>
       <c r="K5" s="15" t="n">
         <f aca="false">Vatinterface!B9</f>
-        <v>46418</v>
+        <v>46446</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18781,7 +18766,7 @@
       <c r="I6" s="14"/>
       <c r="K6" s="15" t="n">
         <f aca="false">Vatinterface!B10</f>
-        <v>46446</v>
+        <v>46477</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18795,13 +18780,13 @@
       <c r="F7" s="31"/>
       <c r="G7" s="32" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!C1:C20)</f>
-        <v>46599</v>
+        <v>46630</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="14"/>
       <c r="K7" s="15" t="n">
         <f aca="false">Vatinterface!B11</f>
-        <v>46477</v>
+        <v>46507</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18816,7 +18801,7 @@
       <c r="I8" s="14"/>
       <c r="K8" s="15" t="n">
         <f aca="false">Vatinterface!B12</f>
-        <v>46507</v>
+        <v>46538</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18838,7 +18823,7 @@
       <c r="I9" s="14"/>
       <c r="K9" s="15" t="n">
         <f aca="false">Vatinterface!B13</f>
-        <v>46538</v>
+        <v>46568</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18853,7 +18838,7 @@
       <c r="I10" s="14"/>
       <c r="K10" s="15" t="n">
         <f aca="false">Vatinterface!B14</f>
-        <v>46568</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18874,7 +18859,7 @@
       <c r="I11" s="14"/>
       <c r="K11" s="15" t="n">
         <f aca="false">Vatinterface!B15</f>
-        <v>46599</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18889,7 +18874,7 @@
       <c r="I12" s="14"/>
       <c r="K12" s="15" t="n">
         <f aca="false">Vatinterface!B16</f>
-        <v>46630</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18911,7 +18896,7 @@
       <c r="I13" s="14"/>
       <c r="K13" s="15" t="n">
         <f aca="false">Vatinterface!B17</f>
-        <v>46660</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18926,7 +18911,7 @@
       <c r="I14" s="14"/>
       <c r="K14" s="15" t="n">
         <f aca="false">Vatinterface!B18</f>
-        <v>46691</v>
+        <v>46721</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18948,7 +18933,7 @@
       <c r="I15" s="14"/>
       <c r="K15" s="15" t="n">
         <f aca="false">Vatinterface!B19</f>
-        <v>46721</v>
+        <v>46752</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18963,7 +18948,7 @@
       <c r="I16" s="14"/>
       <c r="K16" s="15" t="n">
         <f aca="false">Vatinterface!B20</f>
-        <v>46752</v>
+        <v>46783</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19280,7 +19265,7 @@
       <c r="I2" s="14"/>
       <c r="K2" s="15" t="n">
         <f aca="false">Vatinterface!B6</f>
-        <v>46326</v>
+        <v>46356</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19297,7 +19282,7 @@
       <c r="I3" s="14"/>
       <c r="K3" s="15" t="n">
         <f aca="false">Vatinterface!B7</f>
-        <v>46356</v>
+        <v>46387</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19314,7 +19299,7 @@
       <c r="I4" s="14"/>
       <c r="K4" s="15" t="n">
         <f aca="false">Vatinterface!B8</f>
-        <v>46387</v>
+        <v>46418</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19327,13 +19312,13 @@
       </c>
       <c r="F5" s="26"/>
       <c r="G5" s="27" t="n">
-        <v>46660</v>
+        <v>46691</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="14"/>
       <c r="K5" s="15" t="n">
         <f aca="false">Vatinterface!B9</f>
-        <v>46418</v>
+        <v>46446</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19348,7 +19333,7 @@
       <c r="I6" s="14"/>
       <c r="K6" s="15" t="n">
         <f aca="false">Vatinterface!B10</f>
-        <v>46446</v>
+        <v>46477</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19362,13 +19347,13 @@
       <c r="F7" s="31"/>
       <c r="G7" s="32" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!C1:C20)</f>
-        <v>46691</v>
+        <v>46721</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="14"/>
       <c r="K7" s="15" t="n">
         <f aca="false">Vatinterface!B11</f>
-        <v>46477</v>
+        <v>46507</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19383,7 +19368,7 @@
       <c r="I8" s="14"/>
       <c r="K8" s="15" t="n">
         <f aca="false">Vatinterface!B12</f>
-        <v>46507</v>
+        <v>46538</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19405,7 +19390,7 @@
       <c r="I9" s="14"/>
       <c r="K9" s="15" t="n">
         <f aca="false">Vatinterface!B13</f>
-        <v>46538</v>
+        <v>46568</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19420,7 +19405,7 @@
       <c r="I10" s="14"/>
       <c r="K10" s="15" t="n">
         <f aca="false">Vatinterface!B14</f>
-        <v>46568</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19441,7 +19426,7 @@
       <c r="I11" s="14"/>
       <c r="K11" s="15" t="n">
         <f aca="false">Vatinterface!B15</f>
-        <v>46599</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19456,7 +19441,7 @@
       <c r="I12" s="14"/>
       <c r="K12" s="15" t="n">
         <f aca="false">Vatinterface!B16</f>
-        <v>46630</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19478,7 +19463,7 @@
       <c r="I13" s="14"/>
       <c r="K13" s="15" t="n">
         <f aca="false">Vatinterface!B17</f>
-        <v>46660</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19493,7 +19478,7 @@
       <c r="I14" s="14"/>
       <c r="K14" s="15" t="n">
         <f aca="false">Vatinterface!B18</f>
-        <v>46691</v>
+        <v>46721</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19515,7 +19500,7 @@
       <c r="I15" s="14"/>
       <c r="K15" s="15" t="n">
         <f aca="false">Vatinterface!B19</f>
-        <v>46721</v>
+        <v>46752</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19530,7 +19515,7 @@
       <c r="I16" s="14"/>
       <c r="K16" s="15" t="n">
         <f aca="false">Vatinterface!B20</f>
-        <v>46752</v>
+        <v>46783</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19847,7 +19832,7 @@
       <c r="I2" s="14"/>
       <c r="K2" s="15" t="n">
         <f aca="false">Vatinterface!B6</f>
-        <v>46326</v>
+        <v>46356</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19864,7 +19849,7 @@
       <c r="I3" s="14"/>
       <c r="K3" s="15" t="n">
         <f aca="false">Vatinterface!B7</f>
-        <v>46356</v>
+        <v>46387</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19881,7 +19866,7 @@
       <c r="I4" s="14"/>
       <c r="K4" s="15" t="n">
         <f aca="false">Vatinterface!B8</f>
-        <v>46387</v>
+        <v>46418</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19894,13 +19879,13 @@
       </c>
       <c r="F5" s="26"/>
       <c r="G5" s="27" t="n">
-        <v>46752</v>
+        <v>46783</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="14"/>
       <c r="K5" s="15" t="n">
         <f aca="false">Vatinterface!B9</f>
-        <v>46418</v>
+        <v>46446</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19915,7 +19900,7 @@
       <c r="I6" s="14"/>
       <c r="K6" s="15" t="n">
         <f aca="false">Vatinterface!B10</f>
-        <v>46446</v>
+        <v>46477</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19929,13 +19914,13 @@
       <c r="F7" s="31"/>
       <c r="G7" s="32" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!C1:C20)</f>
-        <v>46783</v>
+        <v>46812</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="14"/>
       <c r="K7" s="15" t="n">
         <f aca="false">Vatinterface!B11</f>
-        <v>46477</v>
+        <v>46507</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19950,7 +19935,7 @@
       <c r="I8" s="14"/>
       <c r="K8" s="15" t="n">
         <f aca="false">Vatinterface!B12</f>
-        <v>46507</v>
+        <v>46538</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19972,7 +19957,7 @@
       <c r="I9" s="14"/>
       <c r="K9" s="15" t="n">
         <f aca="false">Vatinterface!B13</f>
-        <v>46538</v>
+        <v>46568</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19987,7 +19972,7 @@
       <c r="I10" s="14"/>
       <c r="K10" s="15" t="n">
         <f aca="false">Vatinterface!B14</f>
-        <v>46568</v>
+        <v>46599</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20008,7 +19993,7 @@
       <c r="I11" s="14"/>
       <c r="K11" s="15" t="n">
         <f aca="false">Vatinterface!B15</f>
-        <v>46599</v>
+        <v>46630</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20023,7 +20008,7 @@
       <c r="I12" s="14"/>
       <c r="K12" s="15" t="n">
         <f aca="false">Vatinterface!B16</f>
-        <v>46630</v>
+        <v>46660</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20045,7 +20030,7 @@
       <c r="I13" s="14"/>
       <c r="K13" s="15" t="n">
         <f aca="false">Vatinterface!B17</f>
-        <v>46660</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20060,7 +20045,7 @@
       <c r="I14" s="14"/>
       <c r="K14" s="15" t="n">
         <f aca="false">Vatinterface!B18</f>
-        <v>46691</v>
+        <v>46721</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20082,7 +20067,7 @@
       <c r="I15" s="14"/>
       <c r="K15" s="15" t="n">
         <f aca="false">Vatinterface!B19</f>
-        <v>46721</v>
+        <v>46752</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20097,7 +20082,7 @@
       <c r="I16" s="14"/>
       <c r="K16" s="15" t="n">
         <f aca="false">Vatinterface!B20</f>
-        <v>46752</v>
+        <v>46783</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20458,11 +20443,11 @@
       <c r="A4" s="84"/>
       <c r="B4" s="85" t="n">
         <f aca="false">[1]Admin!$B$6</f>
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="C4" s="85" t="n">
         <f aca="false">B5</f>
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="D4" s="86" t="n">
         <f aca="false">S02Y1!$H$1</f>
@@ -20486,7 +20471,7 @@
       <c r="K4" s="87"/>
       <c r="L4" s="88"/>
       <c r="M4" s="89" t="n">
-        <f aca="false">IF([2]Oct!$G$4&gt;0,[2]Oct!$G$4,0)</f>
+        <f aca="false">IF([2]Nov!$G$4&gt;0,[2]Nov!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N4" s="90"/>
@@ -20495,11 +20480,11 @@
       <c r="A5" s="84"/>
       <c r="B5" s="85" t="n">
         <f aca="false">[1]Admin!$B$8</f>
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C5" s="85" t="n">
         <f aca="false">B6</f>
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="D5" s="86" t="n">
         <f aca="false">S03Y1!$H$1</f>
@@ -20523,7 +20508,7 @@
       <c r="K5" s="87"/>
       <c r="L5" s="88"/>
       <c r="M5" s="89" t="n">
-        <f aca="false">IF([2]Oct!$G$4&gt;0,[2]Oct!$G$4,0)</f>
+        <f aca="false">IF([2]Nov!$G$4&gt;0,[2]Nov!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N5" s="90"/>
@@ -20532,14 +20517,14 @@
       <c r="A6" s="84"/>
       <c r="B6" s="85" t="n">
         <f aca="false">[1]Admin!$B$10</f>
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="C6" s="85" t="n">
         <f aca="false">B7</f>
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="D6" s="86" t="n">
-        <f aca="false">[2]Oct!$H$1</f>
+        <f aca="false">[2]Nov!$H$1</f>
         <v>27833.3333333333</v>
       </c>
       <c r="E6" s="87" t="n">
@@ -20547,7 +20532,7 @@
         <v>33833.3333333333</v>
       </c>
       <c r="F6" s="87" t="n">
-        <f aca="false">[2]Oct!$G$1</f>
+        <f aca="false">[2]Nov!$G$1</f>
         <v>5566.66666666667</v>
       </c>
       <c r="G6" s="87" t="n">
@@ -20555,7 +20540,7 @@
         <v>6766.66666666667</v>
       </c>
       <c r="H6" s="87" t="n">
-        <f aca="false">[3]Oct!$H$1</f>
+        <f aca="false">[3]Nov!$H$1</f>
         <v>4259.375</v>
       </c>
       <c r="I6" s="87" t="n">
@@ -20563,7 +20548,7 @@
         <v>5859.375</v>
       </c>
       <c r="J6" s="87" t="n">
-        <f aca="false">[3]Oct!$G$1</f>
+        <f aca="false">[3]Nov!$G$1</f>
         <v>851.875</v>
       </c>
       <c r="K6" s="87" t="n">
@@ -20572,7 +20557,7 @@
       </c>
       <c r="L6" s="88"/>
       <c r="M6" s="89" t="n">
-        <f aca="false">IF([2]Oct!$G$4&gt;0,[2]Oct!$G$4,0)</f>
+        <f aca="false">IF([2]Nov!$G$4&gt;0,[2]Nov!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N6" s="90"/>
@@ -20581,14 +20566,14 @@
       <c r="A7" s="84"/>
       <c r="B7" s="85" t="n">
         <f aca="false">[1]Admin!$B$12</f>
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="C7" s="85" t="n">
         <f aca="false">B8</f>
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="D7" s="86" t="n">
-        <f aca="false">[2]Nov!$H$1</f>
+        <f aca="false">[2]Dec!$H$1</f>
         <v>27433.3333333333</v>
       </c>
       <c r="E7" s="87" t="n">
@@ -20596,7 +20581,7 @@
         <v>57266.6666666666</v>
       </c>
       <c r="F7" s="87" t="n">
-        <f aca="false">[2]Nov!$G$1</f>
+        <f aca="false">[2]Dec!$G$1</f>
         <v>5486.66666666667</v>
       </c>
       <c r="G7" s="87" t="n">
@@ -20604,7 +20589,7 @@
         <v>11453.3333333333</v>
       </c>
       <c r="H7" s="87" t="n">
-        <f aca="false">[3]Nov!$H$1</f>
+        <f aca="false">[3]Dec!$H$1</f>
         <v>5312.5</v>
       </c>
       <c r="I7" s="87" t="n">
@@ -20612,7 +20597,7 @@
         <v>10571.875</v>
       </c>
       <c r="J7" s="87" t="n">
-        <f aca="false">[3]Nov!$G$1</f>
+        <f aca="false">[3]Dec!$G$1</f>
         <v>1062.5</v>
       </c>
       <c r="K7" s="87" t="n">
@@ -20621,7 +20606,7 @@
       </c>
       <c r="L7" s="88"/>
       <c r="M7" s="89" t="n">
-        <f aca="false">IF([2]Nov!$G$4&gt;0,[2]Nov!$G$4,0)</f>
+        <f aca="false">IF([2]Dec!$G$4&gt;0,[2]Dec!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N7" s="90"/>
@@ -20630,14 +20615,14 @@
       <c r="A8" s="84"/>
       <c r="B8" s="85" t="n">
         <f aca="false">[1]Admin!$B$14</f>
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="C8" s="85" t="n">
         <f aca="false">B9</f>
-        <v>46418</v>
+        <v>46446</v>
       </c>
       <c r="D8" s="86" t="n">
-        <f aca="false">[2]Dec!$H$1</f>
+        <f aca="false">[2]Jan!$H$1</f>
         <v>29333.3333333333</v>
       </c>
       <c r="E8" s="87" t="n">
@@ -20645,7 +20630,7 @@
         <v>84599.9999999999</v>
       </c>
       <c r="F8" s="87" t="n">
-        <f aca="false">[2]Dec!$G$1</f>
+        <f aca="false">[2]Jan!$G$1</f>
         <v>5866.66666666667</v>
       </c>
       <c r="G8" s="87" t="n">
@@ -20653,7 +20638,7 @@
         <v>16920</v>
       </c>
       <c r="H8" s="87" t="n">
-        <f aca="false">[3]Dec!$H$1</f>
+        <f aca="false">[3]Jan!$H$1</f>
         <v>20547.5</v>
       </c>
       <c r="I8" s="87" t="n">
@@ -20661,7 +20646,7 @@
         <v>30119.375</v>
       </c>
       <c r="J8" s="87" t="n">
-        <f aca="false">[3]Dec!$G$1</f>
+        <f aca="false">[3]Jan!$G$1</f>
         <v>4109.5</v>
       </c>
       <c r="K8" s="87" t="n">
@@ -20670,7 +20655,7 @@
       </c>
       <c r="L8" s="88"/>
       <c r="M8" s="89" t="n">
-        <f aca="false">IF([2]Dec!$G$4&gt;0,[2]Dec!$G$4,0)</f>
+        <f aca="false">IF([2]Jan!$G$4&gt;0,[2]Jan!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N8" s="90"/>
@@ -20679,14 +20664,14 @@
       <c r="A9" s="84"/>
       <c r="B9" s="85" t="n">
         <f aca="false">[1]Admin!$B$16</f>
-        <v>46418</v>
+        <v>46446</v>
       </c>
       <c r="C9" s="85" t="n">
         <f aca="false">B10</f>
-        <v>46446</v>
+        <v>46477</v>
       </c>
       <c r="D9" s="86" t="n">
-        <f aca="false">[2]Jan!$H$1</f>
+        <f aca="false">[2]Feb!$H$1</f>
         <v>28133.3333333333</v>
       </c>
       <c r="E9" s="87" t="n">
@@ -20694,7 +20679,7 @@
         <v>84899.9999999999</v>
       </c>
       <c r="F9" s="87" t="n">
-        <f aca="false">[2]Jan!$G$1</f>
+        <f aca="false">[2]Feb!$G$1</f>
         <v>5626.66666666667</v>
       </c>
       <c r="G9" s="87" t="n">
@@ -20702,7 +20687,7 @@
         <v>16980</v>
       </c>
       <c r="H9" s="87" t="n">
-        <f aca="false">[3]Jan!$H$1</f>
+        <f aca="false">[3]Feb!$H$1</f>
         <v>7549.375</v>
       </c>
       <c r="I9" s="87" t="n">
@@ -20710,7 +20695,7 @@
         <v>33409.375</v>
       </c>
       <c r="J9" s="87" t="n">
-        <f aca="false">[3]Jan!$G$1</f>
+        <f aca="false">[3]Feb!$G$1</f>
         <v>1509.875</v>
       </c>
       <c r="K9" s="87" t="n">
@@ -20719,7 +20704,7 @@
       </c>
       <c r="L9" s="88"/>
       <c r="M9" s="89" t="n">
-        <f aca="false">IF([2]Jan!$G$4&gt;0,[2]Jan!$G$4,0)</f>
+        <f aca="false">IF([2]Feb!$G$4&gt;0,[2]Feb!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N9" s="90"/>
@@ -20728,14 +20713,14 @@
       <c r="A10" s="84"/>
       <c r="B10" s="85" t="n">
         <f aca="false">[1]Admin!$B$18</f>
-        <v>46446</v>
+        <v>46477</v>
       </c>
       <c r="C10" s="85" t="n">
         <f aca="false">B11</f>
-        <v>46477</v>
+        <v>46507</v>
       </c>
       <c r="D10" s="86" t="n">
-        <f aca="false">[2]Feb!$H$1</f>
+        <f aca="false">[2]Mar!$H$1</f>
         <v>30016.6666666667</v>
       </c>
       <c r="E10" s="87" t="n">
@@ -20743,7 +20728,7 @@
         <v>87483.3333333333</v>
       </c>
       <c r="F10" s="87" t="n">
-        <f aca="false">[2]Feb!$G$1</f>
+        <f aca="false">[2]Mar!$G$1</f>
         <v>6003.33333333333</v>
       </c>
       <c r="G10" s="87" t="n">
@@ -20751,7 +20736,7 @@
         <v>17496.6666666667</v>
       </c>
       <c r="H10" s="87" t="n">
-        <f aca="false">[3]Feb!$H$1</f>
+        <f aca="false">[3]Mar!$H$1</f>
         <v>3671.04166666667</v>
       </c>
       <c r="I10" s="87" t="n">
@@ -20759,7 +20744,7 @@
         <v>31767.9166666667</v>
       </c>
       <c r="J10" s="87" t="n">
-        <f aca="false">[3]Feb!$G$1</f>
+        <f aca="false">[3]Mar!$G$1</f>
         <v>734.208333333333</v>
       </c>
       <c r="K10" s="87" t="n">
@@ -20768,7 +20753,7 @@
       </c>
       <c r="L10" s="88"/>
       <c r="M10" s="89" t="n">
-        <f aca="false">IF([2]Feb!$G$4&gt;0,[2]Feb!$G$4,0)</f>
+        <f aca="false">IF([2]Mar!$G$4&gt;0,[2]Mar!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N10" s="90"/>
@@ -20777,14 +20762,14 @@
       <c r="A11" s="84"/>
       <c r="B11" s="85" t="n">
         <f aca="false">[1]Admin!$B$20</f>
-        <v>46477</v>
+        <v>46507</v>
       </c>
       <c r="C11" s="85" t="n">
         <f aca="false">B12</f>
-        <v>46507</v>
+        <v>46538</v>
       </c>
       <c r="D11" s="86" t="n">
-        <f aca="false">[2]Mar!$H$1</f>
+        <f aca="false">[2]Apr!$H$1</f>
         <v>28133.3333333333</v>
       </c>
       <c r="E11" s="87" t="n">
@@ -20792,7 +20777,7 @@
         <v>86283.3333333333</v>
       </c>
       <c r="F11" s="87" t="n">
-        <f aca="false">[2]Mar!$G$1</f>
+        <f aca="false">[2]Apr!$G$1</f>
         <v>5626.66666666667</v>
       </c>
       <c r="G11" s="87" t="n">
@@ -20800,7 +20785,7 @@
         <v>17256.6666666667</v>
       </c>
       <c r="H11" s="87" t="n">
-        <f aca="false">[3]Mar!$H$1</f>
+        <f aca="false">[3]Apr!$H$1</f>
         <v>11145.8333333333</v>
       </c>
       <c r="I11" s="87" t="n">
@@ -20808,7 +20793,7 @@
         <v>22366.25</v>
       </c>
       <c r="J11" s="87" t="n">
-        <f aca="false">[3]Mar!$G$1</f>
+        <f aca="false">[3]Apr!$G$1</f>
         <v>2229.16666666667</v>
       </c>
       <c r="K11" s="87" t="n">
@@ -20817,7 +20802,7 @@
       </c>
       <c r="L11" s="88"/>
       <c r="M11" s="89" t="n">
-        <f aca="false">IF([2]Mar!$G$4&gt;0,[2]Mar!$G$4,0)</f>
+        <f aca="false">IF([2]Apr!$G$4&gt;0,[2]Apr!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N11" s="90"/>
@@ -20826,14 +20811,14 @@
       <c r="A12" s="84"/>
       <c r="B12" s="85" t="n">
         <f aca="false">[1]Admin!$B$22</f>
-        <v>46507</v>
+        <v>46538</v>
       </c>
       <c r="C12" s="85" t="n">
         <f aca="false">B13</f>
-        <v>46538</v>
+        <v>46568</v>
       </c>
       <c r="D12" s="86" t="n">
-        <f aca="false">[2]Apr!$H$1</f>
+        <f aca="false">[2]May!$H$1</f>
         <v>42133.3333333333</v>
       </c>
       <c r="E12" s="87" t="n">
@@ -20841,7 +20826,7 @@
         <v>100283.333333333</v>
       </c>
       <c r="F12" s="87" t="n">
-        <f aca="false">[2]Apr!$G$1</f>
+        <f aca="false">[2]May!$G$1</f>
         <v>8426.66666666667</v>
       </c>
       <c r="G12" s="87" t="n">
@@ -20849,7 +20834,7 @@
         <v>20056.6666666667</v>
       </c>
       <c r="H12" s="87" t="n">
-        <f aca="false">[3]Apr!$H$1</f>
+        <f aca="false">[3]May!$H$1</f>
         <v>35838.125</v>
       </c>
       <c r="I12" s="87" t="n">
@@ -20857,7 +20842,7 @@
         <v>50655</v>
       </c>
       <c r="J12" s="87" t="n">
-        <f aca="false">[3]Apr!$G$1</f>
+        <f aca="false">[3]May!$G$1</f>
         <v>7167.625</v>
       </c>
       <c r="K12" s="87" t="n">
@@ -20866,7 +20851,7 @@
       </c>
       <c r="L12" s="88"/>
       <c r="M12" s="89" t="n">
-        <f aca="false">IF([2]Apr!$G$4&gt;0,[2]Apr!$G$4,0)</f>
+        <f aca="false">IF([2]May!$G$4&gt;0,[2]May!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N12" s="90"/>
@@ -20875,14 +20860,14 @@
       <c r="A13" s="84"/>
       <c r="B13" s="85" t="n">
         <f aca="false">[1]Admin!$B$24</f>
-        <v>46538</v>
+        <v>46568</v>
       </c>
       <c r="C13" s="85" t="n">
         <f aca="false">B14</f>
-        <v>46568</v>
+        <v>46599</v>
       </c>
       <c r="D13" s="86" t="n">
-        <f aca="false">[2]May!$H$1</f>
+        <f aca="false">[2]Jun!$H$1</f>
         <v>29433.3333333333</v>
       </c>
       <c r="E13" s="87" t="n">
@@ -20890,7 +20875,7 @@
         <v>99699.9999999999</v>
       </c>
       <c r="F13" s="87" t="n">
-        <f aca="false">[2]May!$G$1</f>
+        <f aca="false">[2]Jun!$G$1</f>
         <v>5886.66666666667</v>
       </c>
       <c r="G13" s="87" t="n">
@@ -20898,7 +20883,7 @@
         <v>19940</v>
       </c>
       <c r="H13" s="87" t="n">
-        <f aca="false">[3]May!$H$1</f>
+        <f aca="false">[3]Jun!$H$1</f>
         <v>5765</v>
       </c>
       <c r="I13" s="87" t="n">
@@ -20906,7 +20891,7 @@
         <v>52748.9583333333</v>
       </c>
       <c r="J13" s="87" t="n">
-        <f aca="false">[3]May!$G$1</f>
+        <f aca="false">[3]Jun!$G$1</f>
         <v>1153</v>
       </c>
       <c r="K13" s="87" t="n">
@@ -20915,7 +20900,7 @@
       </c>
       <c r="L13" s="88"/>
       <c r="M13" s="89" t="n">
-        <f aca="false">IF([2]May!$G$4&gt;0,[2]May!$G$4,0)</f>
+        <f aca="false">IF([2]Jun!$G$4&gt;0,[2]Jun!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N13" s="90"/>
@@ -20924,14 +20909,14 @@
       <c r="A14" s="84"/>
       <c r="B14" s="85" t="n">
         <f aca="false">[1]Admin!$B$26</f>
-        <v>46568</v>
+        <v>46599</v>
       </c>
       <c r="C14" s="85" t="n">
         <f aca="false">B15</f>
-        <v>46599</v>
+        <v>46630</v>
       </c>
       <c r="D14" s="86" t="n">
-        <f aca="false">[2]Jun!$H$1</f>
+        <f aca="false">[2]Jul!$H$1</f>
         <v>27333.3333333333</v>
       </c>
       <c r="E14" s="87" t="n">
@@ -20939,7 +20924,7 @@
         <v>98899.9999999999</v>
       </c>
       <c r="F14" s="87" t="n">
-        <f aca="false">[2]Jun!$G$1</f>
+        <f aca="false">[2]Jul!$G$1</f>
         <v>5466.66666666667</v>
       </c>
       <c r="G14" s="87" t="n">
@@ -20947,7 +20932,7 @@
         <v>19780</v>
       </c>
       <c r="H14" s="87" t="n">
-        <f aca="false">[3]Jun!$H$1</f>
+        <f aca="false">[3]Jul!$H$1</f>
         <v>7876.25</v>
       </c>
       <c r="I14" s="87" t="n">
@@ -20955,7 +20940,7 @@
         <v>49479.375</v>
       </c>
       <c r="J14" s="87" t="n">
-        <f aca="false">[3]Jun!$G$1</f>
+        <f aca="false">[3]Jul!$G$1</f>
         <v>1575.25</v>
       </c>
       <c r="K14" s="87" t="n">
@@ -20964,7 +20949,7 @@
       </c>
       <c r="L14" s="88"/>
       <c r="M14" s="89" t="n">
-        <f aca="false">IF([2]Jun!$G$4&gt;0,[2]Jun!$G$4,0)</f>
+        <f aca="false">IF([2]Jul!$G$4&gt;0,[2]Jul!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N14" s="90"/>
@@ -20973,14 +20958,14 @@
       <c r="A15" s="84"/>
       <c r="B15" s="85" t="n">
         <f aca="false">[1]Admin!$B$28</f>
-        <v>46599</v>
+        <v>46630</v>
       </c>
       <c r="C15" s="85" t="n">
         <f aca="false">B16</f>
-        <v>46630</v>
+        <v>46660</v>
       </c>
       <c r="D15" s="86" t="n">
-        <f aca="false">[2]Jul!$H$1</f>
+        <f aca="false">[2]Aug!$H$1</f>
         <v>29533.3333333333</v>
       </c>
       <c r="E15" s="87" t="n">
@@ -20988,7 +20973,7 @@
         <v>86299.9999999999</v>
       </c>
       <c r="F15" s="87" t="n">
-        <f aca="false">[2]Jul!$G$1</f>
+        <f aca="false">[2]Aug!$G$1</f>
         <v>5906.66666666667</v>
       </c>
       <c r="G15" s="87" t="n">
@@ -20996,7 +20981,7 @@
         <v>17260</v>
       </c>
       <c r="H15" s="87" t="n">
-        <f aca="false">[3]Jul!$H$1</f>
+        <f aca="false">[3]Aug!$H$1</f>
         <v>3759.375</v>
       </c>
       <c r="I15" s="87" t="n">
@@ -21004,7 +20989,7 @@
         <v>17400.625</v>
       </c>
       <c r="J15" s="87" t="n">
-        <f aca="false">[3]Jul!$G$1</f>
+        <f aca="false">[3]Aug!$G$1</f>
         <v>751.875</v>
       </c>
       <c r="K15" s="87" t="n">
@@ -21013,7 +20998,7 @@
       </c>
       <c r="L15" s="88"/>
       <c r="M15" s="89" t="n">
-        <f aca="false">IF([2]Jul!$G$4&gt;0,[2]Jul!$G$4,0)</f>
+        <f aca="false">IF([2]Aug!$G$4&gt;0,[2]Aug!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N15" s="90"/>
@@ -21022,14 +21007,14 @@
       <c r="A16" s="84"/>
       <c r="B16" s="85" t="n">
         <f aca="false">[1]Admin!$B$30</f>
-        <v>46630</v>
+        <v>46660</v>
       </c>
       <c r="C16" s="85" t="n">
         <f aca="false">B17</f>
-        <v>46660</v>
+        <v>46691</v>
       </c>
       <c r="D16" s="86" t="n">
-        <f aca="false">[2]Aug!$H$1</f>
+        <f aca="false">[2]Sep!$H$1</f>
         <v>28633.3333333333</v>
       </c>
       <c r="E16" s="87" t="n">
@@ -21037,7 +21022,7 @@
         <v>85499.9999999999</v>
       </c>
       <c r="F16" s="87" t="n">
-        <f aca="false">[2]Aug!$G$1</f>
+        <f aca="false">[2]Sep!$G$1</f>
         <v>5726.66666666667</v>
       </c>
       <c r="G16" s="87" t="n">
@@ -21045,7 +21030,7 @@
         <v>17100</v>
       </c>
       <c r="H16" s="87" t="n">
-        <f aca="false">[3]Aug!$H$1</f>
+        <f aca="false">[3]Sep!$H$1</f>
         <v>3663.75</v>
       </c>
       <c r="I16" s="87" t="n">
@@ -21053,7 +21038,7 @@
         <v>15299.375</v>
       </c>
       <c r="J16" s="87" t="n">
-        <f aca="false">[3]Aug!$G$1</f>
+        <f aca="false">[3]Sep!$G$1</f>
         <v>732.75</v>
       </c>
       <c r="K16" s="87" t="n">
@@ -21062,7 +21047,7 @@
       </c>
       <c r="L16" s="88"/>
       <c r="M16" s="89" t="n">
-        <f aca="false">IF([2]Aug!$G$4&gt;0,[2]Aug!$G$4,0)</f>
+        <f aca="false">IF([2]Sep!$G$4&gt;0,[2]Sep!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N16" s="90"/>
@@ -21071,14 +21056,14 @@
       <c r="A17" s="84"/>
       <c r="B17" s="85" t="n">
         <f aca="false">[1]Admin!$B$32</f>
-        <v>46660</v>
+        <v>46691</v>
       </c>
       <c r="C17" s="85" t="n">
         <f aca="false">B18</f>
-        <v>46691</v>
+        <v>46721</v>
       </c>
       <c r="D17" s="86" t="n">
-        <f aca="false">[2]Sep!$H$1</f>
+        <f aca="false">[2]Oct!$H$1</f>
         <v>26133.3333333333</v>
       </c>
       <c r="E17" s="87" t="n">
@@ -21086,7 +21071,7 @@
         <v>84299.9999999999</v>
       </c>
       <c r="F17" s="87" t="n">
-        <f aca="false">[2]Sep!$G$1</f>
+        <f aca="false">[2]Oct!$G$1</f>
         <v>5226.66666666667</v>
       </c>
       <c r="G17" s="87" t="n">
@@ -21094,7 +21079,7 @@
         <v>16860</v>
       </c>
       <c r="H17" s="87" t="n">
-        <f aca="false">[3]Sep!$H$1</f>
+        <f aca="false">[3]Oct!$H$1</f>
         <v>3105.41666666667</v>
       </c>
       <c r="I17" s="87" t="n">
@@ -21102,7 +21087,7 @@
         <v>10528.5416666667</v>
       </c>
       <c r="J17" s="87" t="n">
-        <f aca="false">[3]Sep!$G$1</f>
+        <f aca="false">[3]Oct!$G$1</f>
         <v>621.083333333333</v>
       </c>
       <c r="K17" s="87" t="n">
@@ -21111,7 +21096,7 @@
       </c>
       <c r="L17" s="88"/>
       <c r="M17" s="89" t="n">
-        <f aca="false">IF([2]Sep!$G$4&gt;0,[2]Sep!$G$4,0)</f>
+        <f aca="false">IF([2]Oct!$G$4&gt;0,[2]Oct!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N17" s="90"/>
@@ -21120,11 +21105,11 @@
       <c r="A18" s="84"/>
       <c r="B18" s="85" t="n">
         <f aca="false">[1]Admin!$B$34</f>
-        <v>46691</v>
+        <v>46721</v>
       </c>
       <c r="C18" s="85" t="n">
         <f aca="false">B19</f>
-        <v>46721</v>
+        <v>46752</v>
       </c>
       <c r="D18" s="86" t="n">
         <f aca="false">S04Y2!$H$1</f>
@@ -21160,7 +21145,7 @@
       </c>
       <c r="L18" s="88"/>
       <c r="M18" s="89" t="n">
-        <f aca="false">IF([2]Sep!$G$4&gt;0,[2]Sep!$G$4,0)</f>
+        <f aca="false">IF([2]Oct!$G$4&gt;0,[2]Oct!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N18" s="90"/>
@@ -21169,11 +21154,11 @@
       <c r="A19" s="84"/>
       <c r="B19" s="85" t="n">
         <f aca="false">[1]Admin!$B$36</f>
-        <v>46721</v>
+        <v>46752</v>
       </c>
       <c r="C19" s="85" t="n">
         <f aca="false">[1]Admin!$B$38</f>
-        <v>46752</v>
+        <v>46783</v>
       </c>
       <c r="D19" s="86" t="n">
         <f aca="false">S05Y2!$H$1</f>
@@ -21209,7 +21194,7 @@
       </c>
       <c r="L19" s="88"/>
       <c r="M19" s="89" t="n">
-        <f aca="false">IF([2]Sep!$G$4&gt;0,[2]Sep!$G$4,0)</f>
+        <f aca="false">IF([2]Oct!$G$4&gt;0,[2]Oct!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N19" s="90"/>
@@ -21218,11 +21203,11 @@
       <c r="A20" s="84"/>
       <c r="B20" s="85" t="n">
         <f aca="false">[1]Admin!$B$38</f>
-        <v>46752</v>
+        <v>46783</v>
       </c>
       <c r="C20" s="91" t="n">
         <f aca="false">[1]Admin!$B$40</f>
-        <v>46783</v>
+        <v>46812</v>
       </c>
       <c r="D20" s="86" t="n">
         <f aca="false">S06Y2!$H$1</f>
@@ -21258,7 +21243,7 @@
       </c>
       <c r="L20" s="88"/>
       <c r="M20" s="89" t="n">
-        <f aca="false">IF([2]Sep!$G$4&gt;0,[2]Sep!$G$4,0)</f>
+        <f aca="false">IF([2]Oct!$G$4&gt;0,[2]Oct!$G$4,0)</f>
         <v>0</v>
       </c>
       <c r="N20" s="90"/>
@@ -21383,7 +21368,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="98" t="n">
-        <v>45883</v>
+        <v>45914</v>
       </c>
       <c r="B5" s="99" t="s">
         <v>38</v>
@@ -23479,7 +23464,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="98" t="n">
-        <v>45918</v>
+        <v>45948</v>
       </c>
       <c r="B5" s="99" t="s">
         <v>41</v>
@@ -25575,7 +25560,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="98" t="n">
-        <v>46305</v>
+        <v>46336</v>
       </c>
       <c r="B5" s="99" t="s">
         <v>38</v>

--- a/examples/ltd-latest/Vatreturns.xlsx
+++ b/examples/ltd-latest/Vatreturns.xlsx
@@ -2520,7 +2520,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="98" t="n">
-        <v>46368</v>
+        <v>46733</v>
       </c>
       <c r="B5" s="99" t="s">
         <v>44</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="98" t="n">
-        <v>46398</v>
+        <v>46763</v>
       </c>
       <c r="B5" s="99" t="s">
         <v>41</v>
@@ -6711,7 +6711,7 @@
     </row>
     <row r="5" s="119" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="118" t="n">
-        <v>45920</v>
+        <v>46285</v>
       </c>
       <c r="B5" s="122" t="s">
         <v>53</v>
@@ -9004,7 +9004,7 @@
     </row>
     <row r="5" s="119" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="118" t="n">
-        <v>45954</v>
+        <v>46319</v>
       </c>
       <c r="B5" s="122" t="s">
         <v>55</v>
@@ -11297,7 +11297,7 @@
     </row>
     <row r="5" s="119" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="118" t="n">
-        <v>46341</v>
+        <v>46706</v>
       </c>
       <c r="B5" s="122" t="s">
         <v>57</v>
@@ -13590,7 +13590,7 @@
     </row>
     <row r="5" s="119" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="118" t="n">
-        <v>46375</v>
+        <v>46740</v>
       </c>
       <c r="B5" s="122" t="s">
         <v>59</v>
@@ -15883,7 +15883,7 @@
     </row>
     <row r="5" s="119" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="118" t="n">
-        <v>46403</v>
+        <v>46768</v>
       </c>
       <c r="B5" s="122" t="s">
         <v>55</v>
@@ -21368,7 +21368,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="98" t="n">
-        <v>45914</v>
+        <v>46279</v>
       </c>
       <c r="B5" s="99" t="s">
         <v>38</v>
@@ -23464,7 +23464,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="98" t="n">
-        <v>45948</v>
+        <v>46313</v>
       </c>
       <c r="B5" s="99" t="s">
         <v>41</v>
@@ -25560,7 +25560,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="98" t="n">
-        <v>46336</v>
+        <v>46701</v>
       </c>
       <c r="B5" s="99" t="s">
         <v>38</v>

--- a/examples/ltd-latest/Vatreturns.xlsx
+++ b/examples/ltd-latest/Vatreturns.xlsx
@@ -1735,10 +1735,10 @@
       <sheetData sheetId="12">
         <row r="1">
           <cell r="G1">
-            <v>734.208333333333</v>
+            <v>792.541666666667</v>
           </cell>
           <cell r="H1">
-            <v>3671.04166666667</v>
+            <v>3962.70833333333</v>
           </cell>
         </row>
       </sheetData>
@@ -18360,7 +18360,7 @@
       </c>
       <c r="G15" s="37" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!K1:K20)</f>
-        <v>4473.25</v>
+        <v>4531.58333333334</v>
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="14"/>
@@ -18398,7 +18398,7 @@
       </c>
       <c r="G17" s="37" t="n">
         <f aca="false">G13-G15</f>
-        <v>12783.4166666667</v>
+        <v>12725.0833333333</v>
       </c>
       <c r="H17" s="13"/>
       <c r="I17" s="14"/>
@@ -18486,7 +18486,7 @@
       </c>
       <c r="G23" s="52" t="n">
         <f aca="false">LOOKUP(G$5,Vatinterface!B1:B20,Vatinterface!I1:I20)</f>
-        <v>22366.25</v>
+        <v>22657.9166666666</v>
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="14"/>
@@ -20737,19 +20737,19 @@
       </c>
       <c r="H10" s="87" t="n">
         <f aca="false">[3]Mar!$H$1</f>
-        <v>3671.04166666667</v>
+        <v>3962.70833333333</v>
       </c>
       <c r="I10" s="87" t="n">
         <f aca="false">SUM(H8:H10)</f>
-        <v>31767.9166666667</v>
+        <v>32059.5833333333</v>
       </c>
       <c r="J10" s="87" t="n">
         <f aca="false">[3]Mar!$G$1</f>
-        <v>734.208333333333</v>
+        <v>792.541666666667</v>
       </c>
       <c r="K10" s="87" t="n">
         <f aca="false">SUM(J8:J10)</f>
-        <v>6353.58333333333</v>
+        <v>6411.91666666667</v>
       </c>
       <c r="L10" s="88"/>
       <c r="M10" s="89" t="n">
@@ -20790,7 +20790,7 @@
       </c>
       <c r="I11" s="87" t="n">
         <f aca="false">SUM(H9:H11)</f>
-        <v>22366.25</v>
+        <v>22657.9166666666</v>
       </c>
       <c r="J11" s="87" t="n">
         <f aca="false">[3]Apr!$G$1</f>
@@ -20798,7 +20798,7 @@
       </c>
       <c r="K11" s="87" t="n">
         <f aca="false">SUM(J9:J11)</f>
-        <v>4473.25</v>
+        <v>4531.58333333334</v>
       </c>
       <c r="L11" s="88"/>
       <c r="M11" s="89" t="n">
@@ -20839,7 +20839,7 @@
       </c>
       <c r="I12" s="87" t="n">
         <f aca="false">SUM(H10:H12)</f>
-        <v>50655</v>
+        <v>50946.6666666666</v>
       </c>
       <c r="J12" s="87" t="n">
         <f aca="false">[3]May!$G$1</f>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="K12" s="87" t="n">
         <f aca="false">SUM(J10:J12)</f>
-        <v>10131</v>
+        <v>10189.3333333333</v>
       </c>
       <c r="L12" s="88"/>
       <c r="M12" s="89" t="n">
